--- a/data/July.xlsx
+++ b/data/July.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52EAA508-9677-4C35-BB54-9CF6271D11D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{324BDE42-9EA2-4C46-A9C4-9A811CDAA27E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -172,18 +172,6 @@
     <t>สาขาแยกคีรีชลบุรี-องค์พระที่่ทำเอง อายุกว่า 20 ปี</t>
   </si>
   <si>
-    <t xml:space="preserve"> Main Account-ลูกค้านำจี้มาขายได้ราคาเกินคาด!</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Main Account-ทองคุณแท้แค่ไหน</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Main Account-ใครบอก ทองชุบ ไม่มีราคา</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Main Account-ทองเก่า เศษทองอาจได้เงินหมื่น!</t>
-  </si>
-  <si>
     <t>KOLs-fern for Fun เฟิร์น ฟ ฟัน</t>
   </si>
   <si>
@@ -443,6 +431,18 @@
   </si>
   <si>
     <t>THB</t>
+  </si>
+  <si>
+    <t>Main Account-ลูกค้านำจี้มาขายได้ราคาเกินคาด!</t>
+  </si>
+  <si>
+    <t>Main Account-ทองคุณแท้แค่ไหน</t>
+  </si>
+  <si>
+    <t>Main Account-ใครบอก ทองชุบ ไม่มีราคา</t>
+  </si>
+  <si>
+    <t>Main Account-ทองเก่า เศษทองอาจได้เงินหมื่น!</t>
   </si>
 </sst>
 </file>
@@ -792,61 +792,61 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="Q1" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>125</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -854,16 +854,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F2" s="2">
         <v>8493</v>
@@ -899,16 +899,16 @@
         <v>0</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -916,16 +916,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F3" s="2">
         <v>7875</v>
@@ -961,16 +961,16 @@
         <v>1</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -978,16 +978,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F4" s="2">
         <v>8634</v>
@@ -1023,16 +1023,16 @@
         <v>0</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1040,16 +1040,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F5" s="2">
         <v>8221</v>
@@ -1085,16 +1085,16 @@
         <v>0</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1102,16 +1102,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F6" s="2">
         <v>8129</v>
@@ -1147,16 +1147,16 @@
         <v>0</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1164,16 +1164,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>54</v>
-      </c>
       <c r="E7" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F7" s="2">
         <v>7529</v>
@@ -1209,16 +1209,16 @@
         <v>0</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1226,16 +1226,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>54</v>
-      </c>
       <c r="E8" s="2" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F8" s="2">
         <v>8269</v>
@@ -1271,16 +1271,16 @@
         <v>2</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1288,16 +1288,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>54</v>
-      </c>
       <c r="E9" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F9" s="2">
         <v>7954</v>
@@ -1333,16 +1333,16 @@
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1350,16 +1350,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>54</v>
-      </c>
       <c r="E10" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="F10" s="2">
         <v>7731</v>
@@ -1395,16 +1395,16 @@
         <v>1</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1412,16 +1412,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F11" s="2">
         <v>8350</v>
@@ -1457,16 +1457,16 @@
         <v>0</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1474,16 +1474,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F12" s="2">
         <v>8373</v>
@@ -1519,16 +1519,16 @@
         <v>1</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1536,16 +1536,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F13" s="2">
         <v>8340</v>
@@ -1581,16 +1581,16 @@
         <v>1</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1598,16 +1598,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F14" s="2">
         <v>8079</v>
@@ -1643,16 +1643,16 @@
         <v>1</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="15" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1660,16 +1660,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F15" s="2">
         <v>7857</v>
@@ -1705,16 +1705,16 @@
         <v>2</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="16" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1722,16 +1722,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F16" s="2">
         <v>7845</v>
@@ -1767,16 +1767,16 @@
         <v>0</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1784,16 +1784,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F17" s="2">
         <v>7951</v>
@@ -1829,16 +1829,16 @@
         <v>2</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="18" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1846,16 +1846,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F18" s="2">
         <v>8457</v>
@@ -1891,16 +1891,16 @@
         <v>2</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1908,16 +1908,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F19" s="2">
         <v>9008</v>
@@ -1953,16 +1953,16 @@
         <v>3</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="20" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1970,16 +1970,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F20" s="2">
         <v>8955</v>
@@ -2015,16 +2015,16 @@
         <v>0</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="21" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -2032,16 +2032,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F21" s="2">
         <v>13004</v>
@@ -2077,16 +2077,16 @@
         <v>1</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="22" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -2094,16 +2094,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F22" s="2">
         <v>11889</v>
@@ -2139,16 +2139,16 @@
         <v>5</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="T22" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="23" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -2156,16 +2156,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F23" s="2">
         <v>8926</v>
@@ -2201,16 +2201,16 @@
         <v>1</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="R23" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="T23" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="24" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -2218,16 +2218,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F24" s="2">
         <v>8926</v>
@@ -2263,16 +2263,16 @@
         <v>0</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="T24" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="25" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -2280,16 +2280,16 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F25" s="2">
         <v>8930</v>
@@ -2325,16 +2325,16 @@
         <v>1</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="T25" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="26" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -2342,16 +2342,16 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F26" s="2">
         <v>8645</v>
@@ -2387,16 +2387,16 @@
         <v>1</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="S26" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="T26" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="27" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -2404,16 +2404,16 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F27" s="2">
         <v>8628</v>
@@ -2449,16 +2449,16 @@
         <v>3</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="R27" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="S27" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="T27" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="28" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -2466,16 +2466,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F28" s="2">
         <v>8904</v>
@@ -2511,16 +2511,16 @@
         <v>0</v>
       </c>
       <c r="Q28" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="R28" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="S28" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="T28" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -2528,16 +2528,16 @@
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F29" s="2">
         <v>12580</v>
@@ -2573,16 +2573,16 @@
         <v>3</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="R29" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="S29" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="T29" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="30" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -2590,16 +2590,16 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F30" s="2">
         <v>22801</v>
@@ -2635,16 +2635,16 @@
         <v>6</v>
       </c>
       <c r="Q30" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="R30" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="S30" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="T30" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="31" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -2652,16 +2652,16 @@
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F31" s="2">
         <v>22007</v>
@@ -2697,16 +2697,16 @@
         <v>2</v>
       </c>
       <c r="Q31" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="R31" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="S31" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="T31" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="32" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -2714,16 +2714,16 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F32" s="2">
         <v>20662</v>
@@ -2759,16 +2759,16 @@
         <v>4</v>
       </c>
       <c r="Q32" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="R32" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="S32" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="T32" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="33" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -2776,16 +2776,16 @@
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F33" s="2">
         <v>28187</v>
@@ -2821,16 +2821,16 @@
         <v>4</v>
       </c>
       <c r="Q33" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="R33" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="S33" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="T33" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="34" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -2838,16 +2838,16 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F34" s="2">
         <v>30053</v>
@@ -2883,16 +2883,16 @@
         <v>6</v>
       </c>
       <c r="Q34" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="R34" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="S34" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="T34" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="35" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -2900,16 +2900,16 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F35" s="2">
         <v>28326</v>
@@ -2945,16 +2945,16 @@
         <v>6</v>
       </c>
       <c r="Q35" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="R35" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="S35" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="T35" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="36" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -2962,16 +2962,16 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F36" s="2">
         <v>30420</v>
@@ -3007,16 +3007,16 @@
         <v>2</v>
       </c>
       <c r="Q36" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="R36" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="S36" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="T36" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="37" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -3024,16 +3024,16 @@
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F37" s="2">
         <v>35185</v>
@@ -3069,16 +3069,16 @@
         <v>6</v>
       </c>
       <c r="Q37" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="R37" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="S37" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="T37" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="38" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -3086,16 +3086,16 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="F38" s="2">
         <v>34132</v>
@@ -3131,16 +3131,16 @@
         <v>9</v>
       </c>
       <c r="Q38" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="R38" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="S38" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="T38" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="39" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -3148,16 +3148,16 @@
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F39" s="2">
         <v>34725</v>
@@ -3193,16 +3193,16 @@
         <v>3</v>
       </c>
       <c r="Q39" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="R39" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="S39" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="T39" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="40" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -3210,16 +3210,16 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F40" s="2">
         <v>34472</v>
@@ -3255,33 +3255,33 @@
         <v>7</v>
       </c>
       <c r="Q40" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="R40" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="S40" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="T40" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="41" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>40</v>
+        <v>127</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F41" s="2">
         <v>70400</v>
@@ -3317,33 +3317,33 @@
         <v>10</v>
       </c>
       <c r="Q41" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="R41" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="S41" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="T41" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="42" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>41</v>
+        <v>128</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F42" s="2">
         <v>67252</v>
@@ -3379,33 +3379,33 @@
         <v>3</v>
       </c>
       <c r="Q42" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="R42" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="S42" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="T42" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="43" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>42</v>
+        <v>129</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="F43" s="2">
         <v>93649</v>
@@ -3441,33 +3441,33 @@
         <v>25</v>
       </c>
       <c r="Q43" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="R43" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="S43" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="T43" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="44" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>43</v>
+        <v>130</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="F44" s="2">
         <v>72458</v>
@@ -3503,33 +3503,33 @@
         <v>10</v>
       </c>
       <c r="Q44" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="R44" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="S44" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="T44" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="45" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="F45" s="2">
         <v>98501</v>
@@ -3565,33 +3565,33 @@
         <v>281</v>
       </c>
       <c r="Q45" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="R45" s="2" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="S45" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="T45" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="46" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="F46" s="2">
         <v>80075</v>
@@ -3627,16 +3627,16 @@
         <v>65</v>
       </c>
       <c r="Q46" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="R46" s="2" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="S46" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="T46" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>

--- a/data/July.xlsx
+++ b/data/July.xlsx
@@ -1,11 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{324BDE42-9EA2-4C46-A9C4-9A811CDAA27E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr filterPrivacy="true" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -15,31 +14,34 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>ผู้สร้าง</author>
+    <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="F1" authorId="0">
       <text>
         <r>
           <rPr>
+            <rFont val="Arial"/>
+            <color/>
             <sz val="12"/>
-            <rFont val="Arial"/>
           </rPr>
-          <t>This is a reach-based metric. Reach-based metrics are de-duplicated metrics so you might see different numbers based on the level at which you are viewing data.</t>
+          <t xml:space="preserve">This is a reach-based metric. Reach-based metrics are de-duplicated metrics so you might see different numbers based on the level at which you are viewing data.</t>
         </r>
         <r>
           <rPr>
+            <rFont val="Arial"/>
+            <color/>
             <sz val="12"/>
-            <rFont val="Arial"/>
           </rPr>
           <t xml:space="preserve">     </t>
         </r>
         <r>
           <rPr>
+            <rFont val="Arial"/>
+            <color/>
             <sz val="12"/>
-            <rFont val="Arial"/>
           </rPr>
           <t xml:space="preserve">     </t>
         </r>
@@ -50,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="133">
   <si>
     <t>Ad name</t>
   </si>
@@ -172,10 +174,25 @@
     <t>สาขาแยกคีรีชลบุรี-องค์พระที่่ทำเอง อายุกว่า 20 ปี</t>
   </si>
   <si>
+    <t>Main Account-ลูกค้านำจี้มาขายได้ราคาเกินคาด!</t>
+  </si>
+  <si>
+    <t>Main Account-ทองคุณแท้แค่ไหน</t>
+  </si>
+  <si>
+    <t>Main Account-ใครบอก ทองชุบ ไม่มีราคา</t>
+  </si>
+  <si>
+    <t>Main Account-ทองเก่า เศษทองอาจได้เงินหมื่น!</t>
+  </si>
+  <si>
     <t>KOLs-fern for Fun เฟิร์น ฟ ฟัน</t>
   </si>
   <si>
-    <t>KOLs-OLE' CH -ตามหาทองนพคุณ</t>
+    <t>KOLs-OLE CH -ตามหาทองนพคุณ</t>
+  </si>
+  <si>
+    <t>Total of 45 results</t>
   </si>
   <si>
     <t>Primary status</t>
@@ -238,139 +255,142 @@
     <t>Spend</t>
   </si>
   <si>
-    <t>122.59</t>
-  </si>
-  <si>
-    <t>121.92</t>
-  </si>
-  <si>
-    <t>127.55</t>
-  </si>
-  <si>
-    <t>124.10</t>
-  </si>
-  <si>
-    <t>122.57</t>
-  </si>
-  <si>
-    <t>115.98</t>
-  </si>
-  <si>
-    <t>126.72</t>
-  </si>
-  <si>
-    <t>125.81</t>
-  </si>
-  <si>
-    <t>121.35</t>
-  </si>
-  <si>
-    <t>126.05</t>
-  </si>
-  <si>
-    <t>124.45</t>
-  </si>
-  <si>
-    <t>126.90</t>
-  </si>
-  <si>
-    <t>122.92</t>
-  </si>
-  <si>
-    <t>122.73</t>
-  </si>
-  <si>
-    <t>122.84</t>
-  </si>
-  <si>
-    <t>118.35</t>
-  </si>
-  <si>
-    <t>134.06</t>
-  </si>
-  <si>
-    <t>134.71</t>
-  </si>
-  <si>
-    <t>128.41</t>
-  </si>
-  <si>
-    <t>111.46</t>
-  </si>
-  <si>
-    <t>120.63</t>
-  </si>
-  <si>
-    <t>129.22</t>
-  </si>
-  <si>
-    <t>131.81</t>
-  </si>
-  <si>
-    <t>130.84</t>
-  </si>
-  <si>
-    <t>126.03</t>
-  </si>
-  <si>
-    <t>125.38</t>
-  </si>
-  <si>
-    <t>128.81</t>
-  </si>
-  <si>
-    <t>116.92</t>
-  </si>
-  <si>
-    <t>613.63</t>
-  </si>
-  <si>
-    <t>571.74</t>
-  </si>
-  <si>
-    <t>556.69</t>
-  </si>
-  <si>
-    <t>580.33</t>
-  </si>
-  <si>
-    <t>624.84</t>
-  </si>
-  <si>
-    <t>611.12</t>
-  </si>
-  <si>
-    <t>616.99</t>
-  </si>
-  <si>
-    <t>631.68</t>
-  </si>
-  <si>
-    <t>616.19</t>
-  </si>
-  <si>
-    <t>626.33</t>
-  </si>
-  <si>
-    <t>591.66</t>
-  </si>
-  <si>
-    <t>1270.95</t>
-  </si>
-  <si>
-    <t>1269.70</t>
-  </si>
-  <si>
-    <t>1156.62</t>
-  </si>
-  <si>
-    <t>1343.47</t>
-  </si>
-  <si>
-    <t>1339.01</t>
-  </si>
-  <si>
-    <t>1363.87</t>
+    <t>295.82</t>
+  </si>
+  <si>
+    <t>294.32</t>
+  </si>
+  <si>
+    <t>301.12</t>
+  </si>
+  <si>
+    <t>297.31</t>
+  </si>
+  <si>
+    <t>292.98</t>
+  </si>
+  <si>
+    <t>295.37</t>
+  </si>
+  <si>
+    <t>301.80</t>
+  </si>
+  <si>
+    <t>295.93</t>
+  </si>
+  <si>
+    <t>296.88</t>
+  </si>
+  <si>
+    <t>300.54</t>
+  </si>
+  <si>
+    <t>299.48</t>
+  </si>
+  <si>
+    <t>296.82</t>
+  </si>
+  <si>
+    <t>297.05</t>
+  </si>
+  <si>
+    <t>292.24</t>
+  </si>
+  <si>
+    <t>295.27</t>
+  </si>
+  <si>
+    <t>285.14</t>
+  </si>
+  <si>
+    <t>308.88</t>
+  </si>
+  <si>
+    <t>311.27</t>
+  </si>
+  <si>
+    <t>303.03</t>
+  </si>
+  <si>
+    <t>267.88</t>
+  </si>
+  <si>
+    <t>276.46</t>
+  </si>
+  <si>
+    <t>300.44</t>
+  </si>
+  <si>
+    <t>301.70</t>
+  </si>
+  <si>
+    <t>306.47</t>
+  </si>
+  <si>
+    <t>296.45</t>
+  </si>
+  <si>
+    <t>295.89</t>
+  </si>
+  <si>
+    <t>291.64</t>
+  </si>
+  <si>
+    <t>270.29</t>
+  </si>
+  <si>
+    <t>858.76</t>
+  </si>
+  <si>
+    <t>811.88</t>
+  </si>
+  <si>
+    <t>797.40</t>
+  </si>
+  <si>
+    <t>821.24</t>
+  </si>
+  <si>
+    <t>865.14</t>
+  </si>
+  <si>
+    <t>856.53</t>
+  </si>
+  <si>
+    <t>863.20</t>
+  </si>
+  <si>
+    <t>873.23</t>
+  </si>
+  <si>
+    <t>854.55</t>
+  </si>
+  <si>
+    <t>878.29</t>
+  </si>
+  <si>
+    <t>842.99</t>
+  </si>
+  <si>
+    <t>1720.00</t>
+  </si>
+  <si>
+    <t>1709.29</t>
+  </si>
+  <si>
+    <t>1594.93</t>
+  </si>
+  <si>
+    <t>1780.47</t>
+  </si>
+  <si>
+    <t>1834.19</t>
+  </si>
+  <si>
+    <t>1828.99</t>
+  </si>
+  <si>
+    <t>28059.55</t>
   </si>
   <si>
     <t>Reach</t>
@@ -431,25 +451,13 @@
   </si>
   <si>
     <t>THB</t>
-  </si>
-  <si>
-    <t>Main Account-ลูกค้านำจี้มาขายได้ราคาเกินคาด!</t>
-  </si>
-  <si>
-    <t>Main Account-ทองคุณแท้แค่ไหน</t>
-  </si>
-  <si>
-    <t>Main Account-ใครบอก ทองชุบ ไม่มีราคา</t>
-  </si>
-  <si>
-    <t>Main Account-ทองเก่า เศษทองอาจได้เงินหมื่น!</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -457,19 +465,17 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
+      <b val="1"/>
       <sz val="12"/>
+      <color/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
+      <color/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="2">
@@ -507,140 +513,136 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
+      <alignment/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="44546A"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="ED7D31"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="FFC000"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4472C4"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="70AD47"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0563C1"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="954F72"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
+<theme xmlns="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+  <themeElements>
+    <clrScheme name="Office">
+      <dk1>
+        <sysClr val="windowText" lastClr="000000"/>
+      </dk1>
+      <lt1>
+        <sysClr val="window" lastClr="FFFFFF"/>
+      </lt1>
+      <dk2>
+        <srgbClr val="44546A"/>
+      </dk2>
+      <lt2>
+        <srgbClr val="E7E6E6"/>
+      </lt2>
+      <accent1>
+        <srgbClr val="5B9BD5"/>
+      </accent1>
+      <accent2>
+        <srgbClr val="ED7D31"/>
+      </accent2>
+      <accent3>
+        <srgbClr val="A5A5A5"/>
+      </accent3>
+      <accent4>
+        <srgbClr val="FFC000"/>
+      </accent4>
+      <accent5>
+        <srgbClr val="4472C4"/>
+      </accent5>
+      <accent6>
+        <srgbClr val="70AD47"/>
+      </accent6>
+      <hlink>
+        <srgbClr val="0563C1"/>
+      </hlink>
+      <folHlink>
+        <srgbClr val="954F72"/>
+      </folHlink>
+    </clrScheme>
+    <fontScheme name="Office">
+      <majorFont>
+        <latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <ea typeface=""/>
+        <cs typeface=""/>
+        <font script="Jpan" typeface="游ゴシック Light"/>
+        <font script="Hang" typeface="맑은 고딕"/>
+        <font script="Hans" typeface="等线 Light"/>
+        <font script="Hant" typeface="新細明體"/>
+        <font script="Arab" typeface="Times New Roman"/>
+        <font script="Hebr" typeface="Times New Roman"/>
+        <font script="Thai" typeface="Tahoma"/>
+        <font script="Ethi" typeface="Nyala"/>
+        <font script="Beng" typeface="Vrinda"/>
+        <font script="Gujr" typeface="Shruti"/>
+        <font script="Khmr" typeface="MoolBoran"/>
+        <font script="Knda" typeface="Tunga"/>
+        <font script="Guru" typeface="Raavi"/>
+        <font script="Cans" typeface="Euphemia"/>
+        <font script="Cher" typeface="Plantagenet Cherokee"/>
+        <font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <font script="Tibt" typeface="Microsoft Himalaya"/>
+        <font script="Thaa" typeface="MV Boli"/>
+        <font script="Deva" typeface="Mangal"/>
+        <font script="Telu" typeface="Gautami"/>
+        <font script="Taml" typeface="Latha"/>
+        <font script="Syrc" typeface="Estrangelo Edessa"/>
+        <font script="Orya" typeface="Kalinga"/>
+        <font script="Mlym" typeface="Kartika"/>
+        <font script="Laoo" typeface="DokChampa"/>
+        <font script="Sinh" typeface="Iskoola Pota"/>
+        <font script="Mong" typeface="Mongolian Baiti"/>
+        <font script="Viet" typeface="Times New Roman"/>
+        <font script="Uigh" typeface="Microsoft Uighur"/>
+        <font script="Geor" typeface="Sylfaen"/>
+      </majorFont>
+      <minorFont>
+        <latin typeface="Calibri" panose="020F0502020204030204"/>
+        <ea typeface=""/>
+        <cs typeface=""/>
+        <font script="Jpan" typeface="游ゴシック"/>
+        <font script="Hang" typeface="맑은 고딕"/>
+        <font script="Hans" typeface="等线"/>
+        <font script="Hant" typeface="新細明體"/>
+        <font script="Arab" typeface="Arial"/>
+        <font script="Hebr" typeface="Arial"/>
+        <font script="Thai" typeface="Tahoma"/>
+        <font script="Ethi" typeface="Nyala"/>
+        <font script="Beng" typeface="Vrinda"/>
+        <font script="Gujr" typeface="Shruti"/>
+        <font script="Khmr" typeface="DaunPenh"/>
+        <font script="Knda" typeface="Tunga"/>
+        <font script="Guru" typeface="Raavi"/>
+        <font script="Cans" typeface="Euphemia"/>
+        <font script="Cher" typeface="Plantagenet Cherokee"/>
+        <font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <font script="Tibt" typeface="Microsoft Himalaya"/>
+        <font script="Thaa" typeface="MV Boli"/>
+        <font script="Deva" typeface="Mangal"/>
+        <font script="Telu" typeface="Gautami"/>
+        <font script="Taml" typeface="Latha"/>
+        <font script="Syrc" typeface="Estrangelo Edessa"/>
+        <font script="Orya" typeface="Kalinga"/>
+        <font script="Mlym" typeface="Kartika"/>
+        <font script="Laoo" typeface="DokChampa"/>
+        <font script="Sinh" typeface="Iskoola Pota"/>
+        <font script="Mong" typeface="Mongolian Baiti"/>
+        <font script="Viet" typeface="Arial"/>
+        <font script="Uigh" typeface="Microsoft Uighur"/>
+        <font script="Geor" typeface="Sylfaen"/>
+      </minorFont>
+    </fontScheme>
+    <fmtScheme name="Office">
+      <fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -696,8 +698,8 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
+      </fillStyleLst>
+      <lnStyleLst>
         <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -719,8 +721,8 @@
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
+      </lnStyleLst>
+      <effectStyleLst>
         <a:effectStyle>
           <a:effectLst/>
         </a:effectStyle>
@@ -736,8 +738,8 @@
             </a:outerShdw>
           </a:effectLst>
         </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
+      </effectStyleLst>
+      <bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -774,114 +776,114 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
+      </bgFillStyleLst>
+    </fmtScheme>
+  </themeElements>
+  <objectDefaults/>
+  <extraClrSchemeLst/>
+</theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T46"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F2" s="2">
-        <v>8493</v>
+        <v>19238</v>
       </c>
       <c r="G2" s="2">
-        <v>10165</v>
+        <v>23646</v>
       </c>
       <c r="H2" s="2">
-        <v>10005</v>
+        <v>23300</v>
       </c>
       <c r="I2" s="2">
-        <v>1852</v>
+        <v>4102</v>
       </c>
       <c r="J2" s="2">
-        <v>333</v>
+        <v>737</v>
       </c>
       <c r="K2" s="2">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="L2" s="2">
         <v>0</v>
@@ -890,60 +892,60 @@
         <v>0</v>
       </c>
       <c r="N2" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O2" s="2">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="P2" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F3" s="2">
-        <v>7875</v>
+        <v>17189</v>
       </c>
       <c r="G3" s="2">
-        <v>9472</v>
+        <v>22387</v>
       </c>
       <c r="H3" s="2">
-        <v>9330</v>
+        <v>22064</v>
       </c>
       <c r="I3" s="2">
-        <v>1321</v>
+        <v>3019</v>
       </c>
       <c r="J3" s="2">
-        <v>310</v>
+        <v>701</v>
       </c>
       <c r="K3" s="2">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="L3" s="2">
         <v>0</v>
@@ -955,57 +957,57 @@
         <v>0</v>
       </c>
       <c r="O3" s="2">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="P3" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F4" s="2">
-        <v>8634</v>
+        <v>17716</v>
       </c>
       <c r="G4" s="2">
-        <v>9954</v>
+        <v>23069</v>
       </c>
       <c r="H4" s="2">
-        <v>9782</v>
+        <v>22682</v>
       </c>
       <c r="I4" s="2">
-        <v>1544</v>
+        <v>3471</v>
       </c>
       <c r="J4" s="2">
-        <v>242</v>
+        <v>551</v>
       </c>
       <c r="K4" s="2">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="L4" s="2">
         <v>0</v>
@@ -1014,60 +1016,60 @@
         <v>0</v>
       </c>
       <c r="N4" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" s="2">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="P4" s="2">
         <v>0</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F5" s="2">
-        <v>8221</v>
+        <v>17730</v>
       </c>
       <c r="G5" s="2">
-        <v>9523</v>
+        <v>22430</v>
       </c>
       <c r="H5" s="2">
-        <v>9391</v>
+        <v>22120</v>
       </c>
       <c r="I5" s="2">
-        <v>5351</v>
+        <v>11726</v>
       </c>
       <c r="J5" s="2">
-        <v>1361</v>
+        <v>2956</v>
       </c>
       <c r="K5" s="2">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="L5" s="2">
         <v>1</v>
@@ -1076,60 +1078,60 @@
         <v>0</v>
       </c>
       <c r="N5" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O5" s="2">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="P5" s="2">
         <v>0</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F6" s="2">
-        <v>8129</v>
+        <v>17371</v>
       </c>
       <c r="G6" s="2">
-        <v>9721</v>
+        <v>22517</v>
       </c>
       <c r="H6" s="2">
-        <v>9592</v>
+        <v>22185</v>
       </c>
       <c r="I6" s="2">
-        <v>1495</v>
+        <v>3445</v>
       </c>
       <c r="J6" s="2">
-        <v>313</v>
+        <v>749</v>
       </c>
       <c r="K6" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L6" s="2">
         <v>0</v>
@@ -1141,57 +1143,57 @@
         <v>0</v>
       </c>
       <c r="O6" s="2">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="P6" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F7" s="2">
-        <v>7529</v>
+        <v>18091</v>
       </c>
       <c r="G7" s="2">
-        <v>9261</v>
+        <v>22991</v>
       </c>
       <c r="H7" s="2">
-        <v>9078</v>
+        <v>22563</v>
       </c>
       <c r="I7" s="2">
-        <v>938</v>
+        <v>2169</v>
       </c>
       <c r="J7" s="2">
-        <v>176</v>
+        <v>390</v>
       </c>
       <c r="K7" s="2">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="L7" s="2">
         <v>0</v>
@@ -1200,60 +1202,60 @@
         <v>0</v>
       </c>
       <c r="N7" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7" s="2">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="P7" s="2">
         <v>0</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F8" s="2">
-        <v>8269</v>
+        <v>17905</v>
       </c>
       <c r="G8" s="2">
-        <v>9773</v>
+        <v>22863</v>
       </c>
       <c r="H8" s="2">
-        <v>9582</v>
+        <v>22457</v>
       </c>
       <c r="I8" s="2">
-        <v>928</v>
+        <v>2260</v>
       </c>
       <c r="J8" s="2">
-        <v>156</v>
+        <v>379</v>
       </c>
       <c r="K8" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="L8" s="2">
         <v>0</v>
@@ -1265,57 +1267,57 @@
         <v>0</v>
       </c>
       <c r="O8" s="2">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="P8" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F9" s="2">
-        <v>7954</v>
+        <v>16997</v>
       </c>
       <c r="G9" s="2">
-        <v>9399</v>
+        <v>21828</v>
       </c>
       <c r="H9" s="2">
-        <v>9230</v>
+        <v>21451</v>
       </c>
       <c r="I9" s="2">
-        <v>1150</v>
+        <v>2731</v>
       </c>
       <c r="J9" s="2">
-        <v>178</v>
+        <v>455</v>
       </c>
       <c r="K9" s="2">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="L9" s="2">
         <v>0</v>
@@ -1324,122 +1326,122 @@
         <v>0</v>
       </c>
       <c r="N9" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O9" s="2">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="P9" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F10" s="2">
-        <v>7731</v>
+        <v>17781</v>
       </c>
       <c r="G10" s="2">
-        <v>9448</v>
+        <v>22617</v>
       </c>
       <c r="H10" s="2">
-        <v>9264</v>
+        <v>22192</v>
       </c>
       <c r="I10" s="2">
-        <v>781</v>
+        <v>1814</v>
       </c>
       <c r="J10" s="2">
-        <v>167</v>
+        <v>350</v>
       </c>
       <c r="K10" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L10" s="2">
         <v>0</v>
       </c>
       <c r="M10" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" s="2">
         <v>0</v>
       </c>
       <c r="O10" s="2">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="P10" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F11" s="2">
-        <v>8350</v>
+        <v>17874</v>
       </c>
       <c r="G11" s="2">
-        <v>9608</v>
+        <v>22648</v>
       </c>
       <c r="H11" s="2">
-        <v>9457</v>
+        <v>22301</v>
       </c>
       <c r="I11" s="2">
-        <v>812</v>
+        <v>1934</v>
       </c>
       <c r="J11" s="2">
-        <v>194</v>
+        <v>440</v>
       </c>
       <c r="K11" s="2">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="L11" s="2">
         <v>0</v>
@@ -1448,60 +1450,60 @@
         <v>0</v>
       </c>
       <c r="N11" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O11" s="2">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="P11" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F12" s="2">
-        <v>8373</v>
+        <v>17912</v>
       </c>
       <c r="G12" s="2">
-        <v>9699</v>
+        <v>22747</v>
       </c>
       <c r="H12" s="2">
-        <v>9531</v>
+        <v>22404</v>
       </c>
       <c r="I12" s="2">
-        <v>1256</v>
+        <v>2868</v>
       </c>
       <c r="J12" s="2">
-        <v>251</v>
+        <v>568</v>
       </c>
       <c r="K12" s="2">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="L12" s="2">
         <v>0</v>
@@ -1513,57 +1515,57 @@
         <v>1</v>
       </c>
       <c r="O12" s="2">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="P12" s="2">
         <v>1</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F13" s="2">
-        <v>8340</v>
+        <v>17425</v>
       </c>
       <c r="G13" s="2">
-        <v>9837</v>
+        <v>22439</v>
       </c>
       <c r="H13" s="2">
-        <v>9694</v>
+        <v>22129</v>
       </c>
       <c r="I13" s="2">
-        <v>1009</v>
+        <v>2242</v>
       </c>
       <c r="J13" s="2">
-        <v>227</v>
+        <v>497</v>
       </c>
       <c r="K13" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="L13" s="2">
         <v>0</v>
@@ -1572,60 +1574,60 @@
         <v>0</v>
       </c>
       <c r="N13" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" s="2">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="P13" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F14" s="2">
-        <v>8079</v>
+        <v>17252</v>
       </c>
       <c r="G14" s="2">
-        <v>9698</v>
+        <v>22875</v>
       </c>
       <c r="H14" s="2">
-        <v>9584</v>
+        <v>22575</v>
       </c>
       <c r="I14" s="2">
-        <v>2713</v>
+        <v>6014</v>
       </c>
       <c r="J14" s="2">
-        <v>1162</v>
+        <v>2473</v>
       </c>
       <c r="K14" s="2">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="L14" s="2">
         <v>0</v>
@@ -1634,60 +1636,60 @@
         <v>1</v>
       </c>
       <c r="N14" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O14" s="2">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="P14" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F15" s="2">
-        <v>7857</v>
+        <v>16504</v>
       </c>
       <c r="G15" s="2">
-        <v>9308</v>
+        <v>21700</v>
       </c>
       <c r="H15" s="2">
-        <v>9161</v>
+        <v>21362</v>
       </c>
       <c r="I15" s="2">
-        <v>1822</v>
+        <v>4037</v>
       </c>
       <c r="J15" s="2">
-        <v>337</v>
+        <v>722</v>
       </c>
       <c r="K15" s="2">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="L15" s="2">
         <v>0</v>
@@ -1696,184 +1698,184 @@
         <v>0</v>
       </c>
       <c r="N15" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" s="2">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="P15" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F16" s="2">
+        <v>16383</v>
+      </c>
+      <c r="G16" s="2">
+        <v>21825</v>
+      </c>
+      <c r="H16" s="2">
+        <v>21449</v>
+      </c>
+      <c r="I16" s="2">
+        <v>3799</v>
+      </c>
+      <c r="J16" s="2">
+        <v>888</v>
+      </c>
+      <c r="K16" s="2">
+        <v>19</v>
+      </c>
+      <c r="L16" s="2">
+        <v>0</v>
+      </c>
+      <c r="M16" s="2">
+        <v>1</v>
+      </c>
+      <c r="N16" s="2">
+        <v>2</v>
+      </c>
+      <c r="O16" s="2">
         <v>43</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F16" s="2">
-        <v>7845</v>
-      </c>
-      <c r="G16" s="2">
-        <v>9215</v>
-      </c>
-      <c r="H16" s="2">
-        <v>9080</v>
-      </c>
-      <c r="I16" s="2">
-        <v>1696</v>
-      </c>
-      <c r="J16" s="2">
-        <v>382</v>
-      </c>
-      <c r="K16" s="2">
-        <v>5</v>
-      </c>
-      <c r="L16" s="2">
-        <v>0</v>
-      </c>
-      <c r="M16" s="2">
-        <v>0</v>
-      </c>
-      <c r="N16" s="2">
-        <v>1</v>
-      </c>
-      <c r="O16" s="2">
-        <v>19</v>
-      </c>
       <c r="P16" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="F17" s="2">
-        <v>7951</v>
+        <v>16723</v>
       </c>
       <c r="G17" s="2">
-        <v>9423</v>
+        <v>22109</v>
       </c>
       <c r="H17" s="2">
-        <v>9269</v>
+        <v>21759</v>
       </c>
       <c r="I17" s="2">
-        <v>1080</v>
+        <v>2566</v>
       </c>
       <c r="J17" s="2">
-        <v>217</v>
+        <v>538</v>
       </c>
       <c r="K17" s="2">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="L17" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="2">
         <v>0</v>
       </c>
       <c r="N17" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O17" s="2">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="P17" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F18" s="2">
-        <v>8457</v>
+        <v>18732</v>
       </c>
       <c r="G18" s="2">
-        <v>10126</v>
+        <v>23240</v>
       </c>
       <c r="H18" s="2">
-        <v>9917</v>
+        <v>22832</v>
       </c>
       <c r="I18" s="2">
-        <v>3781</v>
+        <v>8113</v>
       </c>
       <c r="J18" s="2">
-        <v>826</v>
+        <v>1671</v>
       </c>
       <c r="K18" s="2">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="L18" s="2">
         <v>1</v>
@@ -1885,57 +1887,57 @@
         <v>2</v>
       </c>
       <c r="O18" s="2">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="P18" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F19" s="2">
-        <v>9008</v>
+        <v>19443</v>
       </c>
       <c r="G19" s="2">
-        <v>10516</v>
+        <v>24057</v>
       </c>
       <c r="H19" s="2">
-        <v>10345</v>
+        <v>23691</v>
       </c>
       <c r="I19" s="2">
-        <v>2127</v>
+        <v>4750</v>
       </c>
       <c r="J19" s="2">
-        <v>376</v>
+        <v>792</v>
       </c>
       <c r="K19" s="2">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="L19" s="2">
         <v>0</v>
@@ -1947,57 +1949,57 @@
         <v>0</v>
       </c>
       <c r="O19" s="2">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="P19" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="20">
       <c r="A20" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="F20" s="2">
-        <v>8955</v>
+        <v>19010</v>
       </c>
       <c r="G20" s="2">
-        <v>10289</v>
+        <v>23675</v>
       </c>
       <c r="H20" s="2">
-        <v>10101</v>
+        <v>23295</v>
       </c>
       <c r="I20" s="2">
-        <v>1185</v>
+        <v>2830</v>
       </c>
       <c r="J20" s="2">
-        <v>193</v>
+        <v>433</v>
       </c>
       <c r="K20" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L20" s="2">
         <v>0</v>
@@ -2009,57 +2011,57 @@
         <v>0</v>
       </c>
       <c r="O20" s="2">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="P20" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="21">
       <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F21" s="2">
-        <v>13004</v>
+        <v>32278</v>
       </c>
       <c r="G21" s="2">
-        <v>15788</v>
+        <v>40871</v>
       </c>
       <c r="H21" s="2">
-        <v>15279</v>
+        <v>39578</v>
       </c>
       <c r="I21" s="2">
-        <v>4404</v>
+        <v>10671</v>
       </c>
       <c r="J21" s="2">
-        <v>788</v>
+        <v>1881</v>
       </c>
       <c r="K21" s="2">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="L21" s="2">
         <v>0</v>
@@ -2068,60 +2070,60 @@
         <v>1</v>
       </c>
       <c r="N21" s="2">
+        <v>10</v>
+      </c>
+      <c r="O21" s="2">
+        <v>54</v>
+      </c>
+      <c r="P21" s="2">
         <v>4</v>
       </c>
-      <c r="O21" s="2">
-        <v>29</v>
-      </c>
-      <c r="P21" s="2">
-        <v>1</v>
-      </c>
       <c r="Q21" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="22">
       <c r="A22" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F22" s="2">
-        <v>11889</v>
+        <v>26056</v>
       </c>
       <c r="G22" s="2">
-        <v>14151</v>
+        <v>33015</v>
       </c>
       <c r="H22" s="2">
-        <v>13820</v>
+        <v>32071</v>
       </c>
       <c r="I22" s="2">
-        <v>2016</v>
+        <v>4651</v>
       </c>
       <c r="J22" s="2">
-        <v>359</v>
+        <v>852</v>
       </c>
       <c r="K22" s="2">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="L22" s="2">
         <v>0</v>
@@ -2130,60 +2132,60 @@
         <v>1</v>
       </c>
       <c r="N22" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O22" s="2">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="P22" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="T22" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="23">
       <c r="A23" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F23" s="2">
-        <v>8926</v>
+        <v>18800</v>
       </c>
       <c r="G23" s="2">
-        <v>10254</v>
+        <v>23260</v>
       </c>
       <c r="H23" s="2">
-        <v>10131</v>
+        <v>22974</v>
       </c>
       <c r="I23" s="2">
-        <v>1499</v>
+        <v>3379</v>
       </c>
       <c r="J23" s="2">
-        <v>391</v>
+        <v>899</v>
       </c>
       <c r="K23" s="2">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="L23" s="2">
         <v>0</v>
@@ -2195,57 +2197,57 @@
         <v>1</v>
       </c>
       <c r="O23" s="2">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="P23" s="2">
         <v>1</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="R23" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="T23" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="24">
       <c r="A24" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F24" s="2">
-        <v>8926</v>
+        <v>18433</v>
       </c>
       <c r="G24" s="2">
-        <v>10274</v>
+        <v>23108</v>
       </c>
       <c r="H24" s="2">
-        <v>10097</v>
+        <v>22674</v>
       </c>
       <c r="I24" s="2">
-        <v>927</v>
+        <v>2007</v>
       </c>
       <c r="J24" s="2">
-        <v>167</v>
+        <v>352</v>
       </c>
       <c r="K24" s="2">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="L24" s="2">
         <v>0</v>
@@ -2257,119 +2259,119 @@
         <v>0</v>
       </c>
       <c r="O24" s="2">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="P24" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="T24" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="25">
       <c r="A25" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F25" s="2">
-        <v>8930</v>
+        <v>18450</v>
       </c>
       <c r="G25" s="2">
-        <v>10326</v>
+        <v>23512</v>
       </c>
       <c r="H25" s="2">
-        <v>10194</v>
+        <v>23227</v>
       </c>
       <c r="I25" s="2">
-        <v>1186</v>
+        <v>2555</v>
       </c>
       <c r="J25" s="2">
-        <v>202</v>
+        <v>458</v>
       </c>
       <c r="K25" s="2">
+        <v>12</v>
+      </c>
+      <c r="L25" s="2">
+        <v>0</v>
+      </c>
+      <c r="M25" s="2">
+        <v>0</v>
+      </c>
+      <c r="N25" s="2">
+        <v>0</v>
+      </c>
+      <c r="O25" s="2">
+        <v>28</v>
+      </c>
+      <c r="P25" s="2">
         <v>3</v>
       </c>
-      <c r="L25" s="2">
-        <v>0</v>
-      </c>
-      <c r="M25" s="2">
-        <v>0</v>
-      </c>
-      <c r="N25" s="2">
-        <v>0</v>
-      </c>
-      <c r="O25" s="2">
-        <v>18</v>
-      </c>
-      <c r="P25" s="2">
-        <v>1</v>
-      </c>
       <c r="Q25" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="T25" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="26">
       <c r="A26" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F26" s="2">
-        <v>8645</v>
+        <v>19033</v>
       </c>
       <c r="G26" s="2">
-        <v>10233</v>
+        <v>23384</v>
       </c>
       <c r="H26" s="2">
-        <v>10100</v>
+        <v>23035</v>
       </c>
       <c r="I26" s="2">
-        <v>2100</v>
+        <v>4613</v>
       </c>
       <c r="J26" s="2">
-        <v>217</v>
+        <v>519</v>
       </c>
       <c r="K26" s="2">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="L26" s="2">
         <v>0</v>
@@ -2378,60 +2380,60 @@
         <v>0</v>
       </c>
       <c r="N26" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O26" s="2">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="P26" s="2">
         <v>1</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="S26" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="T26" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="27">
       <c r="A27" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F27" s="2">
-        <v>8628</v>
+        <v>18392</v>
       </c>
       <c r="G27" s="2">
-        <v>9815</v>
+        <v>22583</v>
       </c>
       <c r="H27" s="2">
-        <v>9656</v>
+        <v>22195</v>
       </c>
       <c r="I27" s="2">
-        <v>1109</v>
+        <v>2419</v>
       </c>
       <c r="J27" s="2">
-        <v>216</v>
+        <v>493</v>
       </c>
       <c r="K27" s="2">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="L27" s="2">
         <v>0</v>
@@ -2440,122 +2442,122 @@
         <v>0</v>
       </c>
       <c r="N27" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O27" s="2">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="P27" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="R27" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="S27" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="T27" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="28">
       <c r="A28" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="F28" s="2">
-        <v>8904</v>
+        <v>18727</v>
       </c>
       <c r="G28" s="2">
-        <v>10273</v>
+        <v>22770</v>
       </c>
       <c r="H28" s="2">
-        <v>10155</v>
+        <v>22480</v>
       </c>
       <c r="I28" s="2">
-        <v>2248</v>
+        <v>4825</v>
       </c>
       <c r="J28" s="2">
-        <v>437</v>
+        <v>982</v>
       </c>
       <c r="K28" s="2">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="L28" s="2">
         <v>0</v>
       </c>
       <c r="M28" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N28" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O28" s="2">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="P28" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q28" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="R28" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="S28" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="T28" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="29">
       <c r="A29" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="F29" s="2">
-        <v>12580</v>
+        <v>27997</v>
       </c>
       <c r="G29" s="2">
-        <v>15325</v>
+        <v>35656</v>
       </c>
       <c r="H29" s="2">
-        <v>15005</v>
+        <v>34729</v>
       </c>
       <c r="I29" s="2">
-        <v>2300</v>
+        <v>5083</v>
       </c>
       <c r="J29" s="2">
-        <v>322</v>
+        <v>734</v>
       </c>
       <c r="K29" s="2">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="L29" s="2">
         <v>0</v>
@@ -2564,60 +2566,60 @@
         <v>0</v>
       </c>
       <c r="N29" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O29" s="2">
-        <v>32</v>
+        <v>76</v>
       </c>
       <c r="P29" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="R29" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="S29" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="T29" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="30">
       <c r="A30" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F30" s="2">
-        <v>22801</v>
+        <v>27602</v>
       </c>
       <c r="G30" s="2">
-        <v>40615</v>
+        <v>54389</v>
       </c>
       <c r="H30" s="2">
-        <v>39980</v>
+        <v>53500</v>
       </c>
       <c r="I30" s="2">
-        <v>11341</v>
+        <v>14973</v>
       </c>
       <c r="J30" s="2">
-        <v>2718</v>
+        <v>3581</v>
       </c>
       <c r="K30" s="2">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="L30" s="2">
         <v>3</v>
@@ -2626,60 +2628,60 @@
         <v>2</v>
       </c>
       <c r="N30" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="O30" s="2">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="P30" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Q30" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="R30" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="S30" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="T30" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="31">
       <c r="A31" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F31" s="2">
-        <v>22007</v>
+        <v>26528</v>
       </c>
       <c r="G31" s="2">
-        <v>37741</v>
+        <v>51373</v>
       </c>
       <c r="H31" s="2">
-        <v>37081</v>
+        <v>50472</v>
       </c>
       <c r="I31" s="2">
-        <v>6917</v>
+        <v>9673</v>
       </c>
       <c r="J31" s="2">
-        <v>1394</v>
+        <v>1950</v>
       </c>
       <c r="K31" s="2">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L31" s="2">
         <v>0</v>
@@ -2688,122 +2690,122 @@
         <v>0</v>
       </c>
       <c r="N31" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O31" s="2">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="P31" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q31" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="R31" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="S31" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="T31" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="32" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="32">
       <c r="A32" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F32" s="2">
-        <v>20662</v>
+        <v>25301</v>
       </c>
       <c r="G32" s="2">
-        <v>35153</v>
+        <v>48200</v>
       </c>
       <c r="H32" s="2">
-        <v>34540</v>
+        <v>47346</v>
       </c>
       <c r="I32" s="2">
-        <v>4599</v>
+        <v>6432</v>
       </c>
       <c r="J32" s="2">
-        <v>991</v>
+        <v>1393</v>
       </c>
       <c r="K32" s="2">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="L32" s="2">
         <v>0</v>
       </c>
       <c r="M32" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N32" s="2">
+        <v>8</v>
+      </c>
+      <c r="O32" s="2">
+        <v>96</v>
+      </c>
+      <c r="P32" s="2">
         <v>6</v>
       </c>
-      <c r="O32" s="2">
-        <v>67</v>
-      </c>
-      <c r="P32" s="2">
-        <v>4</v>
-      </c>
       <c r="Q32" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="R32" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="S32" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="T32" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="33" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="33">
       <c r="A33" s="2" t="s">
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F33" s="2">
-        <v>28187</v>
+        <v>34164</v>
       </c>
       <c r="G33" s="2">
-        <v>45346</v>
+        <v>61522</v>
       </c>
       <c r="H33" s="2">
-        <v>44583</v>
+        <v>60423</v>
       </c>
       <c r="I33" s="2">
-        <v>4583</v>
+        <v>6299</v>
       </c>
       <c r="J33" s="2">
-        <v>900</v>
+        <v>1261</v>
       </c>
       <c r="K33" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L33" s="2">
         <v>0</v>
@@ -2815,57 +2817,57 @@
         <v>2</v>
       </c>
       <c r="O33" s="2">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="P33" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q33" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="R33" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="S33" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="T33" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="34" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="34">
       <c r="A34" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="F34" s="2">
-        <v>30053</v>
+        <v>35884</v>
       </c>
       <c r="G34" s="2">
-        <v>49281</v>
+        <v>65687</v>
       </c>
       <c r="H34" s="2">
-        <v>48351</v>
+        <v>64372</v>
       </c>
       <c r="I34" s="2">
-        <v>3049</v>
+        <v>4111</v>
       </c>
       <c r="J34" s="2">
-        <v>796</v>
+        <v>1096</v>
       </c>
       <c r="K34" s="2">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="L34" s="2">
         <v>0</v>
@@ -2874,60 +2876,60 @@
         <v>0</v>
       </c>
       <c r="N34" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O34" s="2">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="P34" s="2">
         <v>6</v>
       </c>
       <c r="Q34" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="R34" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="S34" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="T34" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="35" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="35">
       <c r="A35" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F35" s="2">
-        <v>28326</v>
+        <v>34569</v>
       </c>
       <c r="G35" s="2">
-        <v>46764</v>
+        <v>63057</v>
       </c>
       <c r="H35" s="2">
-        <v>45962</v>
+        <v>61976</v>
       </c>
       <c r="I35" s="2">
-        <v>3600</v>
+        <v>4935</v>
       </c>
       <c r="J35" s="2">
-        <v>795</v>
+        <v>1100</v>
       </c>
       <c r="K35" s="2">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="L35" s="2">
         <v>0</v>
@@ -2936,60 +2938,60 @@
         <v>0</v>
       </c>
       <c r="N35" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O35" s="2">
-        <v>92</v>
+        <v>120</v>
       </c>
       <c r="P35" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q35" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="R35" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="S35" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="T35" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="36" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="36">
       <c r="A36" s="2" t="s">
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="F36" s="2">
-        <v>30420</v>
+        <v>36356</v>
       </c>
       <c r="G36" s="2">
-        <v>49217</v>
+        <v>66014</v>
       </c>
       <c r="H36" s="2">
-        <v>48441</v>
+        <v>64927</v>
       </c>
       <c r="I36" s="2">
-        <v>3110</v>
+        <v>4200</v>
       </c>
       <c r="J36" s="2">
-        <v>747</v>
+        <v>1042</v>
       </c>
       <c r="K36" s="2">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="L36" s="2">
         <v>0</v>
@@ -2998,60 +3000,60 @@
         <v>0</v>
       </c>
       <c r="N36" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O36" s="2">
-        <v>87</v>
+        <v>119</v>
       </c>
       <c r="P36" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q36" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="R36" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="S36" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="T36" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="37" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="37">
       <c r="A37" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F37" s="2">
-        <v>35185</v>
+        <v>42175</v>
       </c>
       <c r="G37" s="2">
-        <v>50625</v>
+        <v>67381</v>
       </c>
       <c r="H37" s="2">
-        <v>49866</v>
+        <v>66368</v>
       </c>
       <c r="I37" s="2">
-        <v>14270</v>
+        <v>18860</v>
       </c>
       <c r="J37" s="2">
-        <v>1667</v>
+        <v>2242</v>
       </c>
       <c r="K37" s="2">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="L37" s="2">
         <v>0</v>
@@ -3060,60 +3062,60 @@
         <v>0</v>
       </c>
       <c r="N37" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O37" s="2">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="P37" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q37" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="R37" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="S37" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="T37" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="38" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="38">
       <c r="A38" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="F38" s="2">
-        <v>34132</v>
+        <v>41146</v>
       </c>
       <c r="G38" s="2">
-        <v>49544</v>
+        <v>66149</v>
       </c>
       <c r="H38" s="2">
-        <v>48806</v>
+        <v>65079</v>
       </c>
       <c r="I38" s="2">
-        <v>17162</v>
+        <v>22439</v>
       </c>
       <c r="J38" s="2">
-        <v>3226</v>
+        <v>4222</v>
       </c>
       <c r="K38" s="2">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="L38" s="2">
         <v>1</v>
@@ -3122,184 +3124,184 @@
         <v>0</v>
       </c>
       <c r="N38" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O38" s="2">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="P38" s="2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Q38" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="R38" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="S38" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="T38" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="39" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="39">
       <c r="A39" s="2" t="s">
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="F39" s="2">
-        <v>34725</v>
+        <v>41848</v>
       </c>
       <c r="G39" s="2">
-        <v>50692</v>
+        <v>68489</v>
       </c>
       <c r="H39" s="2">
-        <v>49929</v>
+        <v>67476</v>
       </c>
       <c r="I39" s="2">
-        <v>9998</v>
+        <v>13418</v>
       </c>
       <c r="J39" s="2">
-        <v>1131</v>
+        <v>1491</v>
       </c>
       <c r="K39" s="2">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="L39" s="2">
         <v>0</v>
       </c>
       <c r="M39" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N39" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O39" s="2">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="P39" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q39" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="R39" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="S39" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="T39" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="40" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="40">
       <c r="A40" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E40" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F40" s="2">
+        <v>41733</v>
+      </c>
+      <c r="G40" s="2">
+        <v>65366</v>
+      </c>
+      <c r="H40" s="2">
+        <v>64147</v>
+      </c>
+      <c r="I40" s="2">
+        <v>19677</v>
+      </c>
+      <c r="J40" s="2">
+        <v>3425</v>
+      </c>
+      <c r="K40" s="2">
+        <v>69</v>
+      </c>
+      <c r="L40" s="2">
+        <v>0</v>
+      </c>
+      <c r="M40" s="2">
+        <v>0</v>
+      </c>
+      <c r="N40" s="2">
+        <v>7</v>
+      </c>
+      <c r="O40" s="2">
         <v>100</v>
       </c>
-      <c r="F40" s="2">
-        <v>34472</v>
-      </c>
-      <c r="G40" s="2">
-        <v>47815</v>
-      </c>
-      <c r="H40" s="2">
-        <v>46927</v>
-      </c>
-      <c r="I40" s="2">
-        <v>14366</v>
-      </c>
-      <c r="J40" s="2">
-        <v>2582</v>
-      </c>
-      <c r="K40" s="2">
-        <v>53</v>
-      </c>
-      <c r="L40" s="2">
-        <v>0</v>
-      </c>
-      <c r="M40" s="2">
-        <v>0</v>
-      </c>
-      <c r="N40" s="2">
-        <v>6</v>
-      </c>
-      <c r="O40" s="2">
-        <v>68</v>
-      </c>
       <c r="P40" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q40" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="R40" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="S40" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="T40" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="41" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="41">
       <c r="A41" s="2" t="s">
-        <v>127</v>
+        <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="F41" s="2">
-        <v>70400</v>
+        <v>83009</v>
       </c>
       <c r="G41" s="2">
-        <v>105792</v>
+        <v>138717</v>
       </c>
       <c r="H41" s="2">
-        <v>103997</v>
+        <v>136300</v>
       </c>
       <c r="I41" s="2">
-        <v>21037</v>
+        <v>28437</v>
       </c>
       <c r="J41" s="2">
-        <v>1917</v>
+        <v>2498</v>
       </c>
       <c r="K41" s="2">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="L41" s="2">
         <v>0</v>
@@ -3311,181 +3313,181 @@
         <v>7</v>
       </c>
       <c r="O41" s="2">
-        <v>161</v>
+        <v>207</v>
       </c>
       <c r="P41" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q41" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="R41" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="S41" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="T41" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="42" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="42">
       <c r="A42" s="2" t="s">
-        <v>128</v>
+        <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F42" s="2">
+        <v>77782</v>
+      </c>
+      <c r="G42" s="2">
+        <v>137972</v>
+      </c>
+      <c r="H42" s="2">
+        <v>135295</v>
+      </c>
+      <c r="I42" s="2">
+        <v>8876</v>
+      </c>
+      <c r="J42" s="2">
+        <v>1512</v>
+      </c>
+      <c r="K42" s="2">
+        <v>47</v>
+      </c>
+      <c r="L42" s="2">
+        <v>0</v>
+      </c>
+      <c r="M42" s="2">
+        <v>1</v>
+      </c>
+      <c r="N42" s="2">
+        <v>4</v>
+      </c>
+      <c r="O42" s="2">
+        <v>217</v>
+      </c>
+      <c r="P42" s="2">
+        <v>5</v>
+      </c>
+      <c r="Q42" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="R42" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="S42" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="T42" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F43" s="2">
+        <v>109743</v>
+      </c>
+      <c r="G43" s="2">
+        <v>164023</v>
+      </c>
+      <c r="H43" s="2">
+        <v>160593</v>
+      </c>
+      <c r="I43" s="2">
+        <v>29062</v>
+      </c>
+      <c r="J43" s="2">
+        <v>7193</v>
+      </c>
+      <c r="K43" s="2">
+        <v>392</v>
+      </c>
+      <c r="L43" s="2">
+        <v>0</v>
+      </c>
+      <c r="M43" s="2">
+        <v>2</v>
+      </c>
+      <c r="N43" s="2">
+        <v>23</v>
+      </c>
+      <c r="O43" s="2">
+        <v>355</v>
+      </c>
+      <c r="P43" s="2">
+        <v>30</v>
+      </c>
+      <c r="Q43" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="R43" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="S43" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="T43" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C42" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="F42" s="2">
-        <v>67252</v>
-      </c>
-      <c r="G42" s="2">
-        <v>105983</v>
-      </c>
-      <c r="H42" s="2">
-        <v>104005</v>
-      </c>
-      <c r="I42" s="2">
-        <v>6719</v>
-      </c>
-      <c r="J42" s="2">
-        <v>1123</v>
-      </c>
-      <c r="K42" s="2">
-        <v>39</v>
-      </c>
-      <c r="L42" s="2">
-        <v>0</v>
-      </c>
-      <c r="M42" s="2">
-        <v>0</v>
-      </c>
-      <c r="N42" s="2">
-        <v>3</v>
-      </c>
-      <c r="O42" s="2">
-        <v>163</v>
-      </c>
-      <c r="P42" s="2">
-        <v>3</v>
-      </c>
-      <c r="Q42" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="R42" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="S42" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="T42" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="43" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="F43" s="2">
-        <v>93649</v>
-      </c>
-      <c r="G43" s="2">
-        <v>130218</v>
-      </c>
-      <c r="H43" s="2">
-        <v>127469</v>
-      </c>
-      <c r="I43" s="2">
-        <v>22253</v>
-      </c>
-      <c r="J43" s="2">
-        <v>5809</v>
-      </c>
-      <c r="K43" s="2">
-        <v>329</v>
-      </c>
-      <c r="L43" s="2">
-        <v>0</v>
-      </c>
-      <c r="M43" s="2">
-        <v>1</v>
-      </c>
-      <c r="N43" s="2">
-        <v>22</v>
-      </c>
-      <c r="O43" s="2">
-        <v>301</v>
-      </c>
-      <c r="P43" s="2">
-        <v>25</v>
-      </c>
-      <c r="Q43" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="R43" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="S43" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="T43" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="44" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A44" s="2" t="s">
-        <v>130</v>
-      </c>
       <c r="B44" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="F44" s="2">
-        <v>72458</v>
+        <v>84459</v>
       </c>
       <c r="G44" s="2">
-        <v>109427</v>
+        <v>140838</v>
       </c>
       <c r="H44" s="2">
-        <v>107206</v>
+        <v>137987</v>
       </c>
       <c r="I44" s="2">
-        <v>11173</v>
+        <v>14476</v>
       </c>
       <c r="J44" s="2">
-        <v>1645</v>
+        <v>2102</v>
       </c>
       <c r="K44" s="2">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="L44" s="2">
         <v>1</v>
@@ -3494,153 +3496,214 @@
         <v>0</v>
       </c>
       <c r="N44" s="2">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="O44" s="2">
-        <v>137</v>
+        <v>167</v>
       </c>
       <c r="P44" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q44" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="R44" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="S44" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="T44" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="T44" s="2" t="s">
+      <c r="B45" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F45" s="2">
+        <v>122127</v>
+      </c>
+      <c r="G45" s="2">
+        <v>201991</v>
+      </c>
+      <c r="H45" s="2">
+        <v>195535</v>
+      </c>
+      <c r="I45" s="2">
+        <v>64884</v>
+      </c>
+      <c r="J45" s="2">
+        <v>34538</v>
+      </c>
+      <c r="K45" s="2">
+        <v>3268</v>
+      </c>
+      <c r="L45" s="2">
+        <v>522</v>
+      </c>
+      <c r="M45" s="2">
+        <v>19</v>
+      </c>
+      <c r="N45" s="2">
+        <v>114</v>
+      </c>
+      <c r="O45" s="2">
+        <v>1393</v>
+      </c>
+      <c r="P45" s="2">
+        <v>352</v>
+      </c>
+      <c r="Q45" s="2" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="45" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C45" s="2" t="s">
+      <c r="R45" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="S45" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="T45" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F46" s="2">
+        <v>98818</v>
+      </c>
+      <c r="G46" s="2">
+        <v>160977</v>
+      </c>
+      <c r="H46" s="2">
+        <v>155302</v>
+      </c>
+      <c r="I46" s="2">
+        <v>29525</v>
+      </c>
+      <c r="J46" s="2">
+        <v>11862</v>
+      </c>
+      <c r="K46" s="2">
+        <v>1379</v>
+      </c>
+      <c r="L46" s="2">
+        <v>2</v>
+      </c>
+      <c r="M46" s="2">
+        <v>6</v>
+      </c>
+      <c r="N46" s="2">
+        <v>18</v>
+      </c>
+      <c r="O46" s="2">
+        <v>520</v>
+      </c>
+      <c r="P46" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q46" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="R46" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="S46" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="T46" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D45" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="F45" s="2">
-        <v>98501</v>
-      </c>
-      <c r="G45" s="2">
-        <v>157122</v>
-      </c>
-      <c r="H45" s="2">
-        <v>152279</v>
-      </c>
-      <c r="I45" s="2">
-        <v>51037</v>
-      </c>
-      <c r="J45" s="2">
-        <v>27299</v>
-      </c>
-      <c r="K45" s="2">
-        <v>2572</v>
-      </c>
-      <c r="L45" s="2">
-        <v>410</v>
-      </c>
-      <c r="M45" s="2">
-        <v>13</v>
-      </c>
-      <c r="N45" s="2">
-        <v>87</v>
-      </c>
-      <c r="O45" s="2">
-        <v>1113</v>
-      </c>
-      <c r="P45" s="2">
-        <v>281</v>
-      </c>
-      <c r="Q45" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="R45" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="S45" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="T45" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="46" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="F46" s="2">
-        <v>80075</v>
-      </c>
-      <c r="G46" s="2">
-        <v>125256</v>
-      </c>
-      <c r="H46" s="2">
-        <v>121141</v>
-      </c>
-      <c r="I46" s="2">
-        <v>23539</v>
-      </c>
-      <c r="J46" s="2">
-        <v>9674</v>
-      </c>
-      <c r="K46" s="2">
-        <v>1085</v>
-      </c>
-      <c r="L46" s="2">
-        <v>1</v>
-      </c>
-      <c r="M46" s="2">
-        <v>4</v>
-      </c>
-      <c r="N46" s="2">
-        <v>16</v>
-      </c>
-      <c r="O46" s="2">
-        <v>413</v>
-      </c>
-      <c r="P46" s="2">
-        <v>65</v>
-      </c>
-      <c r="Q46" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="R46" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="S46" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="T46" s="2" t="s">
-        <v>126</v>
+      <c r="B47" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F47" s="2">
+        <v>508601</v>
+      </c>
+      <c r="G47" s="2">
+        <v>2301967</v>
+      </c>
+      <c r="H47" s="2">
+        <v>2254872</v>
+      </c>
+      <c r="I47" s="2">
+        <v>414370</v>
+      </c>
+      <c r="J47" s="2">
+        <v>105968</v>
+      </c>
+      <c r="K47" s="2">
+        <v>6244</v>
+      </c>
+      <c r="L47" s="2">
+        <v>532</v>
+      </c>
+      <c r="M47" s="2">
+        <v>38</v>
+      </c>
+      <c r="N47" s="2">
+        <v>285</v>
+      </c>
+      <c r="O47" s="2">
+        <v>4866</v>
+      </c>
+      <c r="P47" s="2">
+        <v>649</v>
+      </c>
+      <c r="Q47" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="R47" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="S47" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="T47" s="2" t="s">
+        <v>132</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/July.xlsx
+++ b/data/July.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="true" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAB03752-22E0-4835-A3E6-B1EC0A0BFCB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,34 +15,31 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>Author</author>
+    <author>ผู้สร้าง</author>
   </authors>
   <commentList>
-    <comment ref="F1" authorId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
+            <sz val="12"/>
             <rFont val="Arial"/>
-            <color/>
-            <sz val="12"/>
           </rPr>
-          <t xml:space="preserve">This is a reach-based metric. Reach-based metrics are de-duplicated metrics so you might see different numbers based on the level at which you are viewing data.</t>
+          <t>This is a reach-based metric. Reach-based metrics are de-duplicated metrics so you might see different numbers based on the level at which you are viewing data.</t>
         </r>
         <r>
           <rPr>
+            <sz val="12"/>
             <rFont val="Arial"/>
-            <color/>
-            <sz val="12"/>
           </rPr>
           <t xml:space="preserve">     </t>
         </r>
         <r>
           <rPr>
+            <sz val="12"/>
             <rFont val="Arial"/>
-            <color/>
-            <sz val="12"/>
           </rPr>
           <t xml:space="preserve">     </t>
         </r>
@@ -52,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="131">
   <si>
     <t>Ad name</t>
   </si>
@@ -192,9 +190,6 @@
     <t>KOLs-OLE CH -ตามหาทองนพคุณ</t>
   </si>
   <si>
-    <t>Total of 45 results</t>
-  </si>
-  <si>
     <t>Primary status</t>
   </si>
   <si>
@@ -388,9 +383,6 @@
   </si>
   <si>
     <t>1828.99</t>
-  </si>
-  <si>
-    <t>28059.55</t>
   </si>
   <si>
     <t>Reach</t>
@@ -456,8 +448,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -465,17 +457,19 @@
       <family val="2"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
       <sz val="12"/>
-      <color/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
-      <color/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="2">
@@ -513,136 +507,140 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
-      <alignment/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<theme xmlns="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
-  <themeElements>
-    <clrScheme name="Office">
-      <dk1>
-        <sysClr val="windowText" lastClr="000000"/>
-      </dk1>
-      <lt1>
-        <sysClr val="window" lastClr="FFFFFF"/>
-      </lt1>
-      <dk2>
-        <srgbClr val="44546A"/>
-      </dk2>
-      <lt2>
-        <srgbClr val="E7E6E6"/>
-      </lt2>
-      <accent1>
-        <srgbClr val="5B9BD5"/>
-      </accent1>
-      <accent2>
-        <srgbClr val="ED7D31"/>
-      </accent2>
-      <accent3>
-        <srgbClr val="A5A5A5"/>
-      </accent3>
-      <accent4>
-        <srgbClr val="FFC000"/>
-      </accent4>
-      <accent5>
-        <srgbClr val="4472C4"/>
-      </accent5>
-      <accent6>
-        <srgbClr val="70AD47"/>
-      </accent6>
-      <hlink>
-        <srgbClr val="0563C1"/>
-      </hlink>
-      <folHlink>
-        <srgbClr val="954F72"/>
-      </folHlink>
-    </clrScheme>
-    <fontScheme name="Office">
-      <majorFont>
-        <latin typeface="Calibri Light" panose="020F0302020204030204"/>
-        <ea typeface=""/>
-        <cs typeface=""/>
-        <font script="Jpan" typeface="游ゴシック Light"/>
-        <font script="Hang" typeface="맑은 고딕"/>
-        <font script="Hans" typeface="等线 Light"/>
-        <font script="Hant" typeface="新細明體"/>
-        <font script="Arab" typeface="Times New Roman"/>
-        <font script="Hebr" typeface="Times New Roman"/>
-        <font script="Thai" typeface="Tahoma"/>
-        <font script="Ethi" typeface="Nyala"/>
-        <font script="Beng" typeface="Vrinda"/>
-        <font script="Gujr" typeface="Shruti"/>
-        <font script="Khmr" typeface="MoolBoran"/>
-        <font script="Knda" typeface="Tunga"/>
-        <font script="Guru" typeface="Raavi"/>
-        <font script="Cans" typeface="Euphemia"/>
-        <font script="Cher" typeface="Plantagenet Cherokee"/>
-        <font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <font script="Tibt" typeface="Microsoft Himalaya"/>
-        <font script="Thaa" typeface="MV Boli"/>
-        <font script="Deva" typeface="Mangal"/>
-        <font script="Telu" typeface="Gautami"/>
-        <font script="Taml" typeface="Latha"/>
-        <font script="Syrc" typeface="Estrangelo Edessa"/>
-        <font script="Orya" typeface="Kalinga"/>
-        <font script="Mlym" typeface="Kartika"/>
-        <font script="Laoo" typeface="DokChampa"/>
-        <font script="Sinh" typeface="Iskoola Pota"/>
-        <font script="Mong" typeface="Mongolian Baiti"/>
-        <font script="Viet" typeface="Times New Roman"/>
-        <font script="Uigh" typeface="Microsoft Uighur"/>
-        <font script="Geor" typeface="Sylfaen"/>
-      </majorFont>
-      <minorFont>
-        <latin typeface="Calibri" panose="020F0502020204030204"/>
-        <ea typeface=""/>
-        <cs typeface=""/>
-        <font script="Jpan" typeface="游ゴシック"/>
-        <font script="Hang" typeface="맑은 고딕"/>
-        <font script="Hans" typeface="等线"/>
-        <font script="Hant" typeface="新細明體"/>
-        <font script="Arab" typeface="Arial"/>
-        <font script="Hebr" typeface="Arial"/>
-        <font script="Thai" typeface="Tahoma"/>
-        <font script="Ethi" typeface="Nyala"/>
-        <font script="Beng" typeface="Vrinda"/>
-        <font script="Gujr" typeface="Shruti"/>
-        <font script="Khmr" typeface="DaunPenh"/>
-        <font script="Knda" typeface="Tunga"/>
-        <font script="Guru" typeface="Raavi"/>
-        <font script="Cans" typeface="Euphemia"/>
-        <font script="Cher" typeface="Plantagenet Cherokee"/>
-        <font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <font script="Tibt" typeface="Microsoft Himalaya"/>
-        <font script="Thaa" typeface="MV Boli"/>
-        <font script="Deva" typeface="Mangal"/>
-        <font script="Telu" typeface="Gautami"/>
-        <font script="Taml" typeface="Latha"/>
-        <font script="Syrc" typeface="Estrangelo Edessa"/>
-        <font script="Orya" typeface="Kalinga"/>
-        <font script="Mlym" typeface="Kartika"/>
-        <font script="Laoo" typeface="DokChampa"/>
-        <font script="Sinh" typeface="Iskoola Pota"/>
-        <font script="Mong" typeface="Mongolian Baiti"/>
-        <font script="Viet" typeface="Arial"/>
-        <font script="Uigh" typeface="Microsoft Uighur"/>
-        <font script="Geor" typeface="Sylfaen"/>
-      </minorFont>
-    </fontScheme>
-    <fmtScheme name="Office">
-      <fillStyleLst>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4472C4"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -698,8 +696,8 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-      </fillStyleLst>
-      <lnStyleLst>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
         <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -721,8 +719,8 @@
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-      </lnStyleLst>
-      <effectStyleLst>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst/>
         </a:effectStyle>
@@ -738,8 +736,8 @@
             </a:outerShdw>
           </a:effectLst>
         </a:effectStyle>
-      </effectStyleLst>
-      <bgFillStyleLst>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -776,96 +774,96 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-      </bgFillStyleLst>
-    </fmtScheme>
-  </themeElements>
-  <objectDefaults/>
-  <extraClrSchemeLst/>
-</theme>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:T46"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="P1" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>124</v>
-      </c>
       <c r="R1" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="2">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F2" s="2">
         <v>19238</v>
@@ -901,33 +899,33 @@
         <v>1</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F3" s="2">
         <v>17189</v>
@@ -963,33 +961,33 @@
         <v>2</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F4" s="2">
         <v>17716</v>
@@ -1025,33 +1023,33 @@
         <v>0</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F5" s="2">
         <v>17730</v>
@@ -1087,33 +1085,33 @@
         <v>0</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F6" s="2">
         <v>17371</v>
@@ -1149,33 +1147,33 @@
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F7" s="2">
         <v>18091</v>
@@ -1211,33 +1209,33 @@
         <v>0</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F8" s="2">
         <v>17905</v>
@@ -1273,33 +1271,33 @@
         <v>4</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F9" s="2">
         <v>16997</v>
@@ -1335,33 +1333,33 @@
         <v>2</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F10" s="2">
         <v>17781</v>
@@ -1397,33 +1395,33 @@
         <v>2</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F11" s="2">
         <v>17874</v>
@@ -1459,33 +1457,33 @@
         <v>1</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F12" s="2">
         <v>17912</v>
@@ -1521,33 +1519,33 @@
         <v>1</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F13" s="2">
         <v>17425</v>
@@ -1583,33 +1581,33 @@
         <v>3</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F14" s="2">
         <v>17252</v>
@@ -1645,33 +1643,33 @@
         <v>2</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F15" s="2">
         <v>16504</v>
@@ -1707,33 +1705,33 @@
         <v>5</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F16" s="2">
         <v>16383</v>
@@ -1769,33 +1767,33 @@
         <v>2</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F17" s="2">
         <v>16723</v>
@@ -1831,33 +1829,33 @@
         <v>3</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F18" s="2">
         <v>18732</v>
@@ -1893,33 +1891,33 @@
         <v>4</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F19" s="2">
         <v>19443</v>
@@ -1955,33 +1953,33 @@
         <v>5</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="20">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F20" s="2">
         <v>19010</v>
@@ -2017,33 +2015,33 @@
         <v>1</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="21">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F21" s="2">
         <v>32278</v>
@@ -2079,33 +2077,33 @@
         <v>4</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="22">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F22" s="2">
         <v>26056</v>
@@ -2141,33 +2139,33 @@
         <v>11</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T22" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="23">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F23" s="2">
         <v>18800</v>
@@ -2203,33 +2201,33 @@
         <v>1</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="R23" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T23" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="24">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F24" s="2">
         <v>18433</v>
@@ -2265,33 +2263,33 @@
         <v>3</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T24" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F25" s="2">
         <v>18450</v>
@@ -2327,33 +2325,33 @@
         <v>3</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T25" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="26">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F26" s="2">
         <v>19033</v>
@@ -2389,33 +2387,33 @@
         <v>1</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="S26" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T26" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="27">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F27" s="2">
         <v>18392</v>
@@ -2451,33 +2449,33 @@
         <v>6</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="R27" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="S27" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T27" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="28">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F28" s="2">
         <v>18727</v>
@@ -2513,33 +2511,33 @@
         <v>2</v>
       </c>
       <c r="Q28" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="R28" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="S28" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T28" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="29">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F29" s="2">
         <v>27997</v>
@@ -2575,33 +2573,33 @@
         <v>5</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="R29" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="S29" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T29" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="30">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F30" s="2">
         <v>27602</v>
@@ -2637,33 +2635,33 @@
         <v>10</v>
       </c>
       <c r="Q30" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="R30" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="S30" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T30" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="31">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F31" s="2">
         <v>26528</v>
@@ -2699,33 +2697,33 @@
         <v>5</v>
       </c>
       <c r="Q31" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="R31" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="S31" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T31" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="32">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F32" s="2">
         <v>25301</v>
@@ -2761,33 +2759,33 @@
         <v>6</v>
       </c>
       <c r="Q32" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="R32" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="S32" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T32" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="33">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F33" s="2">
         <v>34164</v>
@@ -2823,33 +2821,33 @@
         <v>5</v>
       </c>
       <c r="Q33" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="R33" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="S33" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T33" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="34">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F34" s="2">
         <v>35884</v>
@@ -2885,33 +2883,33 @@
         <v>6</v>
       </c>
       <c r="Q34" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="R34" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="S34" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T34" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="35">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F35" s="2">
         <v>34569</v>
@@ -2947,33 +2945,33 @@
         <v>7</v>
       </c>
       <c r="Q35" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="R35" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="S35" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T35" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="36">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F36" s="2">
         <v>36356</v>
@@ -3009,33 +3007,33 @@
         <v>4</v>
       </c>
       <c r="Q36" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="R36" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="S36" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T36" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="37">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F37" s="2">
         <v>42175</v>
@@ -3071,33 +3069,33 @@
         <v>8</v>
       </c>
       <c r="Q37" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="R37" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="S37" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T37" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="38">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F38" s="2">
         <v>41146</v>
@@ -3133,33 +3131,33 @@
         <v>13</v>
       </c>
       <c r="Q38" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="R38" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="S38" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T38" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="39">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F39" s="2">
         <v>41848</v>
@@ -3195,33 +3193,33 @@
         <v>6</v>
       </c>
       <c r="Q39" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="R39" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="S39" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T39" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="40">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F40" s="2">
         <v>41733</v>
@@ -3257,33 +3255,33 @@
         <v>9</v>
       </c>
       <c r="Q40" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="R40" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="S40" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T40" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="41">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F41" s="2">
         <v>83009</v>
@@ -3319,33 +3317,33 @@
         <v>11</v>
       </c>
       <c r="Q41" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="R41" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="S41" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T41" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="42">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F42" s="2">
         <v>77782</v>
@@ -3381,33 +3379,33 @@
         <v>5</v>
       </c>
       <c r="Q42" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="R42" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="S42" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T42" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="43">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F43" s="2">
         <v>109743</v>
@@ -3443,33 +3441,33 @@
         <v>30</v>
       </c>
       <c r="Q43" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="R43" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="S43" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T43" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="44">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F44" s="2">
         <v>84459</v>
@@ -3505,33 +3503,33 @@
         <v>12</v>
       </c>
       <c r="Q44" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="R44" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="S44" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T44" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="45">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>44</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F45" s="2">
         <v>122127</v>
@@ -3567,33 +3565,33 @@
         <v>352</v>
       </c>
       <c r="Q45" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R45" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="S45" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T45" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="46">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F46" s="2">
         <v>98818</v>
@@ -3629,81 +3627,20 @@
         <v>85</v>
       </c>
       <c r="Q46" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R46" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="S46" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T46" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="F47" s="2">
-        <v>508601</v>
-      </c>
-      <c r="G47" s="2">
-        <v>2301967</v>
-      </c>
-      <c r="H47" s="2">
-        <v>2254872</v>
-      </c>
-      <c r="I47" s="2">
-        <v>414370</v>
-      </c>
-      <c r="J47" s="2">
-        <v>105968</v>
-      </c>
-      <c r="K47" s="2">
-        <v>6244</v>
-      </c>
-      <c r="L47" s="2">
-        <v>532</v>
-      </c>
-      <c r="M47" s="2">
-        <v>38</v>
-      </c>
-      <c r="N47" s="2">
-        <v>285</v>
-      </c>
-      <c r="O47" s="2">
-        <v>4866</v>
-      </c>
-      <c r="P47" s="2">
-        <v>649</v>
-      </c>
-      <c r="Q47" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="R47" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="S47" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="T47" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/July.xlsx
+++ b/data/July.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAB03752-22E0-4835-A3E6-B1EC0A0BFCB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{185E1D0B-DD4E-4325-8062-CD81B31DBF47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -250,139 +250,139 @@
     <t>Spend</t>
   </si>
   <si>
-    <t>295.82</t>
-  </si>
-  <si>
-    <t>294.32</t>
-  </si>
-  <si>
-    <t>301.12</t>
-  </si>
-  <si>
-    <t>297.31</t>
-  </si>
-  <si>
-    <t>292.98</t>
-  </si>
-  <si>
-    <t>295.37</t>
-  </si>
-  <si>
-    <t>301.80</t>
-  </si>
-  <si>
-    <t>295.93</t>
-  </si>
-  <si>
-    <t>296.88</t>
-  </si>
-  <si>
-    <t>300.54</t>
-  </si>
-  <si>
-    <t>299.48</t>
-  </si>
-  <si>
-    <t>296.82</t>
-  </si>
-  <si>
-    <t>297.05</t>
-  </si>
-  <si>
-    <t>292.24</t>
-  </si>
-  <si>
-    <t>295.27</t>
-  </si>
-  <si>
-    <t>285.14</t>
-  </si>
-  <si>
-    <t>308.88</t>
-  </si>
-  <si>
-    <t>311.27</t>
-  </si>
-  <si>
-    <t>303.03</t>
-  </si>
-  <si>
-    <t>267.88</t>
-  </si>
-  <si>
-    <t>276.46</t>
-  </si>
-  <si>
-    <t>300.44</t>
-  </si>
-  <si>
-    <t>301.70</t>
-  </si>
-  <si>
-    <t>306.47</t>
-  </si>
-  <si>
-    <t>296.45</t>
-  </si>
-  <si>
-    <t>295.89</t>
-  </si>
-  <si>
-    <t>291.64</t>
-  </si>
-  <si>
-    <t>270.29</t>
-  </si>
-  <si>
-    <t>858.76</t>
-  </si>
-  <si>
-    <t>811.88</t>
-  </si>
-  <si>
-    <t>797.40</t>
-  </si>
-  <si>
-    <t>821.24</t>
-  </si>
-  <si>
-    <t>865.14</t>
-  </si>
-  <si>
-    <t>856.53</t>
-  </si>
-  <si>
-    <t>863.20</t>
-  </si>
-  <si>
-    <t>873.23</t>
-  </si>
-  <si>
-    <t>854.55</t>
-  </si>
-  <si>
-    <t>878.29</t>
-  </si>
-  <si>
-    <t>842.99</t>
-  </si>
-  <si>
-    <t>1720.00</t>
-  </si>
-  <si>
-    <t>1709.29</t>
-  </si>
-  <si>
-    <t>1594.93</t>
-  </si>
-  <si>
-    <t>1780.47</t>
-  </si>
-  <si>
-    <t>1834.19</t>
-  </si>
-  <si>
-    <t>1828.99</t>
+    <t>872.79</t>
+  </si>
+  <si>
+    <t>878.84</t>
+  </si>
+  <si>
+    <t>851.56</t>
+  </si>
+  <si>
+    <t>866.57</t>
+  </si>
+  <si>
+    <t>850.58</t>
+  </si>
+  <si>
+    <t>822.81</t>
+  </si>
+  <si>
+    <t>861.43</t>
+  </si>
+  <si>
+    <t>868.01</t>
+  </si>
+  <si>
+    <t>868.29</t>
+  </si>
+  <si>
+    <t>889.52</t>
+  </si>
+  <si>
+    <t>870.89</t>
+  </si>
+  <si>
+    <t>865.20</t>
+  </si>
+  <si>
+    <t>839.55</t>
+  </si>
+  <si>
+    <t>854.87</t>
+  </si>
+  <si>
+    <t>849.10</t>
+  </si>
+  <si>
+    <t>785.84</t>
+  </si>
+  <si>
+    <t>906.74</t>
+  </si>
+  <si>
+    <t>887.07</t>
+  </si>
+  <si>
+    <t>888.87</t>
+  </si>
+  <si>
+    <t>763.52</t>
+  </si>
+  <si>
+    <t>668.87</t>
+  </si>
+  <si>
+    <t>909.36</t>
+  </si>
+  <si>
+    <t>896.67</t>
+  </si>
+  <si>
+    <t>889.24</t>
+  </si>
+  <si>
+    <t>845.50</t>
+  </si>
+  <si>
+    <t>901.79</t>
+  </si>
+  <si>
+    <t>733.85</t>
+  </si>
+  <si>
+    <t>695.54</t>
+  </si>
+  <si>
+    <t>1701.09</t>
+  </si>
+  <si>
+    <t>1685.32</t>
+  </si>
+  <si>
+    <t>1633.73</t>
+  </si>
+  <si>
+    <t>1613.20</t>
+  </si>
+  <si>
+    <t>1674.89</t>
+  </si>
+  <si>
+    <t>1697.22</t>
+  </si>
+  <si>
+    <t>1673.65</t>
+  </si>
+  <si>
+    <t>1745.65</t>
+  </si>
+  <si>
+    <t>1721.80</t>
+  </si>
+  <si>
+    <t>1738.31</t>
+  </si>
+  <si>
+    <t>1714.83</t>
+  </si>
+  <si>
+    <t>3395.99</t>
+  </si>
+  <si>
+    <t>3366.22</t>
+  </si>
+  <si>
+    <t>3198.26</t>
+  </si>
+  <si>
+    <t>3454.26</t>
+  </si>
+  <si>
+    <t>3457.24</t>
+  </si>
+  <si>
+    <t>3514.04</t>
   </si>
   <si>
     <t>Reach</t>
@@ -866,37 +866,37 @@
         <v>66</v>
       </c>
       <c r="F2" s="2">
-        <v>19238</v>
+        <v>59501</v>
       </c>
       <c r="G2" s="2">
-        <v>23646</v>
+        <v>72611</v>
       </c>
       <c r="H2" s="2">
-        <v>23300</v>
+        <v>71319</v>
       </c>
       <c r="I2" s="2">
-        <v>4102</v>
+        <v>12662</v>
       </c>
       <c r="J2" s="2">
-        <v>737</v>
+        <v>2380</v>
       </c>
       <c r="K2" s="2">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="L2" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" s="2">
         <v>0</v>
       </c>
       <c r="N2" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="O2" s="2">
-        <v>38</v>
+        <v>109</v>
       </c>
       <c r="P2" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q2" s="2" t="s">
         <v>123</v>
@@ -928,37 +928,37 @@
         <v>67</v>
       </c>
       <c r="F3" s="2">
-        <v>17189</v>
+        <v>49166</v>
       </c>
       <c r="G3" s="2">
-        <v>22387</v>
+        <v>68199</v>
       </c>
       <c r="H3" s="2">
-        <v>22064</v>
+        <v>66890</v>
       </c>
       <c r="I3" s="2">
-        <v>3019</v>
+        <v>8546</v>
       </c>
       <c r="J3" s="2">
-        <v>701</v>
+        <v>2040</v>
       </c>
       <c r="K3" s="2">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="L3" s="2">
         <v>0</v>
       </c>
       <c r="M3" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N3" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O3" s="2">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="P3" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Q3" s="2" t="s">
         <v>123</v>
@@ -990,22 +990,22 @@
         <v>68</v>
       </c>
       <c r="F4" s="2">
-        <v>17716</v>
+        <v>48574</v>
       </c>
       <c r="G4" s="2">
-        <v>23069</v>
+        <v>66733</v>
       </c>
       <c r="H4" s="2">
-        <v>22682</v>
+        <v>65221</v>
       </c>
       <c r="I4" s="2">
-        <v>3471</v>
+        <v>9383</v>
       </c>
       <c r="J4" s="2">
-        <v>551</v>
+        <v>1489</v>
       </c>
       <c r="K4" s="2">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="L4" s="2">
         <v>0</v>
@@ -1014,13 +1014,13 @@
         <v>0</v>
       </c>
       <c r="N4" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O4" s="2">
-        <v>36</v>
+        <v>91</v>
       </c>
       <c r="P4" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q4" s="2" t="s">
         <v>123</v>
@@ -1052,37 +1052,37 @@
         <v>69</v>
       </c>
       <c r="F5" s="2">
-        <v>17730</v>
+        <v>49677</v>
       </c>
       <c r="G5" s="2">
-        <v>22430</v>
+        <v>66829</v>
       </c>
       <c r="H5" s="2">
-        <v>22120</v>
+        <v>65479</v>
       </c>
       <c r="I5" s="2">
-        <v>11726</v>
+        <v>34281</v>
       </c>
       <c r="J5" s="2">
-        <v>2956</v>
+        <v>9447</v>
       </c>
       <c r="K5" s="2">
-        <v>25</v>
+        <v>93</v>
       </c>
       <c r="L5" s="2">
+        <v>3</v>
+      </c>
+      <c r="M5" s="2">
         <v>1</v>
       </c>
-      <c r="M5" s="2">
-        <v>0</v>
-      </c>
       <c r="N5" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O5" s="2">
-        <v>30</v>
+        <v>127</v>
       </c>
       <c r="P5" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q5" s="2" t="s">
         <v>123</v>
@@ -1114,22 +1114,22 @@
         <v>70</v>
       </c>
       <c r="F6" s="2">
-        <v>17371</v>
+        <v>49182</v>
       </c>
       <c r="G6" s="2">
-        <v>22517</v>
+        <v>66791</v>
       </c>
       <c r="H6" s="2">
-        <v>22185</v>
+        <v>65420</v>
       </c>
       <c r="I6" s="2">
-        <v>3445</v>
+        <v>9884</v>
       </c>
       <c r="J6" s="2">
-        <v>749</v>
+        <v>2448</v>
       </c>
       <c r="K6" s="2">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="L6" s="2">
         <v>0</v>
@@ -1138,13 +1138,13 @@
         <v>0</v>
       </c>
       <c r="N6" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O6" s="2">
-        <v>28</v>
+        <v>117</v>
       </c>
       <c r="P6" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Q6" s="2" t="s">
         <v>123</v>
@@ -1176,22 +1176,22 @@
         <v>71</v>
       </c>
       <c r="F7" s="2">
-        <v>18091</v>
+        <v>48421</v>
       </c>
       <c r="G7" s="2">
-        <v>22991</v>
+        <v>65751</v>
       </c>
       <c r="H7" s="2">
-        <v>22563</v>
+        <v>64411</v>
       </c>
       <c r="I7" s="2">
-        <v>2169</v>
+        <v>5883</v>
       </c>
       <c r="J7" s="2">
-        <v>390</v>
+        <v>1049</v>
       </c>
       <c r="K7" s="2">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="L7" s="2">
         <v>0</v>
@@ -1203,10 +1203,10 @@
         <v>1</v>
       </c>
       <c r="O7" s="2">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="P7" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q7" s="2" t="s">
         <v>123</v>
@@ -1238,22 +1238,22 @@
         <v>72</v>
       </c>
       <c r="F8" s="2">
-        <v>17905</v>
+        <v>49489</v>
       </c>
       <c r="G8" s="2">
-        <v>22863</v>
+        <v>66767</v>
       </c>
       <c r="H8" s="2">
-        <v>22457</v>
+        <v>65381</v>
       </c>
       <c r="I8" s="2">
-        <v>2260</v>
+        <v>5942</v>
       </c>
       <c r="J8" s="2">
-        <v>379</v>
+        <v>993</v>
       </c>
       <c r="K8" s="2">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="L8" s="2">
         <v>0</v>
@@ -1262,13 +1262,13 @@
         <v>0</v>
       </c>
       <c r="N8" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O8" s="2">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="P8" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q8" s="2" t="s">
         <v>123</v>
@@ -1300,22 +1300,22 @@
         <v>73</v>
       </c>
       <c r="F9" s="2">
-        <v>16997</v>
+        <v>47498</v>
       </c>
       <c r="G9" s="2">
-        <v>21828</v>
+        <v>66062</v>
       </c>
       <c r="H9" s="2">
-        <v>21451</v>
+        <v>64708</v>
       </c>
       <c r="I9" s="2">
-        <v>2731</v>
+        <v>7995</v>
       </c>
       <c r="J9" s="2">
-        <v>455</v>
+        <v>1433</v>
       </c>
       <c r="K9" s="2">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="L9" s="2">
         <v>0</v>
@@ -1324,13 +1324,13 @@
         <v>0</v>
       </c>
       <c r="N9" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="O9" s="2">
-        <v>27</v>
+        <v>100</v>
       </c>
       <c r="P9" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Q9" s="2" t="s">
         <v>123</v>
@@ -1362,37 +1362,37 @@
         <v>74</v>
       </c>
       <c r="F10" s="2">
-        <v>17781</v>
+        <v>50754</v>
       </c>
       <c r="G10" s="2">
-        <v>22617</v>
+        <v>68291</v>
       </c>
       <c r="H10" s="2">
-        <v>22192</v>
+        <v>66962</v>
       </c>
       <c r="I10" s="2">
-        <v>1814</v>
+        <v>5496</v>
       </c>
       <c r="J10" s="2">
-        <v>350</v>
+        <v>1044</v>
       </c>
       <c r="K10" s="2">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="L10" s="2">
         <v>0</v>
       </c>
       <c r="M10" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N10" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O10" s="2">
-        <v>41</v>
+        <v>123</v>
       </c>
       <c r="P10" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q10" s="2" t="s">
         <v>123</v>
@@ -1424,37 +1424,37 @@
         <v>75</v>
       </c>
       <c r="F11" s="2">
-        <v>17874</v>
+        <v>48806</v>
       </c>
       <c r="G11" s="2">
-        <v>22648</v>
+        <v>68984</v>
       </c>
       <c r="H11" s="2">
-        <v>22301</v>
+        <v>67778</v>
       </c>
       <c r="I11" s="2">
-        <v>1934</v>
+        <v>5767</v>
       </c>
       <c r="J11" s="2">
-        <v>440</v>
+        <v>1329</v>
       </c>
       <c r="K11" s="2">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="L11" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="2">
         <v>0</v>
       </c>
       <c r="N11" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O11" s="2">
-        <v>49</v>
+        <v>113</v>
       </c>
       <c r="P11" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q11" s="2" t="s">
         <v>123</v>
@@ -1486,22 +1486,22 @@
         <v>76</v>
       </c>
       <c r="F12" s="2">
-        <v>17912</v>
+        <v>49943</v>
       </c>
       <c r="G12" s="2">
-        <v>22747</v>
+        <v>67791</v>
       </c>
       <c r="H12" s="2">
-        <v>22404</v>
+        <v>66671</v>
       </c>
       <c r="I12" s="2">
-        <v>2868</v>
+        <v>8610</v>
       </c>
       <c r="J12" s="2">
-        <v>568</v>
+        <v>1805</v>
       </c>
       <c r="K12" s="2">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="L12" s="2">
         <v>0</v>
@@ -1510,13 +1510,13 @@
         <v>0</v>
       </c>
       <c r="N12" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O12" s="2">
-        <v>36</v>
+        <v>110</v>
       </c>
       <c r="P12" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q12" s="2" t="s">
         <v>123</v>
@@ -1548,37 +1548,37 @@
         <v>77</v>
       </c>
       <c r="F13" s="2">
-        <v>17425</v>
+        <v>48340</v>
       </c>
       <c r="G13" s="2">
-        <v>22439</v>
+        <v>67010</v>
       </c>
       <c r="H13" s="2">
-        <v>22129</v>
+        <v>65780</v>
       </c>
       <c r="I13" s="2">
-        <v>2242</v>
+        <v>6642</v>
       </c>
       <c r="J13" s="2">
-        <v>497</v>
+        <v>1552</v>
       </c>
       <c r="K13" s="2">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="L13" s="2">
         <v>0</v>
       </c>
       <c r="M13" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O13" s="2">
-        <v>35</v>
+        <v>107</v>
       </c>
       <c r="P13" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Q13" s="2" t="s">
         <v>123</v>
@@ -1610,22 +1610,22 @@
         <v>78</v>
       </c>
       <c r="F14" s="2">
-        <v>17252</v>
+        <v>47705</v>
       </c>
       <c r="G14" s="2">
-        <v>22875</v>
+        <v>66177</v>
       </c>
       <c r="H14" s="2">
-        <v>22575</v>
+        <v>64917</v>
       </c>
       <c r="I14" s="2">
-        <v>6014</v>
+        <v>17166</v>
       </c>
       <c r="J14" s="2">
-        <v>2473</v>
+        <v>6954</v>
       </c>
       <c r="K14" s="2">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c r="L14" s="2">
         <v>0</v>
@@ -1634,13 +1634,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O14" s="2">
-        <v>43</v>
+        <v>122</v>
       </c>
       <c r="P14" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q14" s="2" t="s">
         <v>123</v>
@@ -1672,37 +1672,37 @@
         <v>79</v>
       </c>
       <c r="F15" s="2">
-        <v>16504</v>
+        <v>46419</v>
       </c>
       <c r="G15" s="2">
-        <v>21700</v>
+        <v>64588</v>
       </c>
       <c r="H15" s="2">
-        <v>21362</v>
+        <v>63234</v>
       </c>
       <c r="I15" s="2">
-        <v>4037</v>
+        <v>12246</v>
       </c>
       <c r="J15" s="2">
-        <v>722</v>
+        <v>2152</v>
       </c>
       <c r="K15" s="2">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="L15" s="2">
         <v>0</v>
       </c>
       <c r="M15" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N15" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O15" s="2">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="P15" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q15" s="2" t="s">
         <v>123</v>
@@ -1734,37 +1734,37 @@
         <v>80</v>
       </c>
       <c r="F16" s="2">
-        <v>16383</v>
+        <v>45806</v>
       </c>
       <c r="G16" s="2">
-        <v>21825</v>
+        <v>63981</v>
       </c>
       <c r="H16" s="2">
-        <v>21449</v>
+        <v>62517</v>
       </c>
       <c r="I16" s="2">
-        <v>3799</v>
+        <v>11257</v>
       </c>
       <c r="J16" s="2">
-        <v>888</v>
+        <v>2819</v>
       </c>
       <c r="K16" s="2">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="L16" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" s="2">
         <v>1</v>
       </c>
       <c r="N16" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O16" s="2">
-        <v>43</v>
+        <v>113</v>
       </c>
       <c r="P16" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q16" s="2" t="s">
         <v>123</v>
@@ -1796,25 +1796,25 @@
         <v>81</v>
       </c>
       <c r="F17" s="2">
-        <v>16723</v>
+        <v>45036</v>
       </c>
       <c r="G17" s="2">
-        <v>22109</v>
+        <v>62616</v>
       </c>
       <c r="H17" s="2">
-        <v>21759</v>
+        <v>61426</v>
       </c>
       <c r="I17" s="2">
-        <v>2566</v>
+        <v>7446</v>
       </c>
       <c r="J17" s="2">
-        <v>538</v>
+        <v>1555</v>
       </c>
       <c r="K17" s="2">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="L17" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M17" s="2">
         <v>0</v>
@@ -1823,10 +1823,10 @@
         <v>2</v>
       </c>
       <c r="O17" s="2">
-        <v>27</v>
+        <v>89</v>
       </c>
       <c r="P17" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q17" s="2" t="s">
         <v>123</v>
@@ -1858,22 +1858,22 @@
         <v>82</v>
       </c>
       <c r="F18" s="2">
-        <v>18732</v>
+        <v>55238</v>
       </c>
       <c r="G18" s="2">
-        <v>23240</v>
+        <v>71384</v>
       </c>
       <c r="H18" s="2">
-        <v>22832</v>
+        <v>69843</v>
       </c>
       <c r="I18" s="2">
-        <v>8113</v>
+        <v>22713</v>
       </c>
       <c r="J18" s="2">
-        <v>1671</v>
+        <v>4763</v>
       </c>
       <c r="K18" s="2">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="L18" s="2">
         <v>1</v>
@@ -1882,10 +1882,10 @@
         <v>0</v>
       </c>
       <c r="N18" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O18" s="2">
-        <v>21</v>
+        <v>72</v>
       </c>
       <c r="P18" s="2">
         <v>4</v>
@@ -1920,22 +1920,22 @@
         <v>83</v>
       </c>
       <c r="F19" s="2">
-        <v>19443</v>
+        <v>54747</v>
       </c>
       <c r="G19" s="2">
-        <v>24057</v>
+        <v>70691</v>
       </c>
       <c r="H19" s="2">
-        <v>23691</v>
+        <v>69180</v>
       </c>
       <c r="I19" s="2">
-        <v>4750</v>
+        <v>12950</v>
       </c>
       <c r="J19" s="2">
-        <v>792</v>
+        <v>2134</v>
       </c>
       <c r="K19" s="2">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="L19" s="2">
         <v>0</v>
@@ -1944,13 +1944,13 @@
         <v>0</v>
       </c>
       <c r="N19" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O19" s="2">
-        <v>31</v>
+        <v>98</v>
       </c>
       <c r="P19" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q19" s="2" t="s">
         <v>123</v>
@@ -1982,37 +1982,37 @@
         <v>84</v>
       </c>
       <c r="F20" s="2">
-        <v>19010</v>
+        <v>55282</v>
       </c>
       <c r="G20" s="2">
-        <v>23675</v>
+        <v>71677</v>
       </c>
       <c r="H20" s="2">
-        <v>23295</v>
+        <v>70357</v>
       </c>
       <c r="I20" s="2">
-        <v>2830</v>
+        <v>7711</v>
       </c>
       <c r="J20" s="2">
-        <v>433</v>
+        <v>1282</v>
       </c>
       <c r="K20" s="2">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="L20" s="2">
         <v>0</v>
       </c>
       <c r="M20" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N20" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O20" s="2">
-        <v>32</v>
+        <v>91</v>
       </c>
       <c r="P20" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q20" s="2" t="s">
         <v>123</v>
@@ -2044,37 +2044,37 @@
         <v>85</v>
       </c>
       <c r="F21" s="2">
-        <v>32278</v>
+        <v>94919</v>
       </c>
       <c r="G21" s="2">
-        <v>40871</v>
+        <v>121866</v>
       </c>
       <c r="H21" s="2">
-        <v>39578</v>
+        <v>117444</v>
       </c>
       <c r="I21" s="2">
-        <v>10671</v>
+        <v>30275</v>
       </c>
       <c r="J21" s="2">
-        <v>1881</v>
+        <v>5793</v>
       </c>
       <c r="K21" s="2">
-        <v>41</v>
+        <v>134</v>
       </c>
       <c r="L21" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M21" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N21" s="2">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="O21" s="2">
-        <v>54</v>
+        <v>187</v>
       </c>
       <c r="P21" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="Q21" s="2" t="s">
         <v>123</v>
@@ -2106,37 +2106,37 @@
         <v>86</v>
       </c>
       <c r="F22" s="2">
-        <v>26056</v>
+        <v>67441</v>
       </c>
       <c r="G22" s="2">
-        <v>33015</v>
+        <v>85122</v>
       </c>
       <c r="H22" s="2">
-        <v>32071</v>
+        <v>81679</v>
       </c>
       <c r="I22" s="2">
-        <v>4651</v>
+        <v>11446</v>
       </c>
       <c r="J22" s="2">
-        <v>852</v>
+        <v>2071</v>
       </c>
       <c r="K22" s="2">
-        <v>33</v>
+        <v>91</v>
       </c>
       <c r="L22" s="2">
         <v>0</v>
       </c>
       <c r="M22" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N22" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O22" s="2">
-        <v>25</v>
+        <v>101</v>
       </c>
       <c r="P22" s="2">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="Q22" s="2" t="s">
         <v>123</v>
@@ -2168,22 +2168,22 @@
         <v>87</v>
       </c>
       <c r="F23" s="2">
-        <v>18800</v>
+        <v>57074</v>
       </c>
       <c r="G23" s="2">
-        <v>23260</v>
+        <v>72931</v>
       </c>
       <c r="H23" s="2">
-        <v>22974</v>
+        <v>71517</v>
       </c>
       <c r="I23" s="2">
-        <v>3379</v>
+        <v>9939</v>
       </c>
       <c r="J23" s="2">
-        <v>899</v>
+        <v>2511</v>
       </c>
       <c r="K23" s="2">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="L23" s="2">
         <v>0</v>
@@ -2192,13 +2192,13 @@
         <v>0</v>
       </c>
       <c r="N23" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O23" s="2">
-        <v>18</v>
+        <v>77</v>
       </c>
       <c r="P23" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Q23" s="2" t="s">
         <v>123</v>
@@ -2230,37 +2230,37 @@
         <v>88</v>
       </c>
       <c r="F24" s="2">
-        <v>18433</v>
+        <v>55187</v>
       </c>
       <c r="G24" s="2">
-        <v>23108</v>
+        <v>71420</v>
       </c>
       <c r="H24" s="2">
-        <v>22674</v>
+        <v>69708</v>
       </c>
       <c r="I24" s="2">
-        <v>2007</v>
+        <v>5875</v>
       </c>
       <c r="J24" s="2">
-        <v>352</v>
+        <v>1036</v>
       </c>
       <c r="K24" s="2">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="L24" s="2">
         <v>0</v>
       </c>
       <c r="M24" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O24" s="2">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="P24" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q24" s="2" t="s">
         <v>123</v>
@@ -2292,37 +2292,37 @@
         <v>89</v>
       </c>
       <c r="F25" s="2">
-        <v>18450</v>
+        <v>54479</v>
       </c>
       <c r="G25" s="2">
-        <v>23512</v>
+        <v>70326</v>
       </c>
       <c r="H25" s="2">
-        <v>23227</v>
+        <v>68947</v>
       </c>
       <c r="I25" s="2">
-        <v>2555</v>
+        <v>7280</v>
       </c>
       <c r="J25" s="2">
-        <v>458</v>
+        <v>1302</v>
       </c>
       <c r="K25" s="2">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="L25" s="2">
         <v>0</v>
       </c>
       <c r="M25" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N25" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O25" s="2">
-        <v>28</v>
+        <v>91</v>
       </c>
       <c r="P25" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Q25" s="2" t="s">
         <v>123</v>
@@ -2354,37 +2354,37 @@
         <v>90</v>
       </c>
       <c r="F26" s="2">
-        <v>19033</v>
+        <v>55902</v>
       </c>
       <c r="G26" s="2">
-        <v>23384</v>
+        <v>68656</v>
       </c>
       <c r="H26" s="2">
-        <v>23035</v>
+        <v>67255</v>
       </c>
       <c r="I26" s="2">
-        <v>4613</v>
+        <v>13328</v>
       </c>
       <c r="J26" s="2">
-        <v>519</v>
+        <v>1634</v>
       </c>
       <c r="K26" s="2">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="L26" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M26" s="2">
         <v>0</v>
       </c>
       <c r="N26" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O26" s="2">
-        <v>38</v>
+        <v>115</v>
       </c>
       <c r="P26" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Q26" s="2" t="s">
         <v>123</v>
@@ -2416,37 +2416,37 @@
         <v>91</v>
       </c>
       <c r="F27" s="2">
-        <v>18392</v>
+        <v>56081</v>
       </c>
       <c r="G27" s="2">
-        <v>22583</v>
+        <v>71125</v>
       </c>
       <c r="H27" s="2">
-        <v>22195</v>
+        <v>69504</v>
       </c>
       <c r="I27" s="2">
-        <v>2419</v>
+        <v>7346</v>
       </c>
       <c r="J27" s="2">
-        <v>493</v>
+        <v>1521</v>
       </c>
       <c r="K27" s="2">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="L27" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" s="2">
         <v>0</v>
       </c>
       <c r="N27" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O27" s="2">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="P27" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q27" s="2" t="s">
         <v>123</v>
@@ -2478,22 +2478,22 @@
         <v>92</v>
       </c>
       <c r="F28" s="2">
-        <v>18727</v>
+        <v>47163</v>
       </c>
       <c r="G28" s="2">
-        <v>22770</v>
+        <v>58237</v>
       </c>
       <c r="H28" s="2">
-        <v>22480</v>
+        <v>57132</v>
       </c>
       <c r="I28" s="2">
-        <v>4825</v>
+        <v>11938</v>
       </c>
       <c r="J28" s="2">
-        <v>982</v>
+        <v>2706</v>
       </c>
       <c r="K28" s="2">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="L28" s="2">
         <v>0</v>
@@ -2502,13 +2502,13 @@
         <v>1</v>
       </c>
       <c r="N28" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="O28" s="2">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="P28" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q28" s="2" t="s">
         <v>123</v>
@@ -2540,22 +2540,22 @@
         <v>93</v>
       </c>
       <c r="F29" s="2">
-        <v>27997</v>
+        <v>74727</v>
       </c>
       <c r="G29" s="2">
-        <v>35656</v>
+        <v>92957</v>
       </c>
       <c r="H29" s="2">
-        <v>34729</v>
+        <v>89813</v>
       </c>
       <c r="I29" s="2">
-        <v>5083</v>
+        <v>13844</v>
       </c>
       <c r="J29" s="2">
-        <v>734</v>
+        <v>2210</v>
       </c>
       <c r="K29" s="2">
-        <v>39</v>
+        <v>109</v>
       </c>
       <c r="L29" s="2">
         <v>0</v>
@@ -2564,13 +2564,13 @@
         <v>0</v>
       </c>
       <c r="N29" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="O29" s="2">
-        <v>76</v>
+        <v>177</v>
       </c>
       <c r="P29" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="Q29" s="2" t="s">
         <v>123</v>
@@ -2602,37 +2602,37 @@
         <v>94</v>
       </c>
       <c r="F30" s="2">
-        <v>27602</v>
+        <v>36854</v>
       </c>
       <c r="G30" s="2">
-        <v>54389</v>
+        <v>99345</v>
       </c>
       <c r="H30" s="2">
-        <v>53500</v>
+        <v>97533</v>
       </c>
       <c r="I30" s="2">
-        <v>14973</v>
+        <v>24903</v>
       </c>
       <c r="J30" s="2">
-        <v>3581</v>
+        <v>5894</v>
       </c>
       <c r="K30" s="2">
-        <v>75</v>
+        <v>140</v>
       </c>
       <c r="L30" s="2">
         <v>3</v>
       </c>
       <c r="M30" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N30" s="2">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="O30" s="2">
-        <v>107</v>
+        <v>199</v>
       </c>
       <c r="P30" s="2">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="Q30" s="2" t="s">
         <v>123</v>
@@ -2664,37 +2664,37 @@
         <v>95</v>
       </c>
       <c r="F31" s="2">
-        <v>26528</v>
+        <v>38640</v>
       </c>
       <c r="G31" s="2">
-        <v>51373</v>
+        <v>100520</v>
       </c>
       <c r="H31" s="2">
-        <v>50472</v>
+        <v>98661</v>
       </c>
       <c r="I31" s="2">
-        <v>9673</v>
+        <v>18781</v>
       </c>
       <c r="J31" s="2">
-        <v>1950</v>
+        <v>3768</v>
       </c>
       <c r="K31" s="2">
-        <v>52</v>
+        <v>89</v>
       </c>
       <c r="L31" s="2">
         <v>0</v>
       </c>
       <c r="M31" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N31" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="O31" s="2">
-        <v>92</v>
+        <v>179</v>
       </c>
       <c r="P31" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="Q31" s="2" t="s">
         <v>123</v>
@@ -2726,37 +2726,37 @@
         <v>96</v>
       </c>
       <c r="F32" s="2">
-        <v>25301</v>
+        <v>37307</v>
       </c>
       <c r="G32" s="2">
-        <v>48200</v>
+        <v>93098</v>
       </c>
       <c r="H32" s="2">
-        <v>47346</v>
+        <v>91208</v>
       </c>
       <c r="I32" s="2">
-        <v>6432</v>
+        <v>12182</v>
       </c>
       <c r="J32" s="2">
-        <v>1393</v>
+        <v>2659</v>
       </c>
       <c r="K32" s="2">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="L32" s="2">
         <v>0</v>
       </c>
       <c r="M32" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N32" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O32" s="2">
-        <v>96</v>
+        <v>187</v>
       </c>
       <c r="P32" s="2">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="Q32" s="2" t="s">
         <v>123</v>
@@ -2788,22 +2788,22 @@
         <v>97</v>
       </c>
       <c r="F33" s="2">
-        <v>34164</v>
+        <v>49585</v>
       </c>
       <c r="G33" s="2">
-        <v>61522</v>
+        <v>115684</v>
       </c>
       <c r="H33" s="2">
-        <v>60423</v>
+        <v>113342</v>
       </c>
       <c r="I33" s="2">
-        <v>6299</v>
+        <v>11388</v>
       </c>
       <c r="J33" s="2">
-        <v>1261</v>
+        <v>2409</v>
       </c>
       <c r="K33" s="2">
-        <v>31</v>
+        <v>65</v>
       </c>
       <c r="L33" s="2">
         <v>0</v>
@@ -2812,13 +2812,13 @@
         <v>0</v>
       </c>
       <c r="N33" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O33" s="2">
-        <v>76</v>
+        <v>169</v>
       </c>
       <c r="P33" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Q33" s="2" t="s">
         <v>123</v>
@@ -2850,22 +2850,22 @@
         <v>98</v>
       </c>
       <c r="F34" s="2">
-        <v>35884</v>
+        <v>49994</v>
       </c>
       <c r="G34" s="2">
-        <v>65687</v>
+        <v>121755</v>
       </c>
       <c r="H34" s="2">
-        <v>64372</v>
+        <v>118997</v>
       </c>
       <c r="I34" s="2">
-        <v>4111</v>
+        <v>7628</v>
       </c>
       <c r="J34" s="2">
-        <v>1096</v>
+        <v>2042</v>
       </c>
       <c r="K34" s="2">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="L34" s="2">
         <v>0</v>
@@ -2874,13 +2874,13 @@
         <v>0</v>
       </c>
       <c r="N34" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O34" s="2">
-        <v>93</v>
+        <v>184</v>
       </c>
       <c r="P34" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Q34" s="2" t="s">
         <v>123</v>
@@ -2912,22 +2912,22 @@
         <v>99</v>
       </c>
       <c r="F35" s="2">
-        <v>34569</v>
+        <v>50217</v>
       </c>
       <c r="G35" s="2">
-        <v>63057</v>
+        <v>119552</v>
       </c>
       <c r="H35" s="2">
-        <v>61976</v>
+        <v>117195</v>
       </c>
       <c r="I35" s="2">
-        <v>4935</v>
+        <v>9276</v>
       </c>
       <c r="J35" s="2">
-        <v>1100</v>
+        <v>2226</v>
       </c>
       <c r="K35" s="2">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="L35" s="2">
         <v>0</v>
@@ -2936,13 +2936,13 @@
         <v>0</v>
       </c>
       <c r="N35" s="2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="O35" s="2">
-        <v>120</v>
+        <v>218</v>
       </c>
       <c r="P35" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q35" s="2" t="s">
         <v>123</v>
@@ -2974,37 +2974,37 @@
         <v>100</v>
       </c>
       <c r="F36" s="2">
-        <v>36356</v>
+        <v>49890</v>
       </c>
       <c r="G36" s="2">
-        <v>66014</v>
+        <v>122408</v>
       </c>
       <c r="H36" s="2">
-        <v>64927</v>
+        <v>120063</v>
       </c>
       <c r="I36" s="2">
-        <v>4200</v>
+        <v>7698</v>
       </c>
       <c r="J36" s="2">
-        <v>1042</v>
+        <v>2039</v>
       </c>
       <c r="K36" s="2">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="L36" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" s="2">
         <v>0</v>
       </c>
       <c r="N36" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O36" s="2">
-        <v>119</v>
+        <v>241</v>
       </c>
       <c r="P36" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Q36" s="2" t="s">
         <v>123</v>
@@ -3036,37 +3036,37 @@
         <v>101</v>
       </c>
       <c r="F37" s="2">
-        <v>42175</v>
+        <v>63268</v>
       </c>
       <c r="G37" s="2">
-        <v>67381</v>
+        <v>126554</v>
       </c>
       <c r="H37" s="2">
-        <v>66368</v>
+        <v>124351</v>
       </c>
       <c r="I37" s="2">
-        <v>18860</v>
+        <v>33753</v>
       </c>
       <c r="J37" s="2">
-        <v>2242</v>
+        <v>4348</v>
       </c>
       <c r="K37" s="2">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="L37" s="2">
         <v>0</v>
       </c>
       <c r="M37" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N37" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="O37" s="2">
-        <v>78</v>
+        <v>164</v>
       </c>
       <c r="P37" s="2">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Q37" s="2" t="s">
         <v>123</v>
@@ -3098,37 +3098,37 @@
         <v>102</v>
       </c>
       <c r="F38" s="2">
-        <v>41146</v>
+        <v>64534</v>
       </c>
       <c r="G38" s="2">
-        <v>66149</v>
+        <v>128514</v>
       </c>
       <c r="H38" s="2">
-        <v>65079</v>
+        <v>125979</v>
       </c>
       <c r="I38" s="2">
-        <v>22439</v>
+        <v>42561</v>
       </c>
       <c r="J38" s="2">
-        <v>4222</v>
+        <v>8228</v>
       </c>
       <c r="K38" s="2">
-        <v>89</v>
+        <v>164</v>
       </c>
       <c r="L38" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M38" s="2">
         <v>0</v>
       </c>
       <c r="N38" s="2">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="O38" s="2">
-        <v>87</v>
+        <v>212</v>
       </c>
       <c r="P38" s="2">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="Q38" s="2" t="s">
         <v>123</v>
@@ -3160,22 +3160,22 @@
         <v>103</v>
       </c>
       <c r="F39" s="2">
-        <v>41848</v>
+        <v>64994</v>
       </c>
       <c r="G39" s="2">
-        <v>68489</v>
+        <v>131023</v>
       </c>
       <c r="H39" s="2">
-        <v>67476</v>
+        <v>128787</v>
       </c>
       <c r="I39" s="2">
-        <v>13418</v>
+        <v>24237</v>
       </c>
       <c r="J39" s="2">
-        <v>1491</v>
+        <v>2984</v>
       </c>
       <c r="K39" s="2">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="L39" s="2">
         <v>0</v>
@@ -3184,13 +3184,13 @@
         <v>1</v>
       </c>
       <c r="N39" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O39" s="2">
-        <v>73</v>
+        <v>154</v>
       </c>
       <c r="P39" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Q39" s="2" t="s">
         <v>123</v>
@@ -3222,37 +3222,37 @@
         <v>104</v>
       </c>
       <c r="F40" s="2">
-        <v>41733</v>
+        <v>67120</v>
       </c>
       <c r="G40" s="2">
-        <v>65366</v>
+        <v>128790</v>
       </c>
       <c r="H40" s="2">
-        <v>64147</v>
+        <v>126169</v>
       </c>
       <c r="I40" s="2">
-        <v>19677</v>
+        <v>37739</v>
       </c>
       <c r="J40" s="2">
-        <v>3425</v>
+        <v>6755</v>
       </c>
       <c r="K40" s="2">
-        <v>69</v>
+        <v>145</v>
       </c>
       <c r="L40" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" s="2">
         <v>0</v>
       </c>
       <c r="N40" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="O40" s="2">
-        <v>100</v>
+        <v>169</v>
       </c>
       <c r="P40" s="2">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="Q40" s="2" t="s">
         <v>123</v>
@@ -3284,37 +3284,37 @@
         <v>105</v>
       </c>
       <c r="F41" s="2">
-        <v>83009</v>
+        <v>123228</v>
       </c>
       <c r="G41" s="2">
-        <v>138717</v>
+        <v>267262</v>
       </c>
       <c r="H41" s="2">
-        <v>136300</v>
+        <v>261860</v>
       </c>
       <c r="I41" s="2">
-        <v>28437</v>
+        <v>51757</v>
       </c>
       <c r="J41" s="2">
-        <v>2498</v>
+        <v>4811</v>
       </c>
       <c r="K41" s="2">
-        <v>60</v>
+        <v>106</v>
       </c>
       <c r="L41" s="2">
         <v>0</v>
       </c>
       <c r="M41" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N41" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O41" s="2">
-        <v>207</v>
+        <v>372</v>
       </c>
       <c r="P41" s="2">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="Q41" s="2" t="s">
         <v>123</v>
@@ -3346,22 +3346,22 @@
         <v>106</v>
       </c>
       <c r="F42" s="2">
-        <v>77782</v>
+        <v>111706</v>
       </c>
       <c r="G42" s="2">
-        <v>137972</v>
+        <v>264194</v>
       </c>
       <c r="H42" s="2">
-        <v>135295</v>
+        <v>258597</v>
       </c>
       <c r="I42" s="2">
-        <v>8876</v>
+        <v>17140</v>
       </c>
       <c r="J42" s="2">
-        <v>1512</v>
+        <v>3080</v>
       </c>
       <c r="K42" s="2">
-        <v>47</v>
+        <v>91</v>
       </c>
       <c r="L42" s="2">
         <v>0</v>
@@ -3370,13 +3370,13 @@
         <v>1</v>
       </c>
       <c r="N42" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="O42" s="2">
-        <v>217</v>
+        <v>388</v>
       </c>
       <c r="P42" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Q42" s="2" t="s">
         <v>123</v>
@@ -3408,37 +3408,37 @@
         <v>107</v>
       </c>
       <c r="F43" s="2">
-        <v>109743</v>
+        <v>153158</v>
       </c>
       <c r="G43" s="2">
-        <v>164023</v>
+        <v>279880</v>
       </c>
       <c r="H43" s="2">
-        <v>160593</v>
+        <v>273712</v>
       </c>
       <c r="I43" s="2">
-        <v>29062</v>
+        <v>50660</v>
       </c>
       <c r="J43" s="2">
-        <v>7193</v>
+        <v>12317</v>
       </c>
       <c r="K43" s="2">
-        <v>392</v>
+        <v>647</v>
       </c>
       <c r="L43" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M43" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N43" s="2">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="O43" s="2">
-        <v>355</v>
+        <v>599</v>
       </c>
       <c r="P43" s="2">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="Q43" s="2" t="s">
         <v>123</v>
@@ -3470,37 +3470,37 @@
         <v>108</v>
       </c>
       <c r="F44" s="2">
-        <v>84459</v>
+        <v>119603</v>
       </c>
       <c r="G44" s="2">
-        <v>140838</v>
+        <v>263068</v>
       </c>
       <c r="H44" s="2">
-        <v>137987</v>
+        <v>257276</v>
       </c>
       <c r="I44" s="2">
-        <v>14476</v>
+        <v>25318</v>
       </c>
       <c r="J44" s="2">
-        <v>2102</v>
+        <v>3785</v>
       </c>
       <c r="K44" s="2">
-        <v>52</v>
+        <v>101</v>
       </c>
       <c r="L44" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M44" s="2">
         <v>0</v>
       </c>
       <c r="N44" s="2">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="O44" s="2">
-        <v>167</v>
+        <v>325</v>
       </c>
       <c r="P44" s="2">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="Q44" s="2" t="s">
         <v>123</v>
@@ -3532,37 +3532,37 @@
         <v>109</v>
       </c>
       <c r="F45" s="2">
-        <v>122127</v>
+        <v>174215</v>
       </c>
       <c r="G45" s="2">
-        <v>201991</v>
+        <v>338157</v>
       </c>
       <c r="H45" s="2">
-        <v>195535</v>
+        <v>327713</v>
       </c>
       <c r="I45" s="2">
-        <v>64884</v>
+        <v>112262</v>
       </c>
       <c r="J45" s="2">
-        <v>34538</v>
+        <v>59798</v>
       </c>
       <c r="K45" s="2">
-        <v>3268</v>
+        <v>5254</v>
       </c>
       <c r="L45" s="2">
-        <v>522</v>
+        <v>819</v>
       </c>
       <c r="M45" s="2">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="N45" s="2">
-        <v>114</v>
+        <v>214</v>
       </c>
       <c r="O45" s="2">
-        <v>1393</v>
+        <v>2234</v>
       </c>
       <c r="P45" s="2">
-        <v>352</v>
+        <v>563</v>
       </c>
       <c r="Q45" s="2" t="s">
         <v>124</v>
@@ -3594,37 +3594,37 @@
         <v>110</v>
       </c>
       <c r="F46" s="2">
-        <v>98818</v>
+        <v>155742</v>
       </c>
       <c r="G46" s="2">
-        <v>160977</v>
+        <v>297659</v>
       </c>
       <c r="H46" s="2">
-        <v>155302</v>
+        <v>286839</v>
       </c>
       <c r="I46" s="2">
-        <v>29525</v>
+        <v>55753</v>
       </c>
       <c r="J46" s="2">
-        <v>11862</v>
+        <v>22176</v>
       </c>
       <c r="K46" s="2">
-        <v>1379</v>
+        <v>2502</v>
       </c>
       <c r="L46" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M46" s="2">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="N46" s="2">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="O46" s="2">
-        <v>520</v>
+        <v>915</v>
       </c>
       <c r="P46" s="2">
-        <v>85</v>
+        <v>161</v>
       </c>
       <c r="Q46" s="2" t="s">
         <v>124</v>

--- a/data/July.xlsx
+++ b/data/July.xlsx
@@ -1,11 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{185E1D0B-DD4E-4325-8062-CD81B31DBF47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr filterPrivacy="true" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -15,31 +14,34 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>ผู้สร้าง</author>
+    <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="F1" authorId="0">
       <text>
         <r>
           <rPr>
+            <rFont val="Arial"/>
+            <color/>
             <sz val="12"/>
-            <rFont val="Arial"/>
           </rPr>
-          <t>This is a reach-based metric. Reach-based metrics are de-duplicated metrics so you might see different numbers based on the level at which you are viewing data.</t>
+          <t xml:space="preserve">This is a reach-based metric. Reach-based metrics are de-duplicated metrics so you might see different numbers based on the level at which you are viewing data.</t>
         </r>
         <r>
           <rPr>
+            <rFont val="Arial"/>
+            <color/>
             <sz val="12"/>
-            <rFont val="Arial"/>
           </rPr>
           <t xml:space="preserve">     </t>
         </r>
         <r>
           <rPr>
+            <rFont val="Arial"/>
+            <color/>
             <sz val="12"/>
-            <rFont val="Arial"/>
           </rPr>
           <t xml:space="preserve">     </t>
         </r>
@@ -50,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="134">
   <si>
     <t>Ad name</t>
   </si>
@@ -190,12 +192,18 @@
     <t>KOLs-OLE CH -ตามหาทองนพคุณ</t>
   </si>
   <si>
+    <t>Total of 45 results</t>
+  </si>
+  <si>
     <t>Primary status</t>
   </si>
   <si>
     <t>Active</t>
   </si>
   <si>
+    <t>Ended</t>
+  </si>
+  <si>
     <t>-</t>
   </si>
   <si>
@@ -205,6 +213,9 @@
     <t>--</t>
   </si>
   <si>
+    <t>Ad completed; Out of ad group budget</t>
+  </si>
+  <si>
     <t>Campaign name</t>
   </si>
   <si>
@@ -250,139 +261,139 @@
     <t>Spend</t>
   </si>
   <si>
-    <t>872.79</t>
-  </si>
-  <si>
-    <t>878.84</t>
-  </si>
-  <si>
-    <t>851.56</t>
-  </si>
-  <si>
-    <t>866.57</t>
-  </si>
-  <si>
-    <t>850.58</t>
-  </si>
-  <si>
-    <t>822.81</t>
-  </si>
-  <si>
-    <t>861.43</t>
-  </si>
-  <si>
-    <t>868.01</t>
-  </si>
-  <si>
-    <t>868.29</t>
-  </si>
-  <si>
-    <t>889.52</t>
-  </si>
-  <si>
-    <t>870.89</t>
-  </si>
-  <si>
-    <t>865.20</t>
-  </si>
-  <si>
-    <t>839.55</t>
-  </si>
-  <si>
-    <t>854.87</t>
-  </si>
-  <si>
-    <t>849.10</t>
-  </si>
-  <si>
-    <t>785.84</t>
-  </si>
-  <si>
-    <t>906.74</t>
-  </si>
-  <si>
-    <t>887.07</t>
-  </si>
-  <si>
-    <t>888.87</t>
-  </si>
-  <si>
-    <t>763.52</t>
-  </si>
-  <si>
-    <t>668.87</t>
-  </si>
-  <si>
-    <t>909.36</t>
-  </si>
-  <si>
-    <t>896.67</t>
-  </si>
-  <si>
-    <t>889.24</t>
-  </si>
-  <si>
-    <t>845.50</t>
-  </si>
-  <si>
-    <t>901.79</t>
-  </si>
-  <si>
-    <t>733.85</t>
-  </si>
-  <si>
-    <t>695.54</t>
-  </si>
-  <si>
-    <t>1701.09</t>
-  </si>
-  <si>
-    <t>1685.32</t>
-  </si>
-  <si>
-    <t>1633.73</t>
-  </si>
-  <si>
-    <t>1613.20</t>
-  </si>
-  <si>
-    <t>1674.89</t>
-  </si>
-  <si>
-    <t>1697.22</t>
-  </si>
-  <si>
-    <t>1673.65</t>
-  </si>
-  <si>
-    <t>1745.65</t>
-  </si>
-  <si>
-    <t>1721.80</t>
-  </si>
-  <si>
-    <t>1738.31</t>
-  </si>
-  <si>
-    <t>1714.83</t>
-  </si>
-  <si>
-    <t>3395.99</t>
-  </si>
-  <si>
-    <t>3366.22</t>
-  </si>
-  <si>
-    <t>3198.26</t>
-  </si>
-  <si>
-    <t>3454.26</t>
-  </si>
-  <si>
-    <t>3457.24</t>
-  </si>
-  <si>
-    <t>3514.04</t>
+    <t>1601.48</t>
+  </si>
+  <si>
+    <t>1588.40</t>
+  </si>
+  <si>
+    <t>1582.71</t>
+  </si>
+  <si>
+    <t>1588.25</t>
+  </si>
+  <si>
+    <t>1577.98</t>
+  </si>
+  <si>
+    <t>1528.15</t>
+  </si>
+  <si>
+    <t>1588.75</t>
+  </si>
+  <si>
+    <t>1594.65</t>
+  </si>
+  <si>
+    <t>1582.54</t>
+  </si>
+  <si>
+    <t>1612.54</t>
+  </si>
+  <si>
+    <t>1600.51</t>
+  </si>
+  <si>
+    <t>1586.93</t>
+  </si>
+  <si>
+    <t>1563.67</t>
+  </si>
+  <si>
+    <t>1588.74</t>
+  </si>
+  <si>
+    <t>1577.19</t>
+  </si>
+  <si>
+    <t>1505.92</t>
+  </si>
+  <si>
+    <t>1628.47</t>
+  </si>
+  <si>
+    <t>1601.52</t>
+  </si>
+  <si>
+    <t>1590.33</t>
+  </si>
+  <si>
+    <t>1469.01</t>
+  </si>
+  <si>
+    <t>1433.00</t>
+  </si>
+  <si>
+    <t>1618.59</t>
+  </si>
+  <si>
+    <t>1629.38</t>
+  </si>
+  <si>
+    <t>1621.87</t>
+  </si>
+  <si>
+    <t>1564.99</t>
+  </si>
+  <si>
+    <t>1640.27</t>
+  </si>
+  <si>
+    <t>1522.84</t>
+  </si>
+  <si>
+    <t>1444.07</t>
+  </si>
+  <si>
+    <t>2772.62</t>
+  </si>
+  <si>
+    <t>2755.48</t>
+  </si>
+  <si>
+    <t>2707.49</t>
+  </si>
+  <si>
+    <t>2702.67</t>
+  </si>
+  <si>
+    <t>2749.11</t>
+  </si>
+  <si>
+    <t>2778.75</t>
+  </si>
+  <si>
+    <t>2738.18</t>
+  </si>
+  <si>
+    <t>2853.13</t>
+  </si>
+  <si>
+    <t>2805.46</t>
+  </si>
+  <si>
+    <t>2828.79</t>
+  </si>
+  <si>
+    <t>2816.08</t>
+  </si>
+  <si>
+    <t>5565.84</t>
+  </si>
+  <si>
+    <t>5463.26</t>
+  </si>
+  <si>
+    <t>5367.48</t>
+  </si>
+  <si>
+    <t>5556.20</t>
+  </si>
+  <si>
+    <t>5000.00</t>
+  </si>
+  <si>
+    <t>106493.29</t>
   </si>
   <si>
     <t>Reach</t>
@@ -448,8 +459,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -457,19 +468,17 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
+      <b val="1"/>
       <sz val="12"/>
+      <color/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
+      <color/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="2">
@@ -507,140 +516,136 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
+      <alignment/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="44546A"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="ED7D31"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="FFC000"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4472C4"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="70AD47"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0563C1"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="954F72"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
+<theme xmlns="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+  <themeElements>
+    <clrScheme name="Office">
+      <dk1>
+        <sysClr val="windowText" lastClr="000000"/>
+      </dk1>
+      <lt1>
+        <sysClr val="window" lastClr="FFFFFF"/>
+      </lt1>
+      <dk2>
+        <srgbClr val="44546A"/>
+      </dk2>
+      <lt2>
+        <srgbClr val="E7E6E6"/>
+      </lt2>
+      <accent1>
+        <srgbClr val="5B9BD5"/>
+      </accent1>
+      <accent2>
+        <srgbClr val="ED7D31"/>
+      </accent2>
+      <accent3>
+        <srgbClr val="A5A5A5"/>
+      </accent3>
+      <accent4>
+        <srgbClr val="FFC000"/>
+      </accent4>
+      <accent5>
+        <srgbClr val="4472C4"/>
+      </accent5>
+      <accent6>
+        <srgbClr val="70AD47"/>
+      </accent6>
+      <hlink>
+        <srgbClr val="0563C1"/>
+      </hlink>
+      <folHlink>
+        <srgbClr val="954F72"/>
+      </folHlink>
+    </clrScheme>
+    <fontScheme name="Office">
+      <majorFont>
+        <latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <ea typeface=""/>
+        <cs typeface=""/>
+        <font script="Jpan" typeface="游ゴシック Light"/>
+        <font script="Hang" typeface="맑은 고딕"/>
+        <font script="Hans" typeface="等线 Light"/>
+        <font script="Hant" typeface="新細明體"/>
+        <font script="Arab" typeface="Times New Roman"/>
+        <font script="Hebr" typeface="Times New Roman"/>
+        <font script="Thai" typeface="Tahoma"/>
+        <font script="Ethi" typeface="Nyala"/>
+        <font script="Beng" typeface="Vrinda"/>
+        <font script="Gujr" typeface="Shruti"/>
+        <font script="Khmr" typeface="MoolBoran"/>
+        <font script="Knda" typeface="Tunga"/>
+        <font script="Guru" typeface="Raavi"/>
+        <font script="Cans" typeface="Euphemia"/>
+        <font script="Cher" typeface="Plantagenet Cherokee"/>
+        <font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <font script="Tibt" typeface="Microsoft Himalaya"/>
+        <font script="Thaa" typeface="MV Boli"/>
+        <font script="Deva" typeface="Mangal"/>
+        <font script="Telu" typeface="Gautami"/>
+        <font script="Taml" typeface="Latha"/>
+        <font script="Syrc" typeface="Estrangelo Edessa"/>
+        <font script="Orya" typeface="Kalinga"/>
+        <font script="Mlym" typeface="Kartika"/>
+        <font script="Laoo" typeface="DokChampa"/>
+        <font script="Sinh" typeface="Iskoola Pota"/>
+        <font script="Mong" typeface="Mongolian Baiti"/>
+        <font script="Viet" typeface="Times New Roman"/>
+        <font script="Uigh" typeface="Microsoft Uighur"/>
+        <font script="Geor" typeface="Sylfaen"/>
+      </majorFont>
+      <minorFont>
+        <latin typeface="Calibri" panose="020F0502020204030204"/>
+        <ea typeface=""/>
+        <cs typeface=""/>
+        <font script="Jpan" typeface="游ゴシック"/>
+        <font script="Hang" typeface="맑은 고딕"/>
+        <font script="Hans" typeface="等线"/>
+        <font script="Hant" typeface="新細明體"/>
+        <font script="Arab" typeface="Arial"/>
+        <font script="Hebr" typeface="Arial"/>
+        <font script="Thai" typeface="Tahoma"/>
+        <font script="Ethi" typeface="Nyala"/>
+        <font script="Beng" typeface="Vrinda"/>
+        <font script="Gujr" typeface="Shruti"/>
+        <font script="Khmr" typeface="DaunPenh"/>
+        <font script="Knda" typeface="Tunga"/>
+        <font script="Guru" typeface="Raavi"/>
+        <font script="Cans" typeface="Euphemia"/>
+        <font script="Cher" typeface="Plantagenet Cherokee"/>
+        <font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <font script="Tibt" typeface="Microsoft Himalaya"/>
+        <font script="Thaa" typeface="MV Boli"/>
+        <font script="Deva" typeface="Mangal"/>
+        <font script="Telu" typeface="Gautami"/>
+        <font script="Taml" typeface="Latha"/>
+        <font script="Syrc" typeface="Estrangelo Edessa"/>
+        <font script="Orya" typeface="Kalinga"/>
+        <font script="Mlym" typeface="Kartika"/>
+        <font script="Laoo" typeface="DokChampa"/>
+        <font script="Sinh" typeface="Iskoola Pota"/>
+        <font script="Mong" typeface="Mongolian Baiti"/>
+        <font script="Viet" typeface="Arial"/>
+        <font script="Uigh" typeface="Microsoft Uighur"/>
+        <font script="Geor" typeface="Sylfaen"/>
+      </minorFont>
+    </fontScheme>
+    <fmtScheme name="Office">
+      <fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -696,8 +701,8 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
+      </fillStyleLst>
+      <lnStyleLst>
         <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -719,8 +724,8 @@
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
+      </lnStyleLst>
+      <effectStyleLst>
         <a:effectStyle>
           <a:effectLst/>
         </a:effectStyle>
@@ -736,8 +741,8 @@
             </a:outerShdw>
           </a:effectLst>
         </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
+      </effectStyleLst>
+      <bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -774,114 +779,114 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
+      </bgFillStyleLst>
+    </fmtScheme>
+  </themeElements>
+  <objectDefaults/>
+  <extraClrSchemeLst/>
+</theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T46"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F2" s="2">
-        <v>59501</v>
+        <v>98035</v>
       </c>
       <c r="G2" s="2">
-        <v>72611</v>
+        <v>133934</v>
       </c>
       <c r="H2" s="2">
-        <v>71319</v>
+        <v>131600</v>
       </c>
       <c r="I2" s="2">
-        <v>12662</v>
+        <v>23155</v>
       </c>
       <c r="J2" s="2">
-        <v>2380</v>
+        <v>4303</v>
       </c>
       <c r="K2" s="2">
-        <v>66</v>
+        <v>117</v>
       </c>
       <c r="L2" s="2">
         <v>1</v>
@@ -890,60 +895,60 @@
         <v>0</v>
       </c>
       <c r="N2" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O2" s="2">
-        <v>109</v>
+        <v>185</v>
       </c>
       <c r="P2" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F3" s="2">
-        <v>49166</v>
+        <v>73894</v>
       </c>
       <c r="G3" s="2">
-        <v>68199</v>
+        <v>120456</v>
       </c>
       <c r="H3" s="2">
-        <v>66890</v>
+        <v>118202</v>
       </c>
       <c r="I3" s="2">
-        <v>8546</v>
+        <v>15405</v>
       </c>
       <c r="J3" s="2">
-        <v>2040</v>
+        <v>3815</v>
       </c>
       <c r="K3" s="2">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="L3" s="2">
         <v>0</v>
@@ -952,60 +957,60 @@
         <v>2</v>
       </c>
       <c r="N3" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="O3" s="2">
-        <v>95</v>
+        <v>173</v>
       </c>
       <c r="P3" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F4" s="2">
-        <v>48574</v>
+        <v>75950</v>
       </c>
       <c r="G4" s="2">
-        <v>66733</v>
+        <v>125330</v>
       </c>
       <c r="H4" s="2">
-        <v>65221</v>
+        <v>122620</v>
       </c>
       <c r="I4" s="2">
-        <v>9383</v>
+        <v>17064</v>
       </c>
       <c r="J4" s="2">
-        <v>1489</v>
+        <v>2751</v>
       </c>
       <c r="K4" s="2">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="L4" s="2">
         <v>0</v>
@@ -1014,60 +1019,60 @@
         <v>0</v>
       </c>
       <c r="N4" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O4" s="2">
-        <v>91</v>
+        <v>159</v>
       </c>
       <c r="P4" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F5" s="2">
-        <v>49677</v>
+        <v>74358</v>
       </c>
       <c r="G5" s="2">
-        <v>66829</v>
+        <v>116353</v>
       </c>
       <c r="H5" s="2">
-        <v>65479</v>
+        <v>113992</v>
       </c>
       <c r="I5" s="2">
-        <v>34281</v>
+        <v>56945</v>
       </c>
       <c r="J5" s="2">
-        <v>9447</v>
+        <v>15674</v>
       </c>
       <c r="K5" s="2">
-        <v>93</v>
+        <v>158</v>
       </c>
       <c r="L5" s="2">
         <v>3</v>
@@ -1076,122 +1081,122 @@
         <v>1</v>
       </c>
       <c r="N5" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="O5" s="2">
-        <v>127</v>
+        <v>192</v>
       </c>
       <c r="P5" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F6" s="2">
-        <v>49182</v>
+        <v>74183</v>
       </c>
       <c r="G6" s="2">
-        <v>66791</v>
+        <v>118646</v>
       </c>
       <c r="H6" s="2">
-        <v>65420</v>
+        <v>116271</v>
       </c>
       <c r="I6" s="2">
-        <v>9884</v>
+        <v>16653</v>
       </c>
       <c r="J6" s="2">
-        <v>2448</v>
+        <v>4169</v>
       </c>
       <c r="K6" s="2">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="L6" s="2">
         <v>0</v>
       </c>
       <c r="M6" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O6" s="2">
-        <v>117</v>
+        <v>204</v>
       </c>
       <c r="P6" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F7" s="2">
-        <v>48421</v>
+        <v>73727</v>
       </c>
       <c r="G7" s="2">
-        <v>65751</v>
+        <v>123052</v>
       </c>
       <c r="H7" s="2">
-        <v>64411</v>
+        <v>120708</v>
       </c>
       <c r="I7" s="2">
-        <v>5883</v>
+        <v>10688</v>
       </c>
       <c r="J7" s="2">
-        <v>1049</v>
+        <v>2003</v>
       </c>
       <c r="K7" s="2">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="L7" s="2">
         <v>0</v>
@@ -1200,60 +1205,60 @@
         <v>0</v>
       </c>
       <c r="N7" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O7" s="2">
-        <v>94</v>
+        <v>192</v>
       </c>
       <c r="P7" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F8" s="2">
-        <v>49489</v>
+        <v>77119</v>
       </c>
       <c r="G8" s="2">
-        <v>66767</v>
+        <v>118871</v>
       </c>
       <c r="H8" s="2">
-        <v>65381</v>
+        <v>116422</v>
       </c>
       <c r="I8" s="2">
-        <v>5942</v>
+        <v>10591</v>
       </c>
       <c r="J8" s="2">
-        <v>993</v>
+        <v>1777</v>
       </c>
       <c r="K8" s="2">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="L8" s="2">
         <v>0</v>
@@ -1262,60 +1267,60 @@
         <v>0</v>
       </c>
       <c r="N8" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O8" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="P8" s="2">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F9" s="2">
-        <v>47498</v>
+        <v>72209</v>
       </c>
       <c r="G9" s="2">
-        <v>66062</v>
+        <v>122934</v>
       </c>
       <c r="H9" s="2">
-        <v>64708</v>
+        <v>120578</v>
       </c>
       <c r="I9" s="2">
-        <v>7995</v>
+        <v>14348</v>
       </c>
       <c r="J9" s="2">
-        <v>1433</v>
+        <v>2604</v>
       </c>
       <c r="K9" s="2">
-        <v>57</v>
+        <v>97</v>
       </c>
       <c r="L9" s="2">
         <v>0</v>
@@ -1324,60 +1329,60 @@
         <v>0</v>
       </c>
       <c r="N9" s="2">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="O9" s="2">
-        <v>100</v>
+        <v>178</v>
       </c>
       <c r="P9" s="2">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F10" s="2">
-        <v>50754</v>
+        <v>79869</v>
       </c>
       <c r="G10" s="2">
-        <v>68291</v>
+        <v>125236</v>
       </c>
       <c r="H10" s="2">
-        <v>66962</v>
+        <v>122713</v>
       </c>
       <c r="I10" s="2">
-        <v>5496</v>
+        <v>10042</v>
       </c>
       <c r="J10" s="2">
-        <v>1044</v>
+        <v>1992</v>
       </c>
       <c r="K10" s="2">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="L10" s="2">
         <v>0</v>
@@ -1386,60 +1391,60 @@
         <v>2</v>
       </c>
       <c r="N10" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="O10" s="2">
-        <v>123</v>
+        <v>222</v>
       </c>
       <c r="P10" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F11" s="2">
-        <v>48806</v>
+        <v>71315</v>
       </c>
       <c r="G11" s="2">
-        <v>68984</v>
+        <v>120686</v>
       </c>
       <c r="H11" s="2">
-        <v>67778</v>
+        <v>118650</v>
       </c>
       <c r="I11" s="2">
-        <v>5767</v>
+        <v>9653</v>
       </c>
       <c r="J11" s="2">
-        <v>1329</v>
+        <v>2186</v>
       </c>
       <c r="K11" s="2">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="L11" s="2">
         <v>1</v>
@@ -1448,60 +1453,60 @@
         <v>0</v>
       </c>
       <c r="N11" s="2">
+        <v>9</v>
+      </c>
+      <c r="O11" s="2">
+        <v>192</v>
+      </c>
+      <c r="P11" s="2">
         <v>6</v>
       </c>
-      <c r="O11" s="2">
-        <v>113</v>
-      </c>
-      <c r="P11" s="2">
-        <v>2</v>
-      </c>
       <c r="Q11" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F12" s="2">
-        <v>49943</v>
+        <v>73382</v>
       </c>
       <c r="G12" s="2">
-        <v>67791</v>
+        <v>119578</v>
       </c>
       <c r="H12" s="2">
-        <v>66671</v>
+        <v>117674</v>
       </c>
       <c r="I12" s="2">
-        <v>8610</v>
+        <v>14864</v>
       </c>
       <c r="J12" s="2">
-        <v>1805</v>
+        <v>3081</v>
       </c>
       <c r="K12" s="2">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="L12" s="2">
         <v>0</v>
@@ -1510,60 +1515,60 @@
         <v>0</v>
       </c>
       <c r="N12" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O12" s="2">
-        <v>110</v>
+        <v>198</v>
       </c>
       <c r="P12" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F13" s="2">
-        <v>48340</v>
+        <v>74187</v>
       </c>
       <c r="G13" s="2">
-        <v>67010</v>
+        <v>123989</v>
       </c>
       <c r="H13" s="2">
-        <v>65780</v>
+        <v>121646</v>
       </c>
       <c r="I13" s="2">
-        <v>6642</v>
+        <v>11888</v>
       </c>
       <c r="J13" s="2">
-        <v>1552</v>
+        <v>2709</v>
       </c>
       <c r="K13" s="2">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="L13" s="2">
         <v>0</v>
@@ -1572,60 +1577,60 @@
         <v>1</v>
       </c>
       <c r="N13" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O13" s="2">
-        <v>107</v>
+        <v>179</v>
       </c>
       <c r="P13" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F14" s="2">
-        <v>47705</v>
+        <v>70216</v>
       </c>
       <c r="G14" s="2">
-        <v>66177</v>
+        <v>118865</v>
       </c>
       <c r="H14" s="2">
-        <v>64917</v>
+        <v>116640</v>
       </c>
       <c r="I14" s="2">
-        <v>17166</v>
+        <v>30450</v>
       </c>
       <c r="J14" s="2">
-        <v>6954</v>
+        <v>12431</v>
       </c>
       <c r="K14" s="2">
-        <v>83</v>
+        <v>163</v>
       </c>
       <c r="L14" s="2">
         <v>0</v>
@@ -1634,184 +1639,184 @@
         <v>1</v>
       </c>
       <c r="N14" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O14" s="2">
-        <v>122</v>
+        <v>217</v>
       </c>
       <c r="P14" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F15" s="2">
-        <v>46419</v>
+        <v>70059</v>
       </c>
       <c r="G15" s="2">
-        <v>64588</v>
+        <v>115609</v>
       </c>
       <c r="H15" s="2">
-        <v>63234</v>
+        <v>113128</v>
       </c>
       <c r="I15" s="2">
-        <v>12246</v>
+        <v>21912</v>
       </c>
       <c r="J15" s="2">
-        <v>2152</v>
+        <v>3920</v>
       </c>
       <c r="K15" s="2">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="L15" s="2">
         <v>0</v>
       </c>
       <c r="M15" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N15" s="2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O15" s="2">
-        <v>88</v>
+        <v>174</v>
       </c>
       <c r="P15" s="2">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F16" s="2">
-        <v>45806</v>
+        <v>70922</v>
       </c>
       <c r="G16" s="2">
-        <v>63981</v>
+        <v>119538</v>
       </c>
       <c r="H16" s="2">
-        <v>62517</v>
+        <v>116771</v>
       </c>
       <c r="I16" s="2">
-        <v>11257</v>
+        <v>20266</v>
       </c>
       <c r="J16" s="2">
-        <v>2819</v>
+        <v>5025</v>
       </c>
       <c r="K16" s="2">
-        <v>60</v>
+        <v>109</v>
       </c>
       <c r="L16" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M16" s="2">
         <v>1</v>
       </c>
       <c r="N16" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="O16" s="2">
-        <v>113</v>
+        <v>200</v>
       </c>
       <c r="P16" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F17" s="2">
-        <v>45036</v>
+        <v>70210</v>
       </c>
       <c r="G17" s="2">
-        <v>62616</v>
+        <v>120830</v>
       </c>
       <c r="H17" s="2">
-        <v>61426</v>
+        <v>118404</v>
       </c>
       <c r="I17" s="2">
-        <v>7446</v>
+        <v>13979</v>
       </c>
       <c r="J17" s="2">
-        <v>1555</v>
+        <v>2962</v>
       </c>
       <c r="K17" s="2">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="L17" s="2">
         <v>2</v>
@@ -1820,60 +1825,60 @@
         <v>0</v>
       </c>
       <c r="N17" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O17" s="2">
-        <v>89</v>
+        <v>191</v>
       </c>
       <c r="P17" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F18" s="2">
-        <v>55238</v>
+        <v>88692</v>
       </c>
       <c r="G18" s="2">
-        <v>71384</v>
+        <v>128829</v>
       </c>
       <c r="H18" s="2">
-        <v>69843</v>
+        <v>126151</v>
       </c>
       <c r="I18" s="2">
-        <v>22713</v>
+        <v>39795</v>
       </c>
       <c r="J18" s="2">
-        <v>4763</v>
+        <v>8483</v>
       </c>
       <c r="K18" s="2">
-        <v>55</v>
+        <v>111</v>
       </c>
       <c r="L18" s="2">
         <v>1</v>
@@ -1882,122 +1887,122 @@
         <v>0</v>
       </c>
       <c r="N18" s="2">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="O18" s="2">
-        <v>72</v>
+        <v>146</v>
       </c>
       <c r="P18" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F19" s="2">
-        <v>54747</v>
+        <v>87056</v>
       </c>
       <c r="G19" s="2">
-        <v>70691</v>
+        <v>128303</v>
       </c>
       <c r="H19" s="2">
-        <v>69180</v>
+        <v>125755</v>
       </c>
       <c r="I19" s="2">
-        <v>12950</v>
+        <v>23170</v>
       </c>
       <c r="J19" s="2">
-        <v>2134</v>
+        <v>3828</v>
       </c>
       <c r="K19" s="2">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="L19" s="2">
         <v>0</v>
       </c>
       <c r="M19" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N19" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O19" s="2">
-        <v>98</v>
+        <v>176</v>
       </c>
       <c r="P19" s="2">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="20">
       <c r="A20" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F20" s="2">
-        <v>55282</v>
+        <v>87808</v>
       </c>
       <c r="G20" s="2">
-        <v>71677</v>
+        <v>129033</v>
       </c>
       <c r="H20" s="2">
-        <v>70357</v>
+        <v>126448</v>
       </c>
       <c r="I20" s="2">
-        <v>7711</v>
+        <v>13452</v>
       </c>
       <c r="J20" s="2">
-        <v>1282</v>
+        <v>2338</v>
       </c>
       <c r="K20" s="2">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="L20" s="2">
         <v>0</v>
@@ -2006,122 +2011,122 @@
         <v>1</v>
       </c>
       <c r="N20" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O20" s="2">
-        <v>91</v>
+        <v>150</v>
       </c>
       <c r="P20" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="21">
       <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F21" s="2">
-        <v>94919</v>
+        <v>167152</v>
       </c>
       <c r="G21" s="2">
-        <v>121866</v>
+        <v>239732</v>
       </c>
       <c r="H21" s="2">
-        <v>117444</v>
+        <v>230796</v>
       </c>
       <c r="I21" s="2">
-        <v>30275</v>
+        <v>60092</v>
       </c>
       <c r="J21" s="2">
-        <v>5793</v>
+        <v>12149</v>
       </c>
       <c r="K21" s="2">
-        <v>134</v>
+        <v>296</v>
       </c>
       <c r="L21" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M21" s="2">
         <v>2</v>
       </c>
       <c r="N21" s="2">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="O21" s="2">
-        <v>187</v>
+        <v>390</v>
       </c>
       <c r="P21" s="2">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="22">
       <c r="A22" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F22" s="2">
-        <v>67441</v>
+        <v>126154</v>
       </c>
       <c r="G22" s="2">
-        <v>85122</v>
+        <v>186837</v>
       </c>
       <c r="H22" s="2">
-        <v>81679</v>
+        <v>179333</v>
       </c>
       <c r="I22" s="2">
-        <v>11446</v>
+        <v>24787</v>
       </c>
       <c r="J22" s="2">
-        <v>2071</v>
+        <v>4720</v>
       </c>
       <c r="K22" s="2">
-        <v>91</v>
+        <v>171</v>
       </c>
       <c r="L22" s="2">
         <v>0</v>
@@ -2130,246 +2135,246 @@
         <v>2</v>
       </c>
       <c r="N22" s="2">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="O22" s="2">
-        <v>101</v>
+        <v>243</v>
       </c>
       <c r="P22" s="2">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T22" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="23">
       <c r="A23" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F23" s="2">
-        <v>57074</v>
+        <v>92406</v>
       </c>
       <c r="G23" s="2">
-        <v>72931</v>
+        <v>129917</v>
       </c>
       <c r="H23" s="2">
-        <v>71517</v>
+        <v>127413</v>
       </c>
       <c r="I23" s="2">
-        <v>9939</v>
+        <v>17468</v>
       </c>
       <c r="J23" s="2">
-        <v>2511</v>
+        <v>4503</v>
       </c>
       <c r="K23" s="2">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="L23" s="2">
         <v>0</v>
       </c>
       <c r="M23" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O23" s="2">
-        <v>77</v>
+        <v>168</v>
       </c>
       <c r="P23" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="R23" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T23" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="24">
       <c r="A24" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F24" s="2">
-        <v>55187</v>
+        <v>90007</v>
       </c>
       <c r="G24" s="2">
-        <v>71420</v>
+        <v>129929</v>
       </c>
       <c r="H24" s="2">
-        <v>69708</v>
+        <v>126998</v>
       </c>
       <c r="I24" s="2">
-        <v>5875</v>
+        <v>10252</v>
       </c>
       <c r="J24" s="2">
-        <v>1036</v>
+        <v>1820</v>
       </c>
       <c r="K24" s="2">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="L24" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" s="2">
         <v>1</v>
       </c>
       <c r="N24" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O24" s="2">
-        <v>68</v>
+        <v>131</v>
       </c>
       <c r="P24" s="2">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T24" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="25">
       <c r="A25" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F25" s="2">
-        <v>54479</v>
+        <v>82759</v>
       </c>
       <c r="G25" s="2">
-        <v>70326</v>
+        <v>120941</v>
       </c>
       <c r="H25" s="2">
-        <v>68947</v>
+        <v>118641</v>
       </c>
       <c r="I25" s="2">
-        <v>7280</v>
+        <v>12373</v>
       </c>
       <c r="J25" s="2">
-        <v>1302</v>
+        <v>2296</v>
       </c>
       <c r="K25" s="2">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="L25" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" s="2">
         <v>1</v>
       </c>
       <c r="N25" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O25" s="2">
-        <v>91</v>
+        <v>157</v>
       </c>
       <c r="P25" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T25" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="26">
       <c r="A26" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F26" s="2">
-        <v>55902</v>
+        <v>93519</v>
       </c>
       <c r="G26" s="2">
-        <v>68656</v>
+        <v>127231</v>
       </c>
       <c r="H26" s="2">
-        <v>67255</v>
+        <v>124578</v>
       </c>
       <c r="I26" s="2">
-        <v>13328</v>
+        <v>25286</v>
       </c>
       <c r="J26" s="2">
-        <v>1634</v>
+        <v>2956</v>
       </c>
       <c r="K26" s="2">
-        <v>49</v>
+        <v>102</v>
       </c>
       <c r="L26" s="2">
         <v>2</v>
@@ -2378,60 +2383,60 @@
         <v>0</v>
       </c>
       <c r="N26" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O26" s="2">
-        <v>115</v>
+        <v>208</v>
       </c>
       <c r="P26" s="2">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="S26" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T26" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="27">
       <c r="A27" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F27" s="2">
-        <v>56081</v>
+        <v>87522</v>
       </c>
       <c r="G27" s="2">
-        <v>71125</v>
+        <v>122131</v>
       </c>
       <c r="H27" s="2">
-        <v>69504</v>
+        <v>119283</v>
       </c>
       <c r="I27" s="2">
-        <v>7346</v>
+        <v>12368</v>
       </c>
       <c r="J27" s="2">
-        <v>1521</v>
+        <v>2531</v>
       </c>
       <c r="K27" s="2">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="L27" s="2">
         <v>1</v>
@@ -2440,60 +2445,60 @@
         <v>0</v>
       </c>
       <c r="N27" s="2">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="O27" s="2">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="P27" s="2">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="R27" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="S27" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T27" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="28">
       <c r="A28" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F28" s="2">
-        <v>47163</v>
+        <v>86677</v>
       </c>
       <c r="G28" s="2">
-        <v>58237</v>
+        <v>120594</v>
       </c>
       <c r="H28" s="2">
-        <v>57132</v>
+        <v>118289</v>
       </c>
       <c r="I28" s="2">
-        <v>11938</v>
+        <v>25411</v>
       </c>
       <c r="J28" s="2">
-        <v>2706</v>
+        <v>5742</v>
       </c>
       <c r="K28" s="2">
-        <v>65</v>
+        <v>128</v>
       </c>
       <c r="L28" s="2">
         <v>0</v>
@@ -2502,60 +2507,60 @@
         <v>1</v>
       </c>
       <c r="N28" s="2">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="O28" s="2">
-        <v>79</v>
+        <v>161</v>
       </c>
       <c r="P28" s="2">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="Q28" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="R28" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="S28" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T28" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="29">
       <c r="A29" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F29" s="2">
-        <v>74727</v>
+        <v>133541</v>
       </c>
       <c r="G29" s="2">
-        <v>92957</v>
+        <v>192733</v>
       </c>
       <c r="H29" s="2">
-        <v>89813</v>
+        <v>186012</v>
       </c>
       <c r="I29" s="2">
-        <v>13844</v>
+        <v>30117</v>
       </c>
       <c r="J29" s="2">
-        <v>2210</v>
+        <v>5171</v>
       </c>
       <c r="K29" s="2">
-        <v>109</v>
+        <v>196</v>
       </c>
       <c r="L29" s="2">
         <v>0</v>
@@ -2564,60 +2569,60 @@
         <v>0</v>
       </c>
       <c r="N29" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O29" s="2">
-        <v>177</v>
+        <v>351</v>
       </c>
       <c r="P29" s="2">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="R29" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="S29" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T29" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="30">
       <c r="A30" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F30" s="2">
-        <v>36854</v>
+        <v>44370</v>
       </c>
       <c r="G30" s="2">
-        <v>99345</v>
+        <v>154353</v>
       </c>
       <c r="H30" s="2">
-        <v>97533</v>
+        <v>151427</v>
       </c>
       <c r="I30" s="2">
-        <v>24903</v>
+        <v>35349</v>
       </c>
       <c r="J30" s="2">
-        <v>5894</v>
+        <v>8310</v>
       </c>
       <c r="K30" s="2">
-        <v>140</v>
+        <v>199</v>
       </c>
       <c r="L30" s="2">
         <v>3</v>
@@ -2626,184 +2631,184 @@
         <v>4</v>
       </c>
       <c r="N30" s="2">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="O30" s="2">
-        <v>199</v>
+        <v>289</v>
       </c>
       <c r="P30" s="2">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="Q30" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="R30" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="S30" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T30" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="31">
       <c r="A31" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F31" s="2">
-        <v>38640</v>
+        <v>48956</v>
       </c>
       <c r="G31" s="2">
-        <v>100520</v>
+        <v>165208</v>
       </c>
       <c r="H31" s="2">
-        <v>98661</v>
+        <v>162054</v>
       </c>
       <c r="I31" s="2">
-        <v>18781</v>
+        <v>29838</v>
       </c>
       <c r="J31" s="2">
-        <v>3768</v>
+        <v>5897</v>
       </c>
       <c r="K31" s="2">
-        <v>89</v>
+        <v>143</v>
       </c>
       <c r="L31" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" s="2">
         <v>1</v>
       </c>
       <c r="N31" s="2">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="O31" s="2">
-        <v>179</v>
+        <v>278</v>
       </c>
       <c r="P31" s="2">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="Q31" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="R31" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="S31" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T31" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="32" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="32">
       <c r="A32" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F32" s="2">
-        <v>37307</v>
+        <v>48698</v>
       </c>
       <c r="G32" s="2">
-        <v>93098</v>
+        <v>154831</v>
       </c>
       <c r="H32" s="2">
-        <v>91208</v>
+        <v>151625</v>
       </c>
       <c r="I32" s="2">
-        <v>12182</v>
+        <v>19245</v>
       </c>
       <c r="J32" s="2">
-        <v>2659</v>
+        <v>4175</v>
       </c>
       <c r="K32" s="2">
-        <v>65</v>
+        <v>119</v>
       </c>
       <c r="L32" s="2">
         <v>0</v>
       </c>
       <c r="M32" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N32" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="O32" s="2">
-        <v>187</v>
+        <v>303</v>
       </c>
       <c r="P32" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Q32" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="R32" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="S32" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T32" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="33" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="33">
       <c r="A33" s="2" t="s">
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F33" s="2">
-        <v>49585</v>
+        <v>65283</v>
       </c>
       <c r="G33" s="2">
-        <v>115684</v>
+        <v>192719</v>
       </c>
       <c r="H33" s="2">
-        <v>113342</v>
+        <v>188720</v>
       </c>
       <c r="I33" s="2">
-        <v>11388</v>
+        <v>18381</v>
       </c>
       <c r="J33" s="2">
-        <v>2409</v>
+        <v>3954</v>
       </c>
       <c r="K33" s="2">
-        <v>65</v>
+        <v>108</v>
       </c>
       <c r="L33" s="2">
         <v>0</v>
@@ -2812,122 +2817,122 @@
         <v>0</v>
       </c>
       <c r="N33" s="2">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="O33" s="2">
-        <v>169</v>
+        <v>301</v>
       </c>
       <c r="P33" s="2">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="Q33" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="R33" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="S33" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T33" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="34" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="34">
       <c r="A34" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E34" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F34" s="2">
+        <v>64488</v>
+      </c>
+      <c r="G34" s="2">
+        <v>199289</v>
+      </c>
+      <c r="H34" s="2">
+        <v>194744</v>
+      </c>
+      <c r="I34" s="2">
+        <v>12303</v>
+      </c>
+      <c r="J34" s="2">
+        <v>3241</v>
+      </c>
+      <c r="K34" s="2">
         <v>98</v>
       </c>
-      <c r="F34" s="2">
-        <v>49994</v>
-      </c>
-      <c r="G34" s="2">
-        <v>121755</v>
-      </c>
-      <c r="H34" s="2">
-        <v>118997</v>
-      </c>
-      <c r="I34" s="2">
-        <v>7628</v>
-      </c>
-      <c r="J34" s="2">
-        <v>2042</v>
-      </c>
-      <c r="K34" s="2">
-        <v>61</v>
-      </c>
       <c r="L34" s="2">
         <v>0</v>
       </c>
       <c r="M34" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N34" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O34" s="2">
-        <v>184</v>
+        <v>304</v>
       </c>
       <c r="P34" s="2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q34" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="R34" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="S34" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T34" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="35" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="35">
       <c r="A35" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F35" s="2">
-        <v>50217</v>
+        <v>67020</v>
       </c>
       <c r="G35" s="2">
-        <v>119552</v>
+        <v>195592</v>
       </c>
       <c r="H35" s="2">
-        <v>117195</v>
+        <v>191646</v>
       </c>
       <c r="I35" s="2">
-        <v>9276</v>
+        <v>15134</v>
       </c>
       <c r="J35" s="2">
-        <v>2226</v>
+        <v>3674</v>
       </c>
       <c r="K35" s="2">
-        <v>60</v>
+        <v>98</v>
       </c>
       <c r="L35" s="2">
         <v>0</v>
@@ -2936,60 +2941,60 @@
         <v>0</v>
       </c>
       <c r="N35" s="2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O35" s="2">
-        <v>218</v>
+        <v>321</v>
       </c>
       <c r="P35" s="2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q35" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="R35" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="S35" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T35" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="36" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="36">
       <c r="A36" s="2" t="s">
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F36" s="2">
-        <v>49890</v>
+        <v>65002</v>
       </c>
       <c r="G36" s="2">
-        <v>122408</v>
+        <v>199302</v>
       </c>
       <c r="H36" s="2">
-        <v>120063</v>
+        <v>195407</v>
       </c>
       <c r="I36" s="2">
-        <v>7698</v>
+        <v>12434</v>
       </c>
       <c r="J36" s="2">
-        <v>2039</v>
+        <v>3380</v>
       </c>
       <c r="K36" s="2">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="L36" s="2">
         <v>1</v>
@@ -2998,60 +3003,60 @@
         <v>0</v>
       </c>
       <c r="N36" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O36" s="2">
-        <v>241</v>
+        <v>387</v>
       </c>
       <c r="P36" s="2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Q36" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="R36" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="S36" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T36" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="37" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="37">
       <c r="A37" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F37" s="2">
-        <v>63268</v>
+        <v>81805</v>
       </c>
       <c r="G37" s="2">
-        <v>126554</v>
+        <v>192498</v>
       </c>
       <c r="H37" s="2">
-        <v>124351</v>
+        <v>189034</v>
       </c>
       <c r="I37" s="2">
-        <v>33753</v>
+        <v>50178</v>
       </c>
       <c r="J37" s="2">
-        <v>4348</v>
+        <v>6617</v>
       </c>
       <c r="K37" s="2">
-        <v>99</v>
+        <v>157</v>
       </c>
       <c r="L37" s="2">
         <v>0</v>
@@ -3060,246 +3065,246 @@
         <v>1</v>
       </c>
       <c r="N37" s="2">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="O37" s="2">
-        <v>164</v>
+        <v>253</v>
       </c>
       <c r="P37" s="2">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="Q37" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="R37" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="S37" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T37" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="38" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="38">
       <c r="A38" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F38" s="2">
-        <v>64534</v>
+        <v>87545</v>
       </c>
       <c r="G38" s="2">
-        <v>128514</v>
+        <v>207461</v>
       </c>
       <c r="H38" s="2">
-        <v>125979</v>
+        <v>203340</v>
       </c>
       <c r="I38" s="2">
-        <v>42561</v>
+        <v>66993</v>
       </c>
       <c r="J38" s="2">
-        <v>8228</v>
+        <v>13034</v>
       </c>
       <c r="K38" s="2">
-        <v>164</v>
+        <v>260</v>
       </c>
       <c r="L38" s="2">
         <v>2</v>
       </c>
       <c r="M38" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N38" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="O38" s="2">
-        <v>212</v>
+        <v>360</v>
       </c>
       <c r="P38" s="2">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="Q38" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="R38" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="S38" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T38" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="39" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="39">
       <c r="A39" s="2" t="s">
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F39" s="2">
-        <v>64994</v>
+        <v>86716</v>
       </c>
       <c r="G39" s="2">
-        <v>131023</v>
+        <v>211526</v>
       </c>
       <c r="H39" s="2">
-        <v>128787</v>
+        <v>207968</v>
       </c>
       <c r="I39" s="2">
-        <v>24237</v>
+        <v>38064</v>
       </c>
       <c r="J39" s="2">
-        <v>2984</v>
+        <v>4873</v>
       </c>
       <c r="K39" s="2">
-        <v>83</v>
+        <v>134</v>
       </c>
       <c r="L39" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M39" s="2">
         <v>1</v>
       </c>
       <c r="N39" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O39" s="2">
-        <v>154</v>
+        <v>242</v>
       </c>
       <c r="P39" s="2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Q39" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="R39" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="S39" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T39" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="40" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="40">
       <c r="A40" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F40" s="2">
-        <v>67120</v>
+        <v>93133</v>
       </c>
       <c r="G40" s="2">
-        <v>128790</v>
+        <v>209858</v>
       </c>
       <c r="H40" s="2">
-        <v>126169</v>
+        <v>205454</v>
       </c>
       <c r="I40" s="2">
-        <v>37739</v>
+        <v>59082</v>
       </c>
       <c r="J40" s="2">
-        <v>6755</v>
+        <v>10490</v>
       </c>
       <c r="K40" s="2">
-        <v>145</v>
+        <v>239</v>
       </c>
       <c r="L40" s="2">
         <v>1</v>
       </c>
       <c r="M40" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N40" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="O40" s="2">
-        <v>169</v>
+        <v>273</v>
       </c>
       <c r="P40" s="2">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="Q40" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="R40" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="S40" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T40" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="41" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="41">
       <c r="A41" s="2" t="s">
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F41" s="2">
-        <v>123228</v>
+        <v>162547</v>
       </c>
       <c r="G41" s="2">
-        <v>267262</v>
+        <v>436446</v>
       </c>
       <c r="H41" s="2">
-        <v>261860</v>
+        <v>427624</v>
       </c>
       <c r="I41" s="2">
-        <v>51757</v>
+        <v>80269</v>
       </c>
       <c r="J41" s="2">
-        <v>4811</v>
+        <v>7787</v>
       </c>
       <c r="K41" s="2">
-        <v>106</v>
+        <v>173</v>
       </c>
       <c r="L41" s="2">
         <v>0</v>
@@ -3308,184 +3313,184 @@
         <v>1</v>
       </c>
       <c r="N41" s="2">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="O41" s="2">
-        <v>372</v>
+        <v>572</v>
       </c>
       <c r="P41" s="2">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="Q41" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="R41" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="S41" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T41" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="42" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="42">
       <c r="A42" s="2" t="s">
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F42" s="2">
-        <v>111706</v>
+        <v>143231</v>
       </c>
       <c r="G42" s="2">
-        <v>264194</v>
+        <v>426819</v>
       </c>
       <c r="H42" s="2">
-        <v>258597</v>
+        <v>417651</v>
       </c>
       <c r="I42" s="2">
-        <v>17140</v>
+        <v>26821</v>
       </c>
       <c r="J42" s="2">
-        <v>3080</v>
+        <v>5037</v>
       </c>
       <c r="K42" s="2">
-        <v>91</v>
+        <v>135</v>
       </c>
       <c r="L42" s="2">
         <v>0</v>
       </c>
       <c r="M42" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N42" s="2">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="O42" s="2">
-        <v>388</v>
+        <v>597</v>
       </c>
       <c r="P42" s="2">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="Q42" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="R42" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="S42" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T42" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="43" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="43">
       <c r="A43" s="2" t="s">
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F43" s="2">
-        <v>153158</v>
+        <v>197032</v>
       </c>
       <c r="G43" s="2">
-        <v>279880</v>
+        <v>404517</v>
       </c>
       <c r="H43" s="2">
-        <v>273712</v>
+        <v>395159</v>
       </c>
       <c r="I43" s="2">
-        <v>50660</v>
+        <v>70160</v>
       </c>
       <c r="J43" s="2">
-        <v>12317</v>
+        <v>16819</v>
       </c>
       <c r="K43" s="2">
-        <v>647</v>
+        <v>860</v>
       </c>
       <c r="L43" s="2">
         <v>2</v>
       </c>
       <c r="M43" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N43" s="2">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="O43" s="2">
-        <v>599</v>
+        <v>815</v>
       </c>
       <c r="P43" s="2">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="Q43" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="R43" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="S43" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T43" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="44" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="44">
       <c r="A44" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F44" s="2">
-        <v>119603</v>
+        <v>151254</v>
       </c>
       <c r="G44" s="2">
-        <v>263068</v>
+        <v>396606</v>
       </c>
       <c r="H44" s="2">
-        <v>257276</v>
+        <v>387785</v>
       </c>
       <c r="I44" s="2">
-        <v>25318</v>
+        <v>37320</v>
       </c>
       <c r="J44" s="2">
-        <v>3785</v>
+        <v>5803</v>
       </c>
       <c r="K44" s="2">
-        <v>101</v>
+        <v>152</v>
       </c>
       <c r="L44" s="2">
         <v>2</v>
@@ -3494,153 +3499,214 @@
         <v>0</v>
       </c>
       <c r="N44" s="2">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="O44" s="2">
-        <v>325</v>
+        <v>473</v>
       </c>
       <c r="P44" s="2">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="Q44" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="R44" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="S44" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T44" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="45" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="45">
       <c r="A45" s="2" t="s">
         <v>44</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F45" s="2">
-        <v>174215</v>
+        <v>204106</v>
       </c>
       <c r="G45" s="2">
-        <v>338157</v>
+        <v>412731</v>
       </c>
       <c r="H45" s="2">
-        <v>327713</v>
+        <v>399630</v>
       </c>
       <c r="I45" s="2">
-        <v>112262</v>
+        <v>135058</v>
       </c>
       <c r="J45" s="2">
-        <v>59798</v>
+        <v>71176</v>
       </c>
       <c r="K45" s="2">
-        <v>5254</v>
+        <v>6035</v>
       </c>
       <c r="L45" s="2">
-        <v>819</v>
+        <v>930</v>
       </c>
       <c r="M45" s="2">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="N45" s="2">
-        <v>214</v>
+        <v>252</v>
       </c>
       <c r="O45" s="2">
-        <v>2234</v>
+        <v>2614</v>
       </c>
       <c r="P45" s="2">
-        <v>563</v>
+        <v>671</v>
       </c>
       <c r="Q45" s="2" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="R45" s="2" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="S45" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T45" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="46" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="46">
       <c r="A46" s="2" t="s">
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F46" s="2">
-        <v>155742</v>
+        <v>194555</v>
       </c>
       <c r="G46" s="2">
-        <v>297659</v>
+        <v>410904</v>
       </c>
       <c r="H46" s="2">
-        <v>286839</v>
+        <v>395481</v>
       </c>
       <c r="I46" s="2">
-        <v>55753</v>
+        <v>73794</v>
       </c>
       <c r="J46" s="2">
-        <v>22176</v>
+        <v>27676</v>
       </c>
       <c r="K46" s="2">
-        <v>2502</v>
+        <v>2965</v>
       </c>
       <c r="L46" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M46" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N46" s="2">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="O46" s="2">
-        <v>915</v>
+        <v>1157</v>
       </c>
       <c r="P46" s="2">
-        <v>161</v>
+        <v>194</v>
       </c>
       <c r="Q46" s="2" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="R46" s="2" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="S46" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T46" s="2" t="s">
-        <v>130</v>
+        <v>133</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F47" s="2">
+        <v>1058517</v>
+      </c>
+      <c r="G47" s="2">
+        <v>8270777</v>
+      </c>
+      <c r="H47" s="2">
+        <v>8080465</v>
+      </c>
+      <c r="I47" s="2">
+        <v>1372897</v>
+      </c>
+      <c r="J47" s="2">
+        <v>329882</v>
+      </c>
+      <c r="K47" s="2">
+        <v>14961</v>
+      </c>
+      <c r="L47" s="2">
+        <v>968</v>
+      </c>
+      <c r="M47" s="2">
+        <v>104</v>
+      </c>
+      <c r="N47" s="2">
+        <v>870</v>
+      </c>
+      <c r="O47" s="2">
+        <v>14925</v>
+      </c>
+      <c r="P47" s="2">
+        <v>1602</v>
+      </c>
+      <c r="Q47" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="R47" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="S47" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="T47" s="2" t="s">
+        <v>133</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/July.xlsx
+++ b/data/July.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="true" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6487D28-2E3B-4D00-9C55-AE84470F05CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,34 +15,31 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>Author</author>
+    <author>ผู้สร้าง</author>
   </authors>
   <commentList>
-    <comment ref="F1" authorId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
+            <sz val="12"/>
             <rFont val="Arial"/>
-            <color/>
-            <sz val="12"/>
           </rPr>
-          <t xml:space="preserve">This is a reach-based metric. Reach-based metrics are de-duplicated metrics so you might see different numbers based on the level at which you are viewing data.</t>
+          <t>This is a reach-based metric. Reach-based metrics are de-duplicated metrics so you might see different numbers based on the level at which you are viewing data.</t>
         </r>
         <r>
           <rPr>
+            <sz val="12"/>
             <rFont val="Arial"/>
-            <color/>
-            <sz val="12"/>
           </rPr>
           <t xml:space="preserve">     </t>
         </r>
         <r>
           <rPr>
+            <sz val="12"/>
             <rFont val="Arial"/>
-            <color/>
-            <sz val="12"/>
           </rPr>
           <t xml:space="preserve">     </t>
         </r>
@@ -52,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="132">
   <si>
     <t>Ad name</t>
   </si>
@@ -192,9 +190,6 @@
     <t>KOLs-OLE CH -ตามหาทองนพคุณ</t>
   </si>
   <si>
-    <t>Total of 45 results</t>
-  </si>
-  <si>
     <t>Primary status</t>
   </si>
   <si>
@@ -391,9 +386,6 @@
   </si>
   <si>
     <t>5000.00</t>
-  </si>
-  <si>
-    <t>106493.29</t>
   </si>
   <si>
     <t>Reach</t>
@@ -459,8 +451,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -468,17 +460,19 @@
       <family val="2"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
       <sz val="12"/>
-      <color/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
-      <color/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="2">
@@ -516,136 +510,140 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
-      <alignment/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<theme xmlns="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
-  <themeElements>
-    <clrScheme name="Office">
-      <dk1>
-        <sysClr val="windowText" lastClr="000000"/>
-      </dk1>
-      <lt1>
-        <sysClr val="window" lastClr="FFFFFF"/>
-      </lt1>
-      <dk2>
-        <srgbClr val="44546A"/>
-      </dk2>
-      <lt2>
-        <srgbClr val="E7E6E6"/>
-      </lt2>
-      <accent1>
-        <srgbClr val="5B9BD5"/>
-      </accent1>
-      <accent2>
-        <srgbClr val="ED7D31"/>
-      </accent2>
-      <accent3>
-        <srgbClr val="A5A5A5"/>
-      </accent3>
-      <accent4>
-        <srgbClr val="FFC000"/>
-      </accent4>
-      <accent5>
-        <srgbClr val="4472C4"/>
-      </accent5>
-      <accent6>
-        <srgbClr val="70AD47"/>
-      </accent6>
-      <hlink>
-        <srgbClr val="0563C1"/>
-      </hlink>
-      <folHlink>
-        <srgbClr val="954F72"/>
-      </folHlink>
-    </clrScheme>
-    <fontScheme name="Office">
-      <majorFont>
-        <latin typeface="Calibri Light" panose="020F0302020204030204"/>
-        <ea typeface=""/>
-        <cs typeface=""/>
-        <font script="Jpan" typeface="游ゴシック Light"/>
-        <font script="Hang" typeface="맑은 고딕"/>
-        <font script="Hans" typeface="等线 Light"/>
-        <font script="Hant" typeface="新細明體"/>
-        <font script="Arab" typeface="Times New Roman"/>
-        <font script="Hebr" typeface="Times New Roman"/>
-        <font script="Thai" typeface="Tahoma"/>
-        <font script="Ethi" typeface="Nyala"/>
-        <font script="Beng" typeface="Vrinda"/>
-        <font script="Gujr" typeface="Shruti"/>
-        <font script="Khmr" typeface="MoolBoran"/>
-        <font script="Knda" typeface="Tunga"/>
-        <font script="Guru" typeface="Raavi"/>
-        <font script="Cans" typeface="Euphemia"/>
-        <font script="Cher" typeface="Plantagenet Cherokee"/>
-        <font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <font script="Tibt" typeface="Microsoft Himalaya"/>
-        <font script="Thaa" typeface="MV Boli"/>
-        <font script="Deva" typeface="Mangal"/>
-        <font script="Telu" typeface="Gautami"/>
-        <font script="Taml" typeface="Latha"/>
-        <font script="Syrc" typeface="Estrangelo Edessa"/>
-        <font script="Orya" typeface="Kalinga"/>
-        <font script="Mlym" typeface="Kartika"/>
-        <font script="Laoo" typeface="DokChampa"/>
-        <font script="Sinh" typeface="Iskoola Pota"/>
-        <font script="Mong" typeface="Mongolian Baiti"/>
-        <font script="Viet" typeface="Times New Roman"/>
-        <font script="Uigh" typeface="Microsoft Uighur"/>
-        <font script="Geor" typeface="Sylfaen"/>
-      </majorFont>
-      <minorFont>
-        <latin typeface="Calibri" panose="020F0502020204030204"/>
-        <ea typeface=""/>
-        <cs typeface=""/>
-        <font script="Jpan" typeface="游ゴシック"/>
-        <font script="Hang" typeface="맑은 고딕"/>
-        <font script="Hans" typeface="等线"/>
-        <font script="Hant" typeface="新細明體"/>
-        <font script="Arab" typeface="Arial"/>
-        <font script="Hebr" typeface="Arial"/>
-        <font script="Thai" typeface="Tahoma"/>
-        <font script="Ethi" typeface="Nyala"/>
-        <font script="Beng" typeface="Vrinda"/>
-        <font script="Gujr" typeface="Shruti"/>
-        <font script="Khmr" typeface="DaunPenh"/>
-        <font script="Knda" typeface="Tunga"/>
-        <font script="Guru" typeface="Raavi"/>
-        <font script="Cans" typeface="Euphemia"/>
-        <font script="Cher" typeface="Plantagenet Cherokee"/>
-        <font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <font script="Tibt" typeface="Microsoft Himalaya"/>
-        <font script="Thaa" typeface="MV Boli"/>
-        <font script="Deva" typeface="Mangal"/>
-        <font script="Telu" typeface="Gautami"/>
-        <font script="Taml" typeface="Latha"/>
-        <font script="Syrc" typeface="Estrangelo Edessa"/>
-        <font script="Orya" typeface="Kalinga"/>
-        <font script="Mlym" typeface="Kartika"/>
-        <font script="Laoo" typeface="DokChampa"/>
-        <font script="Sinh" typeface="Iskoola Pota"/>
-        <font script="Mong" typeface="Mongolian Baiti"/>
-        <font script="Viet" typeface="Arial"/>
-        <font script="Uigh" typeface="Microsoft Uighur"/>
-        <font script="Geor" typeface="Sylfaen"/>
-      </minorFont>
-    </fontScheme>
-    <fmtScheme name="Office">
-      <fillStyleLst>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4472C4"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -701,8 +699,8 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-      </fillStyleLst>
-      <lnStyleLst>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
         <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -724,8 +722,8 @@
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-      </lnStyleLst>
-      <effectStyleLst>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst/>
         </a:effectStyle>
@@ -741,8 +739,8 @@
             </a:outerShdw>
           </a:effectLst>
         </a:effectStyle>
-      </effectStyleLst>
-      <bgFillStyleLst>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -779,96 +777,96 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-      </bgFillStyleLst>
-    </fmtScheme>
-  </themeElements>
-  <objectDefaults/>
-  <extraClrSchemeLst/>
-</theme>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:T46"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="P1" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>125</v>
-      </c>
       <c r="R1" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F2" s="2">
         <v>98035</v>
@@ -904,33 +902,33 @@
         <v>8</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F3" s="2">
         <v>73894</v>
@@ -966,33 +964,33 @@
         <v>12</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F4" s="2">
         <v>75950</v>
@@ -1028,33 +1026,33 @@
         <v>10</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F5" s="2">
         <v>74358</v>
@@ -1090,33 +1088,33 @@
         <v>11</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F6" s="2">
         <v>74183</v>
@@ -1152,33 +1150,33 @@
         <v>10</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F7" s="2">
         <v>73727</v>
@@ -1214,33 +1212,33 @@
         <v>8</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F8" s="2">
         <v>77119</v>
@@ -1276,33 +1274,33 @@
         <v>13</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F9" s="2">
         <v>72209</v>
@@ -1338,33 +1336,33 @@
         <v>16</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F10" s="2">
         <v>79869</v>
@@ -1400,33 +1398,33 @@
         <v>8</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F11" s="2">
         <v>71315</v>
@@ -1462,33 +1460,33 @@
         <v>6</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F12" s="2">
         <v>73382</v>
@@ -1524,33 +1522,33 @@
         <v>12</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F13" s="2">
         <v>74187</v>
@@ -1586,33 +1584,33 @@
         <v>12</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F14" s="2">
         <v>70216</v>
@@ -1648,33 +1646,33 @@
         <v>9</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F15" s="2">
         <v>70059</v>
@@ -1710,33 +1708,33 @@
         <v>14</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F16" s="2">
         <v>70922</v>
@@ -1772,33 +1770,33 @@
         <v>10</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F17" s="2">
         <v>70210</v>
@@ -1834,33 +1832,33 @@
         <v>6</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F18" s="2">
         <v>88692</v>
@@ -1896,33 +1894,33 @@
         <v>8</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F19" s="2">
         <v>87056</v>
@@ -1958,33 +1956,33 @@
         <v>13</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="20">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F20" s="2">
         <v>87808</v>
@@ -2020,33 +2018,33 @@
         <v>4</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="21">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F21" s="2">
         <v>167152</v>
@@ -2082,33 +2080,33 @@
         <v>36</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="22">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F22" s="2">
         <v>126154</v>
@@ -2144,33 +2142,33 @@
         <v>29</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T22" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="23">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F23" s="2">
         <v>92406</v>
@@ -2206,33 +2204,33 @@
         <v>11</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R23" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T23" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="24">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F24" s="2">
         <v>90007</v>
@@ -2268,33 +2266,33 @@
         <v>15</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T24" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="25">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F25" s="2">
         <v>82759</v>
@@ -2330,33 +2328,33 @@
         <v>10</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T25" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="26">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F26" s="2">
         <v>93519</v>
@@ -2392,33 +2390,33 @@
         <v>13</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="S26" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T26" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="27">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F27" s="2">
         <v>87522</v>
@@ -2454,33 +2452,33 @@
         <v>14</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R27" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="S27" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T27" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="28">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F28" s="2">
         <v>86677</v>
@@ -2516,33 +2514,33 @@
         <v>15</v>
       </c>
       <c r="Q28" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R28" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="S28" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T28" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="29">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F29" s="2">
         <v>133541</v>
@@ -2578,33 +2576,33 @@
         <v>25</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R29" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="S29" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T29" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="30">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F30" s="2">
         <v>44370</v>
@@ -2640,33 +2638,33 @@
         <v>26</v>
       </c>
       <c r="Q30" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R30" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="S30" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T30" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="31">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F31" s="2">
         <v>48956</v>
@@ -2702,33 +2700,33 @@
         <v>21</v>
       </c>
       <c r="Q31" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R31" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="S31" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T31" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="32">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F32" s="2">
         <v>48698</v>
@@ -2764,33 +2762,33 @@
         <v>16</v>
       </c>
       <c r="Q32" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R32" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="S32" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T32" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="33">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F33" s="2">
         <v>65283</v>
@@ -2826,33 +2824,33 @@
         <v>18</v>
       </c>
       <c r="Q33" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R33" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="S33" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T33" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="34">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F34" s="2">
         <v>64488</v>
@@ -2888,33 +2886,33 @@
         <v>14</v>
       </c>
       <c r="Q34" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R34" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="S34" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T34" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="35">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F35" s="2">
         <v>67020</v>
@@ -2950,33 +2948,33 @@
         <v>14</v>
       </c>
       <c r="Q35" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R35" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="S35" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T35" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="36">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F36" s="2">
         <v>65002</v>
@@ -3012,33 +3010,33 @@
         <v>13</v>
       </c>
       <c r="Q36" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R36" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="S36" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T36" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="37">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F37" s="2">
         <v>81805</v>
@@ -3074,33 +3072,33 @@
         <v>20</v>
       </c>
       <c r="Q37" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R37" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="S37" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T37" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="38">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F38" s="2">
         <v>87545</v>
@@ -3136,33 +3134,33 @@
         <v>43</v>
       </c>
       <c r="Q38" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R38" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="S38" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T38" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="39">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F39" s="2">
         <v>86716</v>
@@ -3198,33 +3196,33 @@
         <v>13</v>
       </c>
       <c r="Q39" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R39" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="S39" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T39" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="40">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F40" s="2">
         <v>93133</v>
@@ -3260,33 +3258,33 @@
         <v>34</v>
       </c>
       <c r="Q40" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R40" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="S40" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T40" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="41">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F41" s="2">
         <v>162547</v>
@@ -3322,33 +3320,33 @@
         <v>31</v>
       </c>
       <c r="Q41" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R41" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="S41" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T41" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="42">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F42" s="2">
         <v>143231</v>
@@ -3384,33 +3382,33 @@
         <v>18</v>
       </c>
       <c r="Q42" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R42" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="S42" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T42" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="43">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F43" s="2">
         <v>197032</v>
@@ -3446,33 +3444,33 @@
         <v>71</v>
       </c>
       <c r="Q43" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R43" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="S43" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T43" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="44">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F44" s="2">
         <v>151254</v>
@@ -3508,33 +3506,33 @@
         <v>27</v>
       </c>
       <c r="Q44" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R44" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="S44" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T44" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="45">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>44</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F45" s="2">
         <v>204106</v>
@@ -3570,33 +3568,33 @@
         <v>671</v>
       </c>
       <c r="Q45" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="R45" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="S45" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T45" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="46">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F46" s="2">
         <v>194555</v>
@@ -3632,81 +3630,20 @@
         <v>194</v>
       </c>
       <c r="Q46" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="R46" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="S46" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T46" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="F47" s="2">
-        <v>1058517</v>
-      </c>
-      <c r="G47" s="2">
-        <v>8270777</v>
-      </c>
-      <c r="H47" s="2">
-        <v>8080465</v>
-      </c>
-      <c r="I47" s="2">
-        <v>1372897</v>
-      </c>
-      <c r="J47" s="2">
-        <v>329882</v>
-      </c>
-      <c r="K47" s="2">
-        <v>14961</v>
-      </c>
-      <c r="L47" s="2">
-        <v>968</v>
-      </c>
-      <c r="M47" s="2">
-        <v>104</v>
-      </c>
-      <c r="N47" s="2">
-        <v>870</v>
-      </c>
-      <c r="O47" s="2">
-        <v>14925</v>
-      </c>
-      <c r="P47" s="2">
-        <v>1602</v>
-      </c>
-      <c r="Q47" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="R47" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="S47" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="T47" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/July.xlsx
+++ b/data/July.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6487D28-2E3B-4D00-9C55-AE84470F05CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E996C04A-6367-4502-9092-CE2566B02056}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="131">
   <si>
     <t>Ad name</t>
   </si>
@@ -193,9 +193,6 @@
     <t>Primary status</t>
   </si>
   <si>
-    <t>Active</t>
-  </si>
-  <si>
     <t>Ended</t>
   </si>
   <si>
@@ -205,7 +202,7 @@
     <t>Secondary status</t>
   </si>
   <si>
-    <t>--</t>
+    <t>Ad completed</t>
   </si>
   <si>
     <t>Ad completed; Out of ad group budget</t>
@@ -256,133 +253,133 @@
     <t>Spend</t>
   </si>
   <si>
-    <t>1601.48</t>
-  </si>
-  <si>
-    <t>1588.40</t>
-  </si>
-  <si>
-    <t>1582.71</t>
-  </si>
-  <si>
-    <t>1588.25</t>
-  </si>
-  <si>
-    <t>1577.98</t>
-  </si>
-  <si>
-    <t>1528.15</t>
-  </si>
-  <si>
-    <t>1588.75</t>
-  </si>
-  <si>
-    <t>1594.65</t>
-  </si>
-  <si>
-    <t>1582.54</t>
-  </si>
-  <si>
-    <t>1612.54</t>
-  </si>
-  <si>
-    <t>1600.51</t>
-  </si>
-  <si>
-    <t>1586.93</t>
-  </si>
-  <si>
-    <t>1563.67</t>
-  </si>
-  <si>
-    <t>1588.74</t>
-  </si>
-  <si>
-    <t>1577.19</t>
-  </si>
-  <si>
-    <t>1505.92</t>
-  </si>
-  <si>
-    <t>1628.47</t>
-  </si>
-  <si>
-    <t>1601.52</t>
-  </si>
-  <si>
-    <t>1590.33</t>
-  </si>
-  <si>
-    <t>1469.01</t>
-  </si>
-  <si>
-    <t>1433.00</t>
-  </si>
-  <si>
-    <t>1618.59</t>
-  </si>
-  <si>
-    <t>1629.38</t>
-  </si>
-  <si>
-    <t>1621.87</t>
-  </si>
-  <si>
-    <t>1564.99</t>
-  </si>
-  <si>
-    <t>1640.27</t>
-  </si>
-  <si>
-    <t>1522.84</t>
-  </si>
-  <si>
-    <t>1444.07</t>
-  </si>
-  <si>
-    <t>2772.62</t>
-  </si>
-  <si>
-    <t>2755.48</t>
-  </si>
-  <si>
-    <t>2707.49</t>
-  </si>
-  <si>
-    <t>2702.67</t>
-  </si>
-  <si>
-    <t>2749.11</t>
-  </si>
-  <si>
-    <t>2778.75</t>
-  </si>
-  <si>
-    <t>2738.18</t>
-  </si>
-  <si>
-    <t>2853.13</t>
-  </si>
-  <si>
-    <t>2805.46</t>
-  </si>
-  <si>
-    <t>2828.79</t>
-  </si>
-  <si>
-    <t>2816.08</t>
-  </si>
-  <si>
-    <t>5565.84</t>
-  </si>
-  <si>
-    <t>5463.26</t>
-  </si>
-  <si>
-    <t>5367.48</t>
-  </si>
-  <si>
-    <t>5556.20</t>
+    <t>1625.24</t>
+  </si>
+  <si>
+    <t>1616.22</t>
+  </si>
+  <si>
+    <t>1607.80</t>
+  </si>
+  <si>
+    <t>1616.49</t>
+  </si>
+  <si>
+    <t>1605.57</t>
+  </si>
+  <si>
+    <t>1555.16</t>
+  </si>
+  <si>
+    <t>1613.71</t>
+  </si>
+  <si>
+    <t>1618.26</t>
+  </si>
+  <si>
+    <t>1609.66</t>
+  </si>
+  <si>
+    <t>1637.90</t>
+  </si>
+  <si>
+    <t>1625.62</t>
+  </si>
+  <si>
+    <t>1610.65</t>
+  </si>
+  <si>
+    <t>1591.41</t>
+  </si>
+  <si>
+    <t>1614.26</t>
+  </si>
+  <si>
+    <t>1601.02</t>
+  </si>
+  <si>
+    <t>1532.25</t>
+  </si>
+  <si>
+    <t>1650.77</t>
+  </si>
+  <si>
+    <t>1625.92</t>
+  </si>
+  <si>
+    <t>1613.37</t>
+  </si>
+  <si>
+    <t>1493.98</t>
+  </si>
+  <si>
+    <t>1462.08</t>
+  </si>
+  <si>
+    <t>1641.69</t>
+  </si>
+  <si>
+    <t>1649.30</t>
+  </si>
+  <si>
+    <t>1647.88</t>
+  </si>
+  <si>
+    <t>1591.75</t>
+  </si>
+  <si>
+    <t>1661.61</t>
+  </si>
+  <si>
+    <t>1550.17</t>
+  </si>
+  <si>
+    <t>1472.57</t>
+  </si>
+  <si>
+    <t>2812.50</t>
+  </si>
+  <si>
+    <t>2792.68</t>
+  </si>
+  <si>
+    <t>2744.46</t>
+  </si>
+  <si>
+    <t>2740.70</t>
+  </si>
+  <si>
+    <t>2786.93</t>
+  </si>
+  <si>
+    <t>2816.92</t>
+  </si>
+  <si>
+    <t>2777.48</t>
+  </si>
+  <si>
+    <t>2886.45</t>
+  </si>
+  <si>
+    <t>2840.46</t>
+  </si>
+  <si>
+    <t>2863.57</t>
+  </si>
+  <si>
+    <t>2854.00</t>
+  </si>
+  <si>
+    <t>5654.74</t>
+  </si>
+  <si>
+    <t>5535.35</t>
+  </si>
+  <si>
+    <t>5452.87</t>
+  </si>
+  <si>
+    <t>5630.40</t>
   </si>
   <si>
     <t>5000.00</t>
@@ -798,58 +795,58 @@
         <v>46</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="Q1" s="1" t="s">
-        <v>123</v>
-      </c>
       <c r="R1" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="S1" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>129</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -860,31 +857,31 @@
         <v>47</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F2" s="2">
-        <v>98035</v>
+        <v>99650</v>
       </c>
       <c r="G2" s="2">
-        <v>133934</v>
+        <v>135912</v>
       </c>
       <c r="H2" s="2">
-        <v>131600</v>
+        <v>133558</v>
       </c>
       <c r="I2" s="2">
-        <v>23155</v>
+        <v>23496</v>
       </c>
       <c r="J2" s="2">
-        <v>4303</v>
+        <v>4360</v>
       </c>
       <c r="K2" s="2">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L2" s="2">
         <v>1</v>
@@ -896,22 +893,22 @@
         <v>13</v>
       </c>
       <c r="O2" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P2" s="2">
         <v>8</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -922,31 +919,31 @@
         <v>47</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F3" s="2">
-        <v>73894</v>
+        <v>74844</v>
       </c>
       <c r="G3" s="2">
-        <v>120456</v>
+        <v>121624</v>
       </c>
       <c r="H3" s="2">
-        <v>118202</v>
+        <v>119356</v>
       </c>
       <c r="I3" s="2">
-        <v>15405</v>
+        <v>15593</v>
       </c>
       <c r="J3" s="2">
-        <v>3815</v>
+        <v>3865</v>
       </c>
       <c r="K3" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="L3" s="2">
         <v>0</v>
@@ -958,22 +955,22 @@
         <v>9</v>
       </c>
       <c r="O3" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P3" s="2">
         <v>12</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -984,28 +981,28 @@
         <v>47</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F4" s="2">
-        <v>75950</v>
+        <v>77481</v>
       </c>
       <c r="G4" s="2">
-        <v>125330</v>
+        <v>127411</v>
       </c>
       <c r="H4" s="2">
-        <v>122620</v>
+        <v>124671</v>
       </c>
       <c r="I4" s="2">
-        <v>17064</v>
+        <v>17340</v>
       </c>
       <c r="J4" s="2">
-        <v>2751</v>
+        <v>2785</v>
       </c>
       <c r="K4" s="2">
         <v>95</v>
@@ -1020,22 +1017,22 @@
         <v>7</v>
       </c>
       <c r="O4" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="P4" s="2">
         <v>10</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1046,28 +1043,28 @@
         <v>47</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F5" s="2">
-        <v>74358</v>
+        <v>75078</v>
       </c>
       <c r="G5" s="2">
-        <v>116353</v>
+        <v>117444</v>
       </c>
       <c r="H5" s="2">
-        <v>113992</v>
+        <v>115059</v>
       </c>
       <c r="I5" s="2">
-        <v>56945</v>
+        <v>57355</v>
       </c>
       <c r="J5" s="2">
-        <v>15674</v>
+        <v>15774</v>
       </c>
       <c r="K5" s="2">
         <v>158</v>
@@ -1088,16 +1085,16 @@
         <v>11</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1108,28 +1105,28 @@
         <v>47</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F6" s="2">
-        <v>74183</v>
+        <v>74850</v>
       </c>
       <c r="G6" s="2">
-        <v>118646</v>
+        <v>119745</v>
       </c>
       <c r="H6" s="2">
-        <v>116271</v>
+        <v>117350</v>
       </c>
       <c r="I6" s="2">
-        <v>16653</v>
+        <v>16783</v>
       </c>
       <c r="J6" s="2">
-        <v>4169</v>
+        <v>4201</v>
       </c>
       <c r="K6" s="2">
         <v>72</v>
@@ -1144,22 +1141,22 @@
         <v>3</v>
       </c>
       <c r="O6" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P6" s="2">
         <v>10</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1170,31 +1167,31 @@
         <v>47</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F7" s="2">
-        <v>73727</v>
+        <v>75434</v>
       </c>
       <c r="G7" s="2">
-        <v>123052</v>
+        <v>125163</v>
       </c>
       <c r="H7" s="2">
-        <v>120708</v>
+        <v>122778</v>
       </c>
       <c r="I7" s="2">
-        <v>10688</v>
+        <v>10878</v>
       </c>
       <c r="J7" s="2">
-        <v>2003</v>
+        <v>2037</v>
       </c>
       <c r="K7" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L7" s="2">
         <v>0</v>
@@ -1206,22 +1203,22 @@
         <v>3</v>
       </c>
       <c r="O7" s="2">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="P7" s="2">
         <v>8</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1232,28 +1229,28 @@
         <v>47</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F8" s="2">
-        <v>77119</v>
+        <v>78049</v>
       </c>
       <c r="G8" s="2">
-        <v>118871</v>
+        <v>119839</v>
       </c>
       <c r="H8" s="2">
-        <v>116422</v>
+        <v>117375</v>
       </c>
       <c r="I8" s="2">
-        <v>10591</v>
+        <v>10682</v>
       </c>
       <c r="J8" s="2">
-        <v>1777</v>
+        <v>1790</v>
       </c>
       <c r="K8" s="2">
         <v>55</v>
@@ -1268,22 +1265,22 @@
         <v>7</v>
       </c>
       <c r="O8" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P8" s="2">
         <v>13</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1294,31 +1291,31 @@
         <v>47</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F9" s="2">
-        <v>72209</v>
+        <v>73694</v>
       </c>
       <c r="G9" s="2">
-        <v>122934</v>
+        <v>124707</v>
       </c>
       <c r="H9" s="2">
-        <v>120578</v>
+        <v>122319</v>
       </c>
       <c r="I9" s="2">
-        <v>14348</v>
+        <v>14581</v>
       </c>
       <c r="J9" s="2">
-        <v>2604</v>
+        <v>2656</v>
       </c>
       <c r="K9" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L9" s="2">
         <v>0</v>
@@ -1330,22 +1327,22 @@
         <v>18</v>
       </c>
       <c r="O9" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="P9" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1356,31 +1353,31 @@
         <v>47</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F10" s="2">
-        <v>79869</v>
+        <v>81686</v>
       </c>
       <c r="G10" s="2">
-        <v>125236</v>
+        <v>127332</v>
       </c>
       <c r="H10" s="2">
-        <v>122713</v>
+        <v>124775</v>
       </c>
       <c r="I10" s="2">
-        <v>10042</v>
+        <v>10235</v>
       </c>
       <c r="J10" s="2">
-        <v>1992</v>
+        <v>2024</v>
       </c>
       <c r="K10" s="2">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L10" s="2">
         <v>0</v>
@@ -1392,22 +1389,22 @@
         <v>12</v>
       </c>
       <c r="O10" s="2">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="P10" s="2">
         <v>8</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1418,31 +1415,31 @@
         <v>47</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F11" s="2">
-        <v>71315</v>
+        <v>71972</v>
       </c>
       <c r="G11" s="2">
-        <v>120686</v>
+        <v>121668</v>
       </c>
       <c r="H11" s="2">
-        <v>118650</v>
+        <v>119616</v>
       </c>
       <c r="I11" s="2">
-        <v>9653</v>
+        <v>9718</v>
       </c>
       <c r="J11" s="2">
-        <v>2186</v>
+        <v>2206</v>
       </c>
       <c r="K11" s="2">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="L11" s="2">
         <v>1</v>
@@ -1460,16 +1457,16 @@
         <v>6</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1480,31 +1477,31 @@
         <v>47</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F12" s="2">
-        <v>73382</v>
+        <v>73952</v>
       </c>
       <c r="G12" s="2">
-        <v>119578</v>
+        <v>120576</v>
       </c>
       <c r="H12" s="2">
-        <v>117674</v>
+        <v>118655</v>
       </c>
       <c r="I12" s="2">
-        <v>14864</v>
+        <v>14942</v>
       </c>
       <c r="J12" s="2">
-        <v>3081</v>
+        <v>3099</v>
       </c>
       <c r="K12" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L12" s="2">
         <v>0</v>
@@ -1516,22 +1513,22 @@
         <v>3</v>
       </c>
       <c r="O12" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="P12" s="2">
         <v>12</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1542,31 +1539,31 @@
         <v>47</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F13" s="2">
-        <v>74187</v>
+        <v>75717</v>
       </c>
       <c r="G13" s="2">
-        <v>123989</v>
+        <v>125796</v>
       </c>
       <c r="H13" s="2">
-        <v>121646</v>
+        <v>123426</v>
       </c>
       <c r="I13" s="2">
-        <v>11888</v>
+        <v>12087</v>
       </c>
       <c r="J13" s="2">
-        <v>2709</v>
+        <v>2753</v>
       </c>
       <c r="K13" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="L13" s="2">
         <v>0</v>
@@ -1578,22 +1575,22 @@
         <v>7</v>
       </c>
       <c r="O13" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P13" s="2">
         <v>12</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1604,28 +1601,28 @@
         <v>47</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F14" s="2">
-        <v>70216</v>
+        <v>70937</v>
       </c>
       <c r="G14" s="2">
-        <v>118865</v>
+        <v>119990</v>
       </c>
       <c r="H14" s="2">
-        <v>116640</v>
+        <v>117753</v>
       </c>
       <c r="I14" s="2">
-        <v>30450</v>
+        <v>30729</v>
       </c>
       <c r="J14" s="2">
-        <v>12431</v>
+        <v>12544</v>
       </c>
       <c r="K14" s="2">
         <v>163</v>
@@ -1637,25 +1634,25 @@
         <v>1</v>
       </c>
       <c r="N14" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O14" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="P14" s="2">
         <v>9</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="15" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1666,31 +1663,31 @@
         <v>47</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F15" s="2">
-        <v>70059</v>
+        <v>70805</v>
       </c>
       <c r="G15" s="2">
-        <v>115609</v>
+        <v>116575</v>
       </c>
       <c r="H15" s="2">
-        <v>113128</v>
+        <v>114080</v>
       </c>
       <c r="I15" s="2">
-        <v>21912</v>
+        <v>22062</v>
       </c>
       <c r="J15" s="2">
-        <v>3920</v>
+        <v>3936</v>
       </c>
       <c r="K15" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L15" s="2">
         <v>0</v>
@@ -1702,22 +1699,22 @@
         <v>13</v>
       </c>
       <c r="O15" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P15" s="2">
         <v>14</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1728,31 +1725,31 @@
         <v>47</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F16" s="2">
-        <v>70922</v>
+        <v>72373</v>
       </c>
       <c r="G16" s="2">
-        <v>119538</v>
+        <v>121273</v>
       </c>
       <c r="H16" s="2">
-        <v>116771</v>
+        <v>118465</v>
       </c>
       <c r="I16" s="2">
-        <v>20266</v>
+        <v>20541</v>
       </c>
       <c r="J16" s="2">
-        <v>5025</v>
+        <v>5085</v>
       </c>
       <c r="K16" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L16" s="2">
         <v>2</v>
@@ -1764,22 +1761,22 @@
         <v>11</v>
       </c>
       <c r="O16" s="2">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="P16" s="2">
         <v>10</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="17" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1790,31 +1787,31 @@
         <v>47</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F17" s="2">
-        <v>70210</v>
+        <v>71809</v>
       </c>
       <c r="G17" s="2">
-        <v>120830</v>
+        <v>122856</v>
       </c>
       <c r="H17" s="2">
-        <v>118404</v>
+        <v>120380</v>
       </c>
       <c r="I17" s="2">
-        <v>13979</v>
+        <v>14220</v>
       </c>
       <c r="J17" s="2">
-        <v>2962</v>
+        <v>3016</v>
       </c>
       <c r="K17" s="2">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="L17" s="2">
         <v>2</v>
@@ -1826,22 +1823,22 @@
         <v>6</v>
       </c>
       <c r="O17" s="2">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="P17" s="2">
         <v>6</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="18" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1852,31 +1849,31 @@
         <v>47</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F18" s="2">
-        <v>88692</v>
+        <v>90431</v>
       </c>
       <c r="G18" s="2">
-        <v>128829</v>
+        <v>130516</v>
       </c>
       <c r="H18" s="2">
-        <v>126151</v>
+        <v>127812</v>
       </c>
       <c r="I18" s="2">
-        <v>39795</v>
+        <v>40332</v>
       </c>
       <c r="J18" s="2">
-        <v>8483</v>
+        <v>8614</v>
       </c>
       <c r="K18" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="L18" s="2">
         <v>1</v>
@@ -1888,22 +1885,22 @@
         <v>18</v>
       </c>
       <c r="O18" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="P18" s="2">
         <v>8</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="19" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1914,31 +1911,31 @@
         <v>47</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F19" s="2">
-        <v>87056</v>
+        <v>88703</v>
       </c>
       <c r="G19" s="2">
-        <v>128303</v>
+        <v>130216</v>
       </c>
       <c r="H19" s="2">
-        <v>125755</v>
+        <v>127643</v>
       </c>
       <c r="I19" s="2">
-        <v>23170</v>
+        <v>23501</v>
       </c>
       <c r="J19" s="2">
-        <v>3828</v>
+        <v>3881</v>
       </c>
       <c r="K19" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L19" s="2">
         <v>0</v>
@@ -1950,22 +1947,22 @@
         <v>6</v>
       </c>
       <c r="O19" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="P19" s="2">
         <v>13</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="20" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1976,31 +1973,31 @@
         <v>47</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F20" s="2">
-        <v>87808</v>
+        <v>89319</v>
       </c>
       <c r="G20" s="2">
-        <v>129033</v>
+        <v>130868</v>
       </c>
       <c r="H20" s="2">
-        <v>126448</v>
+        <v>128228</v>
       </c>
       <c r="I20" s="2">
-        <v>13452</v>
+        <v>13624</v>
       </c>
       <c r="J20" s="2">
-        <v>2338</v>
+        <v>2372</v>
       </c>
       <c r="K20" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L20" s="2">
         <v>0</v>
@@ -2012,22 +2009,22 @@
         <v>5</v>
       </c>
       <c r="O20" s="2">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="P20" s="2">
         <v>4</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="21" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -2038,31 +2035,31 @@
         <v>47</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F21" s="2">
-        <v>167152</v>
+        <v>171014</v>
       </c>
       <c r="G21" s="2">
-        <v>239732</v>
+        <v>243660</v>
       </c>
       <c r="H21" s="2">
-        <v>230796</v>
+        <v>234578</v>
       </c>
       <c r="I21" s="2">
-        <v>60092</v>
+        <v>61111</v>
       </c>
       <c r="J21" s="2">
-        <v>12149</v>
+        <v>12403</v>
       </c>
       <c r="K21" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="L21" s="2">
         <v>4</v>
@@ -2074,22 +2071,22 @@
         <v>44</v>
       </c>
       <c r="O21" s="2">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="P21" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="22" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -2100,31 +2097,31 @@
         <v>47</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F22" s="2">
-        <v>126154</v>
+        <v>129536</v>
       </c>
       <c r="G22" s="2">
-        <v>186837</v>
+        <v>190380</v>
       </c>
       <c r="H22" s="2">
-        <v>179333</v>
+        <v>182734</v>
       </c>
       <c r="I22" s="2">
-        <v>24787</v>
+        <v>25279</v>
       </c>
       <c r="J22" s="2">
-        <v>4720</v>
+        <v>4817</v>
       </c>
       <c r="K22" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="L22" s="2">
         <v>0</v>
@@ -2136,22 +2133,22 @@
         <v>13</v>
       </c>
       <c r="O22" s="2">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="P22" s="2">
         <v>29</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T22" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="23" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -2162,31 +2159,31 @@
         <v>47</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F23" s="2">
-        <v>92406</v>
+        <v>94123</v>
       </c>
       <c r="G23" s="2">
-        <v>129917</v>
+        <v>131716</v>
       </c>
       <c r="H23" s="2">
-        <v>127413</v>
+        <v>129183</v>
       </c>
       <c r="I23" s="2">
-        <v>17468</v>
+        <v>17722</v>
       </c>
       <c r="J23" s="2">
-        <v>4503</v>
+        <v>4586</v>
       </c>
       <c r="K23" s="2">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="L23" s="2">
         <v>0</v>
@@ -2198,22 +2195,22 @@
         <v>10</v>
       </c>
       <c r="O23" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="P23" s="2">
         <v>11</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R23" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T23" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="24" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -2224,31 +2221,31 @@
         <v>47</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F24" s="2">
-        <v>90007</v>
+        <v>91589</v>
       </c>
       <c r="G24" s="2">
-        <v>129929</v>
+        <v>131465</v>
       </c>
       <c r="H24" s="2">
-        <v>126998</v>
+        <v>128504</v>
       </c>
       <c r="I24" s="2">
-        <v>10252</v>
+        <v>10376</v>
       </c>
       <c r="J24" s="2">
-        <v>1820</v>
+        <v>1851</v>
       </c>
       <c r="K24" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="L24" s="2">
         <v>1</v>
@@ -2260,22 +2257,22 @@
         <v>9</v>
       </c>
       <c r="O24" s="2">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="P24" s="2">
         <v>15</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T24" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="25" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -2286,31 +2283,31 @@
         <v>47</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F25" s="2">
-        <v>82759</v>
+        <v>83655</v>
       </c>
       <c r="G25" s="2">
-        <v>120941</v>
+        <v>121946</v>
       </c>
       <c r="H25" s="2">
-        <v>118641</v>
+        <v>119635</v>
       </c>
       <c r="I25" s="2">
-        <v>12373</v>
+        <v>12463</v>
       </c>
       <c r="J25" s="2">
-        <v>2296</v>
+        <v>2310</v>
       </c>
       <c r="K25" s="2">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L25" s="2">
         <v>1</v>
@@ -2322,22 +2319,22 @@
         <v>6</v>
       </c>
       <c r="O25" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="P25" s="2">
         <v>10</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T25" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="26" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -2348,31 +2345,31 @@
         <v>47</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F26" s="2">
-        <v>93519</v>
+        <v>95502</v>
       </c>
       <c r="G26" s="2">
-        <v>127231</v>
+        <v>129344</v>
       </c>
       <c r="H26" s="2">
-        <v>124578</v>
+        <v>126663</v>
       </c>
       <c r="I26" s="2">
-        <v>25286</v>
+        <v>25696</v>
       </c>
       <c r="J26" s="2">
-        <v>2956</v>
+        <v>2992</v>
       </c>
       <c r="K26" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L26" s="2">
         <v>2</v>
@@ -2384,22 +2381,22 @@
         <v>4</v>
       </c>
       <c r="O26" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="P26" s="2">
         <v>13</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S26" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T26" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="27" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -2410,28 +2407,28 @@
         <v>47</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F27" s="2">
-        <v>87522</v>
+        <v>88234</v>
       </c>
       <c r="G27" s="2">
-        <v>122131</v>
+        <v>122957</v>
       </c>
       <c r="H27" s="2">
-        <v>119283</v>
+        <v>120095</v>
       </c>
       <c r="I27" s="2">
-        <v>12368</v>
+        <v>12446</v>
       </c>
       <c r="J27" s="2">
-        <v>2531</v>
+        <v>2549</v>
       </c>
       <c r="K27" s="2">
         <v>100</v>
@@ -2446,22 +2443,22 @@
         <v>14</v>
       </c>
       <c r="O27" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P27" s="2">
         <v>14</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R27" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S27" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T27" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="28" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -2472,31 +2469,31 @@
         <v>47</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F28" s="2">
-        <v>86677</v>
+        <v>88619</v>
       </c>
       <c r="G28" s="2">
-        <v>120594</v>
+        <v>122677</v>
       </c>
       <c r="H28" s="2">
-        <v>118289</v>
+        <v>120341</v>
       </c>
       <c r="I28" s="2">
-        <v>25411</v>
+        <v>25857</v>
       </c>
       <c r="J28" s="2">
-        <v>5742</v>
+        <v>5824</v>
       </c>
       <c r="K28" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="L28" s="2">
         <v>0</v>
@@ -2505,25 +2502,25 @@
         <v>1</v>
       </c>
       <c r="N28" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O28" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="P28" s="2">
         <v>15</v>
       </c>
       <c r="Q28" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R28" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S28" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T28" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="29" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -2534,31 +2531,31 @@
         <v>47</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F29" s="2">
-        <v>133541</v>
+        <v>137197</v>
       </c>
       <c r="G29" s="2">
-        <v>192733</v>
+        <v>196540</v>
       </c>
       <c r="H29" s="2">
-        <v>186012</v>
+        <v>189734</v>
       </c>
       <c r="I29" s="2">
-        <v>30117</v>
+        <v>30750</v>
       </c>
       <c r="J29" s="2">
-        <v>5171</v>
+        <v>5286</v>
       </c>
       <c r="K29" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="L29" s="2">
         <v>0</v>
@@ -2570,22 +2567,22 @@
         <v>20</v>
       </c>
       <c r="O29" s="2">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="P29" s="2">
         <v>25</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R29" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S29" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T29" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="30" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -2596,58 +2593,58 @@
         <v>47</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F30" s="2">
-        <v>44370</v>
+        <v>44532</v>
       </c>
       <c r="G30" s="2">
-        <v>154353</v>
+        <v>155692</v>
       </c>
       <c r="H30" s="2">
-        <v>151427</v>
+        <v>152743</v>
       </c>
       <c r="I30" s="2">
-        <v>35349</v>
+        <v>35567</v>
       </c>
       <c r="J30" s="2">
-        <v>8310</v>
+        <v>8365</v>
       </c>
       <c r="K30" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="L30" s="2">
         <v>3</v>
       </c>
       <c r="M30" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N30" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O30" s="2">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="P30" s="2">
         <v>26</v>
       </c>
       <c r="Q30" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R30" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S30" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T30" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="31" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -2658,31 +2655,31 @@
         <v>47</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F31" s="2">
-        <v>48956</v>
+        <v>49378</v>
       </c>
       <c r="G31" s="2">
-        <v>165208</v>
+        <v>167462</v>
       </c>
       <c r="H31" s="2">
-        <v>162054</v>
+        <v>164277</v>
       </c>
       <c r="I31" s="2">
-        <v>29838</v>
+        <v>30195</v>
       </c>
       <c r="J31" s="2">
-        <v>5897</v>
+        <v>5950</v>
       </c>
       <c r="K31" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L31" s="2">
         <v>1</v>
@@ -2691,25 +2688,25 @@
         <v>1</v>
       </c>
       <c r="N31" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O31" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P31" s="2">
         <v>21</v>
       </c>
       <c r="Q31" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R31" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S31" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T31" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="32" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -2720,31 +2717,31 @@
         <v>47</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F32" s="2">
-        <v>48698</v>
+        <v>49121</v>
       </c>
       <c r="G32" s="2">
-        <v>154831</v>
+        <v>156915</v>
       </c>
       <c r="H32" s="2">
-        <v>151625</v>
+        <v>153673</v>
       </c>
       <c r="I32" s="2">
-        <v>19245</v>
+        <v>19443</v>
       </c>
       <c r="J32" s="2">
-        <v>4175</v>
+        <v>4220</v>
       </c>
       <c r="K32" s="2">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="L32" s="2">
         <v>0</v>
@@ -2756,22 +2753,22 @@
         <v>14</v>
       </c>
       <c r="O32" s="2">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="P32" s="2">
         <v>16</v>
       </c>
       <c r="Q32" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R32" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S32" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T32" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="33" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -2782,31 +2779,31 @@
         <v>47</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F33" s="2">
-        <v>65283</v>
+        <v>66127</v>
       </c>
       <c r="G33" s="2">
-        <v>192719</v>
+        <v>195374</v>
       </c>
       <c r="H33" s="2">
-        <v>188720</v>
+        <v>191319</v>
       </c>
       <c r="I33" s="2">
-        <v>18381</v>
+        <v>18621</v>
       </c>
       <c r="J33" s="2">
-        <v>3954</v>
+        <v>4024</v>
       </c>
       <c r="K33" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="L33" s="2">
         <v>0</v>
@@ -2818,22 +2815,22 @@
         <v>14</v>
       </c>
       <c r="O33" s="2">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="P33" s="2">
         <v>18</v>
       </c>
       <c r="Q33" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R33" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S33" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T33" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="34" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -2844,28 +2841,28 @@
         <v>47</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F34" s="2">
-        <v>64488</v>
+        <v>65200</v>
       </c>
       <c r="G34" s="2">
-        <v>199289</v>
+        <v>201955</v>
       </c>
       <c r="H34" s="2">
-        <v>194744</v>
+        <v>197352</v>
       </c>
       <c r="I34" s="2">
-        <v>12303</v>
+        <v>12484</v>
       </c>
       <c r="J34" s="2">
-        <v>3241</v>
+        <v>3286</v>
       </c>
       <c r="K34" s="2">
         <v>98</v>
@@ -2880,22 +2877,22 @@
         <v>7</v>
       </c>
       <c r="O34" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="P34" s="2">
         <v>14</v>
       </c>
       <c r="Q34" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R34" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S34" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T34" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="35" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -2906,31 +2903,31 @@
         <v>47</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F35" s="2">
-        <v>67020</v>
+        <v>67847</v>
       </c>
       <c r="G35" s="2">
-        <v>195592</v>
+        <v>198248</v>
       </c>
       <c r="H35" s="2">
-        <v>191646</v>
+        <v>194261</v>
       </c>
       <c r="I35" s="2">
-        <v>15134</v>
+        <v>15337</v>
       </c>
       <c r="J35" s="2">
-        <v>3674</v>
+        <v>3718</v>
       </c>
       <c r="K35" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L35" s="2">
         <v>0</v>
@@ -2942,22 +2939,22 @@
         <v>13</v>
       </c>
       <c r="O35" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="P35" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q35" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R35" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S35" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T35" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="36" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -2968,31 +2965,31 @@
         <v>47</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F36" s="2">
-        <v>65002</v>
+        <v>65628</v>
       </c>
       <c r="G36" s="2">
-        <v>199302</v>
+        <v>202101</v>
       </c>
       <c r="H36" s="2">
-        <v>195407</v>
+        <v>198168</v>
       </c>
       <c r="I36" s="2">
-        <v>12434</v>
+        <v>12611</v>
       </c>
       <c r="J36" s="2">
-        <v>3380</v>
+        <v>3429</v>
       </c>
       <c r="K36" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L36" s="2">
         <v>1</v>
@@ -3004,22 +3001,22 @@
         <v>12</v>
       </c>
       <c r="O36" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="P36" s="2">
         <v>13</v>
       </c>
       <c r="Q36" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R36" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S36" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T36" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="37" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -3030,31 +3027,31 @@
         <v>47</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F37" s="2">
-        <v>81805</v>
+        <v>82066</v>
       </c>
       <c r="G37" s="2">
-        <v>192498</v>
+        <v>193694</v>
       </c>
       <c r="H37" s="2">
-        <v>189034</v>
+        <v>190206</v>
       </c>
       <c r="I37" s="2">
-        <v>50178</v>
+        <v>50434</v>
       </c>
       <c r="J37" s="2">
-        <v>6617</v>
+        <v>6660</v>
       </c>
       <c r="K37" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L37" s="2">
         <v>0</v>
@@ -3066,22 +3063,22 @@
         <v>17</v>
       </c>
       <c r="O37" s="2">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="P37" s="2">
         <v>20</v>
       </c>
       <c r="Q37" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R37" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S37" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T37" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="38" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -3092,31 +3089,31 @@
         <v>47</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F38" s="2">
-        <v>87545</v>
+        <v>88726</v>
       </c>
       <c r="G38" s="2">
-        <v>207461</v>
+        <v>209906</v>
       </c>
       <c r="H38" s="2">
-        <v>203340</v>
+        <v>205735</v>
       </c>
       <c r="I38" s="2">
-        <v>66993</v>
+        <v>67736</v>
       </c>
       <c r="J38" s="2">
-        <v>13034</v>
+        <v>13193</v>
       </c>
       <c r="K38" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="L38" s="2">
         <v>2</v>
@@ -3128,22 +3125,22 @@
         <v>17</v>
       </c>
       <c r="O38" s="2">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="P38" s="2">
         <v>43</v>
       </c>
       <c r="Q38" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R38" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S38" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T38" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="39" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -3154,31 +3151,31 @@
         <v>47</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F39" s="2">
-        <v>86716</v>
+        <v>87712</v>
       </c>
       <c r="G39" s="2">
-        <v>211526</v>
+        <v>214026</v>
       </c>
       <c r="H39" s="2">
-        <v>207968</v>
+        <v>210437</v>
       </c>
       <c r="I39" s="2">
-        <v>38064</v>
+        <v>38427</v>
       </c>
       <c r="J39" s="2">
-        <v>4873</v>
+        <v>4928</v>
       </c>
       <c r="K39" s="2">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L39" s="2">
         <v>1</v>
@@ -3190,22 +3187,22 @@
         <v>10</v>
       </c>
       <c r="O39" s="2">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="P39" s="2">
         <v>13</v>
       </c>
       <c r="Q39" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R39" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S39" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T39" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="40" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -3216,31 +3213,31 @@
         <v>47</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F40" s="2">
-        <v>93133</v>
+        <v>94223</v>
       </c>
       <c r="G40" s="2">
-        <v>209858</v>
+        <v>212524</v>
       </c>
       <c r="H40" s="2">
-        <v>205454</v>
+        <v>208069</v>
       </c>
       <c r="I40" s="2">
-        <v>59082</v>
+        <v>59743</v>
       </c>
       <c r="J40" s="2">
-        <v>10490</v>
+        <v>10579</v>
       </c>
       <c r="K40" s="2">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="L40" s="2">
         <v>1</v>
@@ -3252,22 +3249,22 @@
         <v>15</v>
       </c>
       <c r="O40" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="P40" s="2">
         <v>34</v>
       </c>
       <c r="Q40" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R40" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S40" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T40" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="41" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -3278,31 +3275,31 @@
         <v>47</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F41" s="2">
-        <v>162547</v>
+        <v>165473</v>
       </c>
       <c r="G41" s="2">
-        <v>436446</v>
+        <v>443794</v>
       </c>
       <c r="H41" s="2">
-        <v>427624</v>
+        <v>434829</v>
       </c>
       <c r="I41" s="2">
-        <v>80269</v>
+        <v>81551</v>
       </c>
       <c r="J41" s="2">
-        <v>7787</v>
+        <v>7895</v>
       </c>
       <c r="K41" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L41" s="2">
         <v>0</v>
@@ -3314,22 +3311,22 @@
         <v>17</v>
       </c>
       <c r="O41" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="P41" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q41" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R41" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S41" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T41" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="42" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -3340,31 +3337,31 @@
         <v>47</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F42" s="2">
-        <v>143231</v>
+        <v>145541</v>
       </c>
       <c r="G42" s="2">
-        <v>426819</v>
+        <v>432718</v>
       </c>
       <c r="H42" s="2">
-        <v>417651</v>
+        <v>423433</v>
       </c>
       <c r="I42" s="2">
-        <v>26821</v>
+        <v>27209</v>
       </c>
       <c r="J42" s="2">
-        <v>5037</v>
+        <v>5112</v>
       </c>
       <c r="K42" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L42" s="2">
         <v>0</v>
@@ -3373,25 +3370,25 @@
         <v>2</v>
       </c>
       <c r="N42" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O42" s="2">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="P42" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q42" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R42" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S42" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T42" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="43" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -3402,31 +3399,31 @@
         <v>47</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F43" s="2">
-        <v>197032</v>
+        <v>200079</v>
       </c>
       <c r="G43" s="2">
-        <v>404517</v>
+        <v>407896</v>
       </c>
       <c r="H43" s="2">
-        <v>395159</v>
+        <v>398413</v>
       </c>
       <c r="I43" s="2">
-        <v>70160</v>
+        <v>70523</v>
       </c>
       <c r="J43" s="2">
-        <v>16819</v>
+        <v>16898</v>
       </c>
       <c r="K43" s="2">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="L43" s="2">
         <v>2</v>
@@ -3438,22 +3435,22 @@
         <v>47</v>
       </c>
       <c r="O43" s="2">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="P43" s="2">
         <v>71</v>
       </c>
       <c r="Q43" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R43" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S43" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T43" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="44" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -3464,31 +3461,31 @@
         <v>47</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F44" s="2">
-        <v>151254</v>
+        <v>152156</v>
       </c>
       <c r="G44" s="2">
-        <v>396606</v>
+        <v>399611</v>
       </c>
       <c r="H44" s="2">
-        <v>387785</v>
+        <v>390744</v>
       </c>
       <c r="I44" s="2">
-        <v>37320</v>
+        <v>37643</v>
       </c>
       <c r="J44" s="2">
-        <v>5803</v>
+        <v>5844</v>
       </c>
       <c r="K44" s="2">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="L44" s="2">
         <v>2</v>
@@ -3500,22 +3497,22 @@
         <v>21</v>
       </c>
       <c r="O44" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="P44" s="2">
         <v>27</v>
       </c>
       <c r="Q44" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R44" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S44" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T44" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="45" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -3523,16 +3520,16 @@
         <v>44</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F45" s="2">
         <v>204106</v>
@@ -3568,16 +3565,16 @@
         <v>671</v>
       </c>
       <c r="Q45" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="R45" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="S45" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T45" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="46" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -3585,16 +3582,16 @@
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F46" s="2">
         <v>194555</v>
@@ -3630,16 +3627,16 @@
         <v>194</v>
       </c>
       <c r="Q46" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="R46" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="S46" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T46" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
